--- a/Server/Received_data/Statistics/2025/Documents/Исходные данные за 2025 год.xlsx
+++ b/Server/Received_data/Statistics/2025/Documents/Исходные данные за 2025 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,11 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-1</t>
+          <t>ADOM-SL1-1-2025</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6934</v>
+        <v>6933</v>
       </c>
       <c r="E2" t="n">
         <v>69.16</v>
@@ -575,16 +575,16 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6539</v>
+        <v>0.04134</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3278</v>
+        <v>0.4221</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5536</v>
+        <v>0.06924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4062</v>
+        <v>0.2189</v>
       </c>
     </row>
     <row r="3">
@@ -592,17 +592,17 @@
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-10</t>
+          <t>ADOM-SL1-10-2025</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.869</v>
+        <v>6.352</v>
       </c>
       <c r="E3" t="n">
         <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>2.063</v>
+        <v>2.128</v>
       </c>
       <c r="G3" t="n">
         <v>7.23</v>
@@ -623,16 +623,16 @@
         <v>11.84</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.06589</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5688</v>
+        <v>0.6765</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.1101</v>
       </c>
       <c r="P3" t="n">
-        <v>0.653</v>
+        <v>0.3415</v>
       </c>
     </row>
     <row r="4">
@@ -640,11 +640,11 @@
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-3</t>
+          <t>ADOM-SL1-3-2025</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3937</v>
+        <v>2960</v>
       </c>
       <c r="E4" t="n">
         <v>33.8</v>
@@ -671,16 +671,16 @@
         <v>19.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4236</v>
+        <v>0.01686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4759</v>
+        <v>0.4609</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1754</v>
+        <v>0.0294</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-4</t>
+          <t>ADOM-SL1-4-2025</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -719,16 +719,16 @@
         <v>12.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2706</v>
+        <v>0.01742</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1892</v>
+        <v>0.2201</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2153</v>
+        <v>0.02231</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3126</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="6">
@@ -736,17 +736,17 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-5</t>
+          <t>ADOM-SL1-5-2025</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="E6" t="n">
         <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0.1002</v>
       </c>
       <c r="G6" t="n">
         <v>7.43</v>
@@ -767,16 +767,16 @@
         <v>6.927</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0514</v>
+        <v>0.004694</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04848</v>
+        <v>0.03601</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08825</v>
+        <v>0.00695</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07754999999999999</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="7">
@@ -784,11 +784,11 @@
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-6</t>
+          <t>ADOM-SL1-6-2025</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.055</v>
+        <v>5.053</v>
       </c>
       <c r="E7" t="n">
         <v>15.63</v>
@@ -815,16 +815,16 @@
         <v>16.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4376</v>
+        <v>0.02474</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3193</v>
+        <v>0.3832</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2526</v>
+        <v>0.03167</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.2494</v>
       </c>
     </row>
     <row r="8">
@@ -832,11 +832,11 @@
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-7</t>
+          <t>ADOM-SL1-7-2025</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.356</v>
+        <v>5.355</v>
       </c>
       <c r="E8" t="n">
         <v>16.12</v>
@@ -863,16 +863,16 @@
         <v>11.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.515</v>
+        <v>0.031</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3331</v>
+        <v>0.375</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4045</v>
+        <v>0.0525</v>
       </c>
       <c r="P8" t="n">
-        <v>0.479</v>
+        <v>0.2546</v>
       </c>
     </row>
     <row r="9">
@@ -880,7 +880,7 @@
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-8</t>
+          <t>ADOM-SL1-8-2025</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -911,16 +911,16 @@
         <v>16.99</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4758</v>
+        <v>0.02706</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3629</v>
+        <v>0.4265</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2674</v>
+        <v>0.03355</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5982</v>
+        <v>0.2913</v>
       </c>
     </row>
     <row r="10">
@@ -928,11 +928,11 @@
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL1-9</t>
+          <t>ADOM-SL1-9-2025</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.444</v>
+        <v>5.443</v>
       </c>
       <c r="E10" t="n">
         <v>8.755000000000001</v>
@@ -959,16 +959,16 @@
         <v>17.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7108</v>
+        <v>0.03869</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5517</v>
+        <v>0.6432</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4018</v>
+        <v>0.05252</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8022</v>
+        <v>0.3849</v>
       </c>
     </row>
     <row r="11">
@@ -980,17 +980,17 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-1</t>
+          <t>ADOM-SL10-1-2025</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.985</v>
+        <v>1.268</v>
       </c>
       <c r="E11" t="n">
         <v>7.019</v>
       </c>
       <c r="F11" t="n">
-        <v>2.066</v>
+        <v>4.665</v>
       </c>
       <c r="G11" t="n">
         <v>4.19</v>
@@ -1011,16 +1011,16 @@
         <v>8.742000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3547</v>
+        <v>0.01953</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4662</v>
+        <v>0.3234</v>
       </c>
       <c r="O11" t="n">
-        <v>0.577</v>
+        <v>0.05286</v>
       </c>
       <c r="P11" t="n">
-        <v>0.388</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="12">
@@ -1028,17 +1028,17 @@
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-10</t>
+          <t>ADOM-SL10-10-2025</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2.124</v>
       </c>
       <c r="E12" t="n">
         <v>12.26</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9625</v>
+        <v>1.191</v>
       </c>
       <c r="G12" t="n">
         <v>5.59</v>
@@ -1059,16 +1059,16 @@
         <v>4.038</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3745</v>
+        <v>0.03045</v>
       </c>
       <c r="N12" t="n">
-        <v>0.112</v>
+        <v>0.1216</v>
       </c>
       <c r="O12" t="n">
-        <v>0.633</v>
+        <v>0.06293</v>
       </c>
       <c r="P12" t="n">
-        <v>0.08652</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1076,7 +1076,7 @@
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-2</t>
+          <t>ADOM-SL10-2-2025</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1107,16 +1107,16 @@
         <v>20.56</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5737</v>
+        <v>0.0236</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5105</v>
+        <v>0.5645</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2292</v>
+        <v>0.04383</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5964</v>
+        <v>0.2878</v>
       </c>
     </row>
     <row r="14">
@@ -1124,17 +1124,17 @@
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-3</t>
+          <t>ADOM-SL10-3-2025</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.339</v>
+        <v>2.168</v>
       </c>
       <c r="E14" t="n">
         <v>10.54</v>
       </c>
       <c r="F14" t="n">
-        <v>1.917</v>
+        <v>2.449</v>
       </c>
       <c r="G14" t="n">
         <v>4.01</v>
@@ -1155,16 +1155,16 @@
         <v>16.31</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5423</v>
+        <v>0.022</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5121</v>
+        <v>0.5117</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2676</v>
+        <v>0.04758</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5296</v>
+        <v>0.2781</v>
       </c>
     </row>
     <row r="15">
@@ -1172,11 +1172,11 @@
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-4</t>
+          <t>ADOM-SL10-4-2025</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.304</v>
+        <v>4.303</v>
       </c>
       <c r="E15" t="n">
         <v>4.835</v>
@@ -1203,16 +1203,16 @@
         <v>18.13</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5896</v>
+        <v>0.02033</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7244</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2427</v>
+        <v>0.05027</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7696</v>
+        <v>0.4155</v>
       </c>
     </row>
     <row r="16">
@@ -1220,17 +1220,17 @@
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-5</t>
+          <t>ADOM-SL10-5-2025</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.652</v>
+        <v>2.195</v>
       </c>
       <c r="E16" t="n">
         <v>13.22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6959</v>
+        <v>0.9082</v>
       </c>
       <c r="G16" t="n">
         <v>5.49</v>
@@ -1251,16 +1251,16 @@
         <v>5.798</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2447</v>
+        <v>0.01684</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1362</v>
+        <v>0.1307</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3168</v>
+        <v>0.03744</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1455</v>
+        <v>0.09651</v>
       </c>
     </row>
     <row r="17">
@@ -1268,17 +1268,17 @@
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-6</t>
+          <t>ADOM-SL10-6-2025</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.572</v>
+        <v>1.656</v>
       </c>
       <c r="E17" t="n">
         <v>4.182</v>
       </c>
       <c r="F17" t="n">
-        <v>13.27</v>
+        <v>19.98</v>
       </c>
       <c r="G17" t="n">
         <v>4.87</v>
@@ -1299,16 +1299,16 @@
         <v>12.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7274</v>
+        <v>0.03238</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0.7744</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.08885</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0.5357</v>
       </c>
     </row>
     <row r="18">
@@ -1316,17 +1316,17 @@
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-7</t>
+          <t>ADOM-SL10-7-2025</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.449</v>
+        <v>1.779</v>
       </c>
       <c r="E18" t="n">
         <v>24.07</v>
       </c>
       <c r="F18" t="n">
-        <v>1.068</v>
+        <v>1.417</v>
       </c>
       <c r="G18" t="n">
         <v>5.47</v>
@@ -1347,16 +1347,16 @@
         <v>4.934</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2708</v>
+        <v>0.02016</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1156</v>
+        <v>0.1232</v>
       </c>
       <c r="O18" t="n">
-        <v>0.381</v>
+        <v>0.04316</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1379</v>
+        <v>0.09449</v>
       </c>
     </row>
     <row r="19">
@@ -1364,17 +1364,17 @@
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL10-9</t>
+          <t>ADOM-SL10-9-2025</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.478</v>
+        <v>2.762</v>
       </c>
       <c r="E19" t="n">
         <v>9.007999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>2.986</v>
+        <v>3.298</v>
       </c>
       <c r="G19" t="n">
         <v>4.09</v>
@@ -1395,16 +1395,16 @@
         <v>16.27</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6233</v>
+        <v>0.02318</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6067</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3115</v>
+        <v>0.05572</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5816</v>
+        <v>0.2985</v>
       </c>
     </row>
     <row r="20">
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-10</t>
+          <t>ADOM-SL2-10-2025</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.846</v>
+        <v>1.945</v>
       </c>
       <c r="E20" t="n">
         <v>11.45</v>
       </c>
       <c r="F20" t="n">
-        <v>4.367</v>
+        <v>5.715</v>
       </c>
       <c r="G20" t="n">
         <v>4.5</v>
@@ -1447,16 +1447,16 @@
         <v>14.48</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4208</v>
+        <v>0.01404</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5192</v>
+        <v>0.4547</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2381</v>
+        <v>0.0394</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4016</v>
+        <v>0.2127</v>
       </c>
     </row>
     <row r="21">
@@ -1464,17 +1464,17 @@
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-2</t>
+          <t>ADOM-SL2-2-2025</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.401</v>
+        <v>2.372</v>
       </c>
       <c r="E21" t="n">
         <v>24.62</v>
       </c>
       <c r="F21" t="n">
-        <v>3.964</v>
+        <v>4.762</v>
       </c>
       <c r="G21" t="n">
         <v>5.5</v>
@@ -1495,16 +1495,16 @@
         <v>12.18</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4537</v>
+        <v>0.02114</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4497</v>
+        <v>0.4147</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3038</v>
+        <v>0.04571</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4673</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="22">
@@ -1512,17 +1512,17 @@
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-3</t>
+          <t>ADOM-SL2-3-2025</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.912</v>
+        <v>1.785</v>
       </c>
       <c r="E22" t="n">
         <v>24.03</v>
       </c>
       <c r="F22" t="n">
-        <v>2.697</v>
+        <v>3.923</v>
       </c>
       <c r="G22" t="n">
         <v>5.94</v>
@@ -1543,16 +1543,16 @@
         <v>9.978</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3811</v>
+        <v>0.01965</v>
       </c>
       <c r="N22" t="n">
-        <v>0.297</v>
+        <v>0.2964</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3024</v>
+        <v>0.04459</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2976</v>
+        <v>0.1665</v>
       </c>
     </row>
     <row r="23">
@@ -1560,17 +1560,17 @@
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-5</t>
+          <t>ADOM-SL2-5-2025</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.139</v>
+        <v>2.295</v>
       </c>
       <c r="E23" t="n">
         <v>6.966</v>
       </c>
       <c r="F23" t="n">
-        <v>2.139</v>
+        <v>2.542</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1591,16 +1591,16 @@
         <v>10.29</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3573</v>
+        <v>0.01785</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3084</v>
+        <v>0.3071</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2793</v>
+        <v>0.03682</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2963</v>
+        <v>0.1589</v>
       </c>
     </row>
     <row r="24">
@@ -1608,17 +1608,17 @@
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-6</t>
+          <t>ADOM-SL2-6-2025</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.105</v>
+        <v>1.999</v>
       </c>
       <c r="E24" t="n">
         <v>2.448</v>
       </c>
       <c r="F24" t="n">
-        <v>5.31</v>
+        <v>7.029</v>
       </c>
       <c r="G24" t="n">
         <v>6.07</v>
@@ -1639,16 +1639,16 @@
         <v>16.04</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5407</v>
+        <v>0.02532</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5585</v>
+        <v>0.5544</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3507</v>
+        <v>0.04387</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5618</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="25">
@@ -1656,17 +1656,17 @@
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-7</t>
+          <t>ADOM-SL2-7-2025</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.066</v>
+        <v>1.92</v>
       </c>
       <c r="E25" t="n">
         <v>5.335</v>
       </c>
       <c r="F25" t="n">
-        <v>2.849</v>
+        <v>3.901</v>
       </c>
       <c r="G25" t="n">
         <v>5.6</v>
@@ -1687,16 +1687,16 @@
         <v>13.71</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4207</v>
+        <v>0.01864</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4424</v>
+        <v>0.4061</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2849</v>
+        <v>0.04041</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4564</v>
+        <v>0.2404</v>
       </c>
     </row>
     <row r="26">
@@ -1704,17 +1704,17 @@
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-8</t>
+          <t>ADOM-SL2-8-2025</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.812</v>
+        <v>1.689</v>
       </c>
       <c r="E26" t="n">
         <v>9.819000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>3.534</v>
+        <v>5.392</v>
       </c>
       <c r="G26" t="n">
         <v>5.29</v>
@@ -1735,16 +1735,16 @@
         <v>14.23</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4466</v>
+        <v>0.01899</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4218</v>
+        <v>0.418</v>
       </c>
       <c r="O26" t="n">
-        <v>0.233</v>
+        <v>0.03987</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4289</v>
+        <v>0.2246</v>
       </c>
     </row>
     <row r="27">
@@ -1752,17 +1752,17 @@
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-9</t>
+          <t>ADOM-SL2-9-2025</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.79</v>
+        <v>1.616</v>
       </c>
       <c r="E27" t="n">
         <v>7.737</v>
       </c>
       <c r="F27" t="n">
-        <v>3.218</v>
+        <v>5.213</v>
       </c>
       <c r="G27" t="n">
         <v>3.72</v>
@@ -1783,16 +1783,16 @@
         <v>15.11</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4245</v>
+        <v>0.01407</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4679</v>
+        <v>0.4428</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2064</v>
+        <v>0.03842</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3769</v>
+        <v>0.1952</v>
       </c>
     </row>
     <row r="28">
@@ -1804,47 +1804,47 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-2</t>
+          <t>ADOM-SL3-5-2025</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.318</v>
+        <v>1.548</v>
       </c>
       <c r="E28" t="n">
-        <v>14.55</v>
+        <v>6.378</v>
       </c>
       <c r="F28" t="n">
-        <v>4.297</v>
+        <v>4.693</v>
       </c>
       <c r="G28" t="n">
-        <v>5.77</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-115</v>
+        <v>-59</v>
       </c>
       <c r="I28" t="n">
-        <v>4.509</v>
+        <v>4.527</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8922</v>
+        <v>0.7696</v>
       </c>
       <c r="K28" t="n">
-        <v>1.353</v>
+        <v>1.396</v>
       </c>
       <c r="L28" t="n">
-        <v>12.61</v>
+        <v>14.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2988</v>
+        <v>0.01512</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3456</v>
+        <v>0.3248</v>
       </c>
       <c r="O28" t="n">
-        <v>0.3876</v>
+        <v>0.02716</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3478</v>
+        <v>0.1766</v>
       </c>
     </row>
     <row r="29">
@@ -1852,147 +1852,147 @@
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-5</t>
+          <t>ADOM-SL3-6-2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.741</v>
+        <v>2.174</v>
       </c>
       <c r="E29" t="n">
-        <v>6.378</v>
+        <v>5.197</v>
       </c>
       <c r="F29" t="n">
-        <v>2.713</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>7.15</v>
       </c>
       <c r="H29" t="n">
-        <v>-59</v>
+        <v>-35</v>
       </c>
       <c r="I29" t="n">
-        <v>4.527</v>
+        <v>4.78</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7696</v>
+        <v>0.8157</v>
       </c>
       <c r="K29" t="n">
-        <v>1.396</v>
+        <v>1.368</v>
       </c>
       <c r="L29" t="n">
-        <v>14.37</v>
+        <v>14.38</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3261</v>
+        <v>0.01422</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3254</v>
+        <v>0.2361</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2083</v>
+        <v>0.02211</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3494</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Storage 4</t>
+        </is>
+      </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-6</t>
+          <t>ADOM-SL4-1-2025</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.31</v>
+        <v>4.654</v>
       </c>
       <c r="E30" t="n">
-        <v>5.197</v>
+        <v>30.24</v>
       </c>
       <c r="F30" t="n">
-        <v>2.04</v>
+        <v>0.5457</v>
       </c>
       <c r="G30" t="n">
-        <v>7.15</v>
+        <v>9.18</v>
       </c>
       <c r="H30" t="n">
-        <v>-35</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
-        <v>4.78</v>
+        <v>5.162</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8157</v>
+        <v>1.217</v>
       </c>
       <c r="K30" t="n">
-        <v>1.368</v>
+        <v>1.495</v>
       </c>
       <c r="L30" t="n">
-        <v>14.38</v>
+        <v>6.572</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2611</v>
+        <v>0.01007</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2151</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1838</v>
+        <v>0.01357</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2713</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Storage 4</t>
-        </is>
-      </c>
+      <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-1</t>
+          <t>ADOM-SL4-2-2025</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.656</v>
+        <v>2.082</v>
       </c>
       <c r="E31" t="n">
-        <v>30.24</v>
+        <v>22.83</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5456</v>
+        <v>2.468</v>
       </c>
       <c r="G31" t="n">
-        <v>9.18</v>
+        <v>7.78</v>
       </c>
       <c r="H31" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I31" t="n">
-        <v>5.162</v>
+        <v>5.028</v>
       </c>
       <c r="J31" t="n">
-        <v>1.217</v>
+        <v>0.6597</v>
       </c>
       <c r="K31" t="n">
-        <v>1.495</v>
+        <v>1.435</v>
       </c>
       <c r="L31" t="n">
-        <v>6.572</v>
+        <v>21.35</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1157</v>
+        <v>0.01738</v>
       </c>
       <c r="N31" t="n">
-        <v>0.06069</v>
+        <v>0.3456</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1589</v>
+        <v>0.02753</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1139</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="32">
@@ -2000,47 +2000,47 @@
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-2</t>
+          <t>ADOM-SL4-3-2025</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.804</v>
+        <v>4.412</v>
       </c>
       <c r="E32" t="n">
-        <v>22.83</v>
+        <v>10.18</v>
       </c>
       <c r="F32" t="n">
-        <v>1.792</v>
+        <v>1.395</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78</v>
+        <v>7.56</v>
       </c>
       <c r="H32" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="I32" t="n">
-        <v>5.028</v>
+        <v>4.893</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6597</v>
+        <v>0.7004</v>
       </c>
       <c r="K32" t="n">
-        <v>1.435</v>
+        <v>1.382</v>
       </c>
       <c r="L32" t="n">
-        <v>21.35</v>
+        <v>20.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3777</v>
+        <v>0.01859</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2786</v>
+        <v>0.3305</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1428</v>
+        <v>0.028</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3732</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="33">
@@ -2048,47 +2048,47 @@
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-3</t>
+          <t>ADOM-SL4-4-2025</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.414</v>
+        <v>3.548</v>
       </c>
       <c r="E33" t="n">
-        <v>10.18</v>
+        <v>8.74</v>
       </c>
       <c r="F33" t="n">
-        <v>1.395</v>
+        <v>1.396</v>
       </c>
       <c r="G33" t="n">
-        <v>7.56</v>
+        <v>6.95</v>
       </c>
       <c r="H33" t="n">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="I33" t="n">
-        <v>4.893</v>
+        <v>4.648</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7004</v>
+        <v>0.8043</v>
       </c>
       <c r="K33" t="n">
-        <v>1.382</v>
+        <v>1.366</v>
       </c>
       <c r="L33" t="n">
-        <v>20.06</v>
+        <v>13.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3772</v>
+        <v>0.01318</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2581</v>
+        <v>0.1817</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1627</v>
+        <v>0.01974</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3704</v>
+        <v>0.1166</v>
       </c>
     </row>
     <row r="34">
@@ -2096,47 +2096,47 @@
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-4</t>
+          <t>ADOM-SL4-5-2025</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.548</v>
+        <v>3.498</v>
       </c>
       <c r="E34" t="n">
-        <v>8.74</v>
+        <v>6.687</v>
       </c>
       <c r="F34" t="n">
-        <v>1.396</v>
+        <v>1.511</v>
       </c>
       <c r="G34" t="n">
-        <v>6.95</v>
+        <v>7.9</v>
       </c>
       <c r="H34" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>4.648</v>
+        <v>5.084</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8043</v>
+        <v>0.9669</v>
       </c>
       <c r="K34" t="n">
-        <v>1.366</v>
+        <v>1.481</v>
       </c>
       <c r="L34" t="n">
-        <v>13.7</v>
+        <v>10.87</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2272</v>
+        <v>0.02028</v>
       </c>
       <c r="N34" t="n">
-        <v>0.15</v>
+        <v>0.2602</v>
       </c>
       <c r="O34" t="n">
-        <v>0.15</v>
+        <v>0.03134</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2266</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="35">
@@ -2144,47 +2144,47 @@
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-5</t>
+          <t>ADOM-SL4-6-2025</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>2.112</v>
       </c>
       <c r="E35" t="n">
-        <v>6.687</v>
+        <v>6.655</v>
       </c>
       <c r="F35" t="n">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="G35" t="n">
-        <v>7.9</v>
+        <v>7.62</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="I35" t="n">
-        <v>5.084</v>
+        <v>5.286</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9669</v>
+        <v>0.8024</v>
       </c>
       <c r="K35" t="n">
-        <v>1.481</v>
+        <v>1.443</v>
       </c>
       <c r="L35" t="n">
-        <v>10.87</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3308</v>
+        <v>0.01533</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2163</v>
+        <v>0.2425</v>
       </c>
       <c r="O35" t="n">
-        <v>0.289</v>
+        <v>0.0237</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3075</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="36">
@@ -2192,47 +2192,47 @@
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-6</t>
+          <t>ADOM-SL4-7-2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.029</v>
+        <v>3.823</v>
       </c>
       <c r="E36" t="n">
-        <v>6.655</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>1.698</v>
+        <v>1.187</v>
       </c>
       <c r="G36" t="n">
-        <v>7.62</v>
+        <v>8.16</v>
       </c>
       <c r="H36" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="I36" t="n">
-        <v>5.286</v>
+        <v>5.202</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8024</v>
+        <v>0.9537</v>
       </c>
       <c r="K36" t="n">
-        <v>1.443</v>
+        <v>1.407</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>9.884</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2881</v>
+        <v>0.01314</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1876</v>
+        <v>0.1479</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1636</v>
+        <v>0.019</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2652</v>
+        <v>0.09665</v>
       </c>
     </row>
     <row r="37">
@@ -2240,47 +2240,47 @@
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-7</t>
+          <t>ADOM-SL4-8-2025</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.826</v>
+        <v>1.086</v>
       </c>
       <c r="E37" t="n">
-        <v>8.260999999999999</v>
+        <v>5.989</v>
       </c>
       <c r="F37" t="n">
-        <v>1.186</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>8.16</v>
+        <v>7.66</v>
       </c>
       <c r="H37" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I37" t="n">
-        <v>5.202</v>
+        <v>4.898</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9537</v>
+        <v>0.8845</v>
       </c>
       <c r="K37" t="n">
-        <v>1.407</v>
+        <v>1.371</v>
       </c>
       <c r="L37" t="n">
-        <v>9.884</v>
+        <v>12.27</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2021</v>
+        <v>0.01798</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1141</v>
+        <v>0.2375</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1678</v>
+        <v>0.02637</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1855</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="38">
@@ -2288,147 +2288,147 @@
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-8</t>
+          <t>ADOM-SL4-9-2025</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.503</v>
+        <v>1.803</v>
       </c>
       <c r="E38" t="n">
-        <v>5.989</v>
+        <v>10.11</v>
       </c>
       <c r="F38" t="n">
-        <v>4.409</v>
+        <v>4.821</v>
       </c>
       <c r="G38" t="n">
-        <v>7.66</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="I38" t="n">
-        <v>4.898</v>
+        <v>4.567</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8845</v>
+        <v>0.577</v>
       </c>
       <c r="K38" t="n">
-        <v>1.371</v>
+        <v>1.373</v>
       </c>
       <c r="L38" t="n">
-        <v>12.27</v>
+        <v>28.37</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2985</v>
+        <v>0.02514</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1904</v>
+        <v>0.6325</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2268</v>
+        <v>0.04413</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2851</v>
+        <v>0.3088</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Storage 5</t>
+        </is>
+      </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-9</t>
+          <t>ADOM-SL5-10-2025</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.808</v>
+        <v>3.12</v>
       </c>
       <c r="E39" t="n">
-        <v>10.11</v>
+        <v>8.589</v>
       </c>
       <c r="F39" t="n">
-        <v>3.017</v>
+        <v>2.958</v>
       </c>
       <c r="G39" t="n">
-        <v>8.289999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="H39" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4.567</v>
+        <v>4.937</v>
       </c>
       <c r="J39" t="n">
-        <v>0.577</v>
+        <v>0.786</v>
       </c>
       <c r="K39" t="n">
-        <v>1.373</v>
+        <v>1.441</v>
       </c>
       <c r="L39" t="n">
-        <v>28.37</v>
+        <v>16.35</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6498</v>
+        <v>0.03037</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5289</v>
+        <v>0.5641</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1565</v>
+        <v>0.05713</v>
       </c>
       <c r="P39" t="n">
-        <v>0.6518</v>
+        <v>0.2696</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Storage 5</t>
-        </is>
-      </c>
+      <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-10</t>
+          <t>ADOM-SL5-5-2025</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.413</v>
+        <v>1.985</v>
       </c>
       <c r="E40" t="n">
-        <v>8.589</v>
+        <v>5.377</v>
       </c>
       <c r="F40" t="n">
-        <v>2.631</v>
+        <v>2.829</v>
       </c>
       <c r="G40" t="n">
-        <v>7.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I40" t="n">
-        <v>4.937</v>
+        <v>5.189</v>
       </c>
       <c r="J40" t="n">
-        <v>0.786</v>
+        <v>0.9896</v>
       </c>
       <c r="K40" t="n">
-        <v>1.441</v>
+        <v>1.471</v>
       </c>
       <c r="L40" t="n">
-        <v>16.35</v>
+        <v>11.54</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.02226</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4616</v>
+        <v>0.2991</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3088</v>
+        <v>0.03865</v>
       </c>
       <c r="P40" t="n">
-        <v>0.5481</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="41">
@@ -2436,47 +2436,47 @@
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-5</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.414</v>
+        <v>2.332</v>
       </c>
       <c r="E41" t="n">
-        <v>5.377</v>
+        <v>2.09</v>
       </c>
       <c r="F41" t="n">
-        <v>2.046</v>
+        <v>6.177</v>
       </c>
       <c r="G41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="H41" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="I41" t="n">
-        <v>5.189</v>
+        <v>5.135</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9896</v>
+        <v>0.7693</v>
       </c>
       <c r="K41" t="n">
-        <v>1.471</v>
+        <v>1.426</v>
       </c>
       <c r="L41" t="n">
-        <v>11.54</v>
+        <v>16.24</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4083</v>
+        <v>0.02916</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2204</v>
+        <v>0.5155</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2567</v>
+        <v>0.04511</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2905</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="42">
@@ -2484,17 +2484,17 @@
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.956</v>
+        <v>2.332</v>
       </c>
       <c r="E42" t="n">
         <v>2.09</v>
       </c>
       <c r="F42" t="n">
-        <v>4.834</v>
+        <v>6.177</v>
       </c>
       <c r="G42" t="n">
         <v>7.9</v>
@@ -2515,16 +2515,16 @@
         <v>16.24</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5845</v>
+        <v>0.02916</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4093</v>
+        <v>0.5155</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2945</v>
+        <v>0.04511</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="43">
@@ -2532,17 +2532,17 @@
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.956</v>
+        <v>2.332</v>
       </c>
       <c r="E43" t="n">
         <v>2.09</v>
       </c>
       <c r="F43" t="n">
-        <v>4.834</v>
+        <v>6.177</v>
       </c>
       <c r="G43" t="n">
         <v>7.9</v>
@@ -2563,16 +2563,16 @@
         <v>16.24</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5845</v>
+        <v>0.02916</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4093</v>
+        <v>0.5155</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2945</v>
+        <v>0.04511</v>
       </c>
       <c r="P43" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="44">
@@ -2580,47 +2580,47 @@
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6</t>
+          <t>ADOM-SL5-7-2025</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.956</v>
+        <v>4.7</v>
       </c>
       <c r="E44" t="n">
-        <v>2.09</v>
+        <v>4.861</v>
       </c>
       <c r="F44" t="n">
-        <v>4.834</v>
+        <v>2.139</v>
       </c>
       <c r="G44" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="H44" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I44" t="n">
-        <v>5.135</v>
+        <v>4.883</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7693</v>
+        <v>0.9748</v>
       </c>
       <c r="K44" t="n">
-        <v>1.426</v>
+        <v>1.448</v>
       </c>
       <c r="L44" t="n">
-        <v>16.24</v>
+        <v>11.25</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5845</v>
+        <v>0.02195</v>
       </c>
       <c r="N44" t="n">
-        <v>0.4093</v>
+        <v>0.2926</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2945</v>
+        <v>0.03929</v>
       </c>
       <c r="P44" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="45">
@@ -2628,7 +2628,7 @@
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7</t>
+          <t>ADOM-SL5-7-2025</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2659,16 +2659,16 @@
         <v>11.25</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3986</v>
+        <v>0.02195</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2339</v>
+        <v>0.2926</v>
       </c>
       <c r="O45" t="n">
-        <v>0.2742</v>
+        <v>0.03929</v>
       </c>
       <c r="P45" t="n">
-        <v>0.3054</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="46">
@@ -2676,47 +2676,47 @@
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.7</v>
+        <v>4.237</v>
       </c>
       <c r="E46" t="n">
-        <v>4.861</v>
+        <v>5.999</v>
       </c>
       <c r="F46" t="n">
-        <v>2.139</v>
+        <v>2.967</v>
       </c>
       <c r="G46" t="n">
-        <v>7.8</v>
+        <v>8.15</v>
       </c>
       <c r="H46" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I46" t="n">
-        <v>4.883</v>
+        <v>4.427</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9748</v>
+        <v>0.7196</v>
       </c>
       <c r="K46" t="n">
-        <v>1.448</v>
+        <v>1.362</v>
       </c>
       <c r="L46" t="n">
-        <v>11.25</v>
+        <v>15.77</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3986</v>
+        <v>0.02534</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2339</v>
+        <v>0.4913</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2742</v>
+        <v>0.0466</v>
       </c>
       <c r="P46" t="n">
-        <v>0.3054</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="47">
@@ -2724,7 +2724,7 @@
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2755,16 +2755,16 @@
         <v>15.77</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.02534</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4413</v>
+        <v>0.4913</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2674</v>
+        <v>0.0466</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5269</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="48">
@@ -2772,7 +2772,7 @@
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2803,16 +2803,16 @@
         <v>15.77</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.02534</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4413</v>
+        <v>0.4913</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2674</v>
+        <v>0.0466</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5269</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="49">
@@ -2820,47 +2820,47 @@
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8</t>
+          <t>ADOM-SL5-9-2025</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.237</v>
+        <v>4.071</v>
       </c>
       <c r="E49" t="n">
-        <v>5.999</v>
+        <v>7.726</v>
       </c>
       <c r="F49" t="n">
-        <v>2.967</v>
+        <v>3.275</v>
       </c>
       <c r="G49" t="n">
-        <v>8.15</v>
+        <v>7.67</v>
       </c>
       <c r="H49" t="n">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="I49" t="n">
-        <v>4.427</v>
+        <v>4.309</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7196</v>
+        <v>0.631</v>
       </c>
       <c r="K49" t="n">
-        <v>1.362</v>
+        <v>1.317</v>
       </c>
       <c r="L49" t="n">
-        <v>15.77</v>
+        <v>19.52</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.02894</v>
       </c>
       <c r="N49" t="n">
-        <v>0.4413</v>
+        <v>0.6939</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2674</v>
+        <v>0.05412</v>
       </c>
       <c r="P49" t="n">
-        <v>0.5269</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="50">
@@ -2868,7 +2868,7 @@
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9</t>
+          <t>ADOM-SL5-9-2025</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2899,86 +2899,86 @@
         <v>19.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.02894</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6401</v>
+        <v>0.6939</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2525</v>
+        <v>0.05412</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7209</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="n"/>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Storage 6</t>
+        </is>
+      </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9</t>
+          <t>ADOM-SL6-1-2025</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.071</v>
+        <v>2.858</v>
       </c>
       <c r="E51" t="n">
-        <v>7.726</v>
+        <v>24.45</v>
       </c>
       <c r="F51" t="n">
-        <v>3.275</v>
+        <v>2.925</v>
       </c>
       <c r="G51" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="H51" t="n">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="I51" t="n">
-        <v>4.309</v>
+        <v>4.584</v>
       </c>
       <c r="J51" t="n">
-        <v>0.631</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>1.317</v>
+        <v>1.395</v>
       </c>
       <c r="L51" t="n">
-        <v>19.52</v>
+        <v>28.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.01775</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6401</v>
+        <v>0.4815</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2525</v>
+        <v>0.03025</v>
       </c>
       <c r="P51" t="n">
-        <v>0.7209</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>Storage 6</t>
-        </is>
-      </c>
+      <c r="B52" s="1" t="n"/>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1</t>
+          <t>ADOM-SL6-1-2025</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.252</v>
+        <v>2.858</v>
       </c>
       <c r="E52" t="n">
         <v>24.45</v>
       </c>
       <c r="F52" t="n">
-        <v>2.524</v>
+        <v>2.925</v>
       </c>
       <c r="G52" t="n">
         <v>7.54</v>
@@ -2999,16 +2999,16 @@
         <v>28.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4695</v>
+        <v>0.01775</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4265</v>
+        <v>0.4815</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1058</v>
+        <v>0.03025</v>
       </c>
       <c r="P52" t="n">
-        <v>0.5131</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="53">
@@ -3016,47 +3016,47 @@
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1</t>
+          <t>ADOM-SL6-10-2025</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.252</v>
+        <v>4.135</v>
       </c>
       <c r="E53" t="n">
-        <v>24.45</v>
+        <v>7.377</v>
       </c>
       <c r="F53" t="n">
-        <v>2.524</v>
+        <v>2.779</v>
       </c>
       <c r="G53" t="n">
-        <v>7.54</v>
+        <v>7.68</v>
       </c>
       <c r="H53" t="n">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="I53" t="n">
-        <v>4.584</v>
+        <v>4.499</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5392</v>
       </c>
       <c r="K53" t="n">
-        <v>1.395</v>
+        <v>1.331</v>
       </c>
       <c r="L53" t="n">
-        <v>28.5</v>
+        <v>31.71</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4695</v>
+        <v>0.02497</v>
       </c>
       <c r="N53" t="n">
-        <v>0.4265</v>
+        <v>0.5331</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1058</v>
+        <v>0.03323</v>
       </c>
       <c r="P53" t="n">
-        <v>0.5131</v>
+        <v>0.2959</v>
       </c>
     </row>
     <row r="54">
@@ -3064,11 +3064,11 @@
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10</t>
+          <t>ADOM-SL6-10-2025</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.136</v>
+        <v>4.135</v>
       </c>
       <c r="E54" t="n">
         <v>7.377</v>
@@ -3095,16 +3095,16 @@
         <v>31.71</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5564</v>
+        <v>0.02497</v>
       </c>
       <c r="N54" t="n">
-        <v>0.4087</v>
+        <v>0.5331</v>
       </c>
       <c r="O54" t="n">
-        <v>0.1353</v>
+        <v>0.03323</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6397</v>
+        <v>0.2959</v>
       </c>
     </row>
     <row r="55">
@@ -3112,47 +3112,47 @@
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10</t>
+          <t>ADOM-SL6-2-2025</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.136</v>
+        <v>4.199</v>
       </c>
       <c r="E55" t="n">
-        <v>7.377</v>
+        <v>13.93</v>
       </c>
       <c r="F55" t="n">
-        <v>2.779</v>
+        <v>2.175</v>
       </c>
       <c r="G55" t="n">
-        <v>7.68</v>
+        <v>6.61</v>
       </c>
       <c r="H55" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I55" t="n">
-        <v>4.499</v>
+        <v>4.712</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5392</v>
+        <v>0.8028</v>
       </c>
       <c r="K55" t="n">
-        <v>1.331</v>
+        <v>1.415</v>
       </c>
       <c r="L55" t="n">
-        <v>31.71</v>
+        <v>14.4</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5564</v>
+        <v>0.02235</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4087</v>
+        <v>0.4232</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1353</v>
+        <v>0.04509</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6397</v>
+        <v>0.2539</v>
       </c>
     </row>
     <row r="56">
@@ -3160,11 +3160,11 @@
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2</t>
+          <t>ADOM-SL6-2-2025</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.2</v>
+        <v>4.199</v>
       </c>
       <c r="E56" t="n">
         <v>13.93</v>
@@ -3191,16 +3191,16 @@
         <v>14.4</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4419</v>
+        <v>0.02235</v>
       </c>
       <c r="N56" t="n">
-        <v>0.4445</v>
+        <v>0.4232</v>
       </c>
       <c r="O56" t="n">
-        <v>0.428</v>
+        <v>0.04509</v>
       </c>
       <c r="P56" t="n">
-        <v>0.4944</v>
+        <v>0.2539</v>
       </c>
     </row>
     <row r="57">
@@ -3208,47 +3208,47 @@
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.2</v>
+        <v>4.619</v>
       </c>
       <c r="E57" t="n">
-        <v>13.93</v>
+        <v>8.983000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>2.175</v>
+        <v>2.093</v>
       </c>
       <c r="G57" t="n">
-        <v>6.61</v>
+        <v>6.91</v>
       </c>
       <c r="H57" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I57" t="n">
-        <v>4.712</v>
+        <v>4.516</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8028</v>
+        <v>0.6419</v>
       </c>
       <c r="K57" t="n">
-        <v>1.415</v>
+        <v>1.369</v>
       </c>
       <c r="L57" t="n">
-        <v>14.4</v>
+        <v>20.53</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4419</v>
+        <v>0.01709</v>
       </c>
       <c r="N57" t="n">
-        <v>0.4445</v>
+        <v>0.3512</v>
       </c>
       <c r="O57" t="n">
-        <v>0.428</v>
+        <v>0.02824</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4944</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="58">
@@ -3256,11 +3256,11 @@
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.621</v>
+        <v>4.619</v>
       </c>
       <c r="E58" t="n">
         <v>8.983000000000001</v>
@@ -3287,16 +3287,16 @@
         <v>20.53</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3722</v>
+        <v>0.01709</v>
       </c>
       <c r="N58" t="n">
-        <v>0.3124</v>
+        <v>0.3512</v>
       </c>
       <c r="O58" t="n">
-        <v>0.1685</v>
+        <v>0.02824</v>
       </c>
       <c r="P58" t="n">
-        <v>0.4066</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="59">
@@ -3304,11 +3304,11 @@
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.621</v>
+        <v>4.619</v>
       </c>
       <c r="E59" t="n">
         <v>8.983000000000001</v>
@@ -3335,16 +3335,16 @@
         <v>20.53</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3722</v>
+        <v>0.01709</v>
       </c>
       <c r="N59" t="n">
-        <v>0.3124</v>
+        <v>0.3512</v>
       </c>
       <c r="O59" t="n">
-        <v>0.1685</v>
+        <v>0.02824</v>
       </c>
       <c r="P59" t="n">
-        <v>0.4066</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="60">
@@ -3352,47 +3352,47 @@
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3</t>
+          <t>ADOM-SL6-4-2025</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.621</v>
+        <v>3.639</v>
       </c>
       <c r="E60" t="n">
-        <v>8.983000000000001</v>
+        <v>8.987</v>
       </c>
       <c r="F60" t="n">
-        <v>2.093</v>
+        <v>2.226</v>
       </c>
       <c r="G60" t="n">
-        <v>6.91</v>
+        <v>6.63</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>-46</v>
       </c>
       <c r="I60" t="n">
-        <v>4.516</v>
+        <v>4.954</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6419</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>1.369</v>
+        <v>1.436</v>
       </c>
       <c r="L60" t="n">
-        <v>20.53</v>
+        <v>12.45</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3722</v>
+        <v>0.02173</v>
       </c>
       <c r="N60" t="n">
-        <v>0.3124</v>
+        <v>0.3436</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1685</v>
+        <v>0.04184</v>
       </c>
       <c r="P60" t="n">
-        <v>0.4066</v>
+        <v>0.2084</v>
       </c>
     </row>
     <row r="61">
@@ -3400,17 +3400,17 @@
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4</t>
+          <t>ADOM-SL6-4-2025</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.64</v>
+        <v>3.639</v>
       </c>
       <c r="E61" t="n">
         <v>8.987</v>
       </c>
       <c r="F61" t="n">
-        <v>2.225</v>
+        <v>2.226</v>
       </c>
       <c r="G61" t="n">
         <v>6.63</v>
@@ -3431,16 +3431,16 @@
         <v>12.45</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3883</v>
+        <v>0.02173</v>
       </c>
       <c r="N61" t="n">
-        <v>0.3511</v>
+        <v>0.3436</v>
       </c>
       <c r="O61" t="n">
-        <v>0.4133</v>
+        <v>0.04184</v>
       </c>
       <c r="P61" t="n">
-        <v>0.4013</v>
+        <v>0.2084</v>
       </c>
     </row>
     <row r="62">
@@ -3448,47 +3448,47 @@
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4</t>
+          <t>ADOM-SL6-6-2025</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.64</v>
+        <v>2.998</v>
       </c>
       <c r="E62" t="n">
-        <v>8.987</v>
+        <v>8.151</v>
       </c>
       <c r="F62" t="n">
-        <v>2.225</v>
+        <v>1.73</v>
       </c>
       <c r="G62" t="n">
-        <v>6.63</v>
+        <v>6.99</v>
       </c>
       <c r="H62" t="n">
-        <v>-46</v>
+        <v>-43</v>
       </c>
       <c r="I62" t="n">
-        <v>4.954</v>
+        <v>4.513</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8676</v>
       </c>
       <c r="K62" t="n">
-        <v>1.436</v>
+        <v>1.374</v>
       </c>
       <c r="L62" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3883</v>
+        <v>0.01654</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3511</v>
+        <v>0.2206</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4133</v>
+        <v>0.02485</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4013</v>
+        <v>0.1534</v>
       </c>
     </row>
     <row r="63">
@@ -3496,47 +3496,47 @@
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-6</t>
+          <t>ADOM-SL6-7-2025</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4.115</v>
       </c>
       <c r="E63" t="n">
-        <v>8.151</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="G63" t="n">
-        <v>6.99</v>
+        <v>7.15</v>
       </c>
       <c r="H63" t="n">
-        <v>-43</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>4.513</v>
+        <v>4.706</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8676</v>
+        <v>0.8653</v>
       </c>
       <c r="K63" t="n">
-        <v>1.374</v>
+        <v>1.359</v>
       </c>
       <c r="L63" t="n">
-        <v>12.4</v>
+        <v>13.32</v>
       </c>
       <c r="M63" t="n">
-        <v>0.2658</v>
+        <v>0.02341</v>
       </c>
       <c r="N63" t="n">
-        <v>0.2043</v>
+        <v>0.3523</v>
       </c>
       <c r="O63" t="n">
-        <v>0.243</v>
+        <v>0.04123</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2979</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="64">
@@ -3544,47 +3544,47 @@
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-7</t>
+          <t>ADOM-SL6-8-2025</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4.115</v>
+        <v>2.197</v>
       </c>
       <c r="E64" t="n">
-        <v>8.904999999999999</v>
+        <v>9.698</v>
       </c>
       <c r="F64" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="G64" t="n">
-        <v>7.15</v>
+        <v>6.98</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>-93</v>
       </c>
       <c r="I64" t="n">
-        <v>4.706</v>
+        <v>5.121</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8653</v>
+        <v>0.8416</v>
       </c>
       <c r="K64" t="n">
-        <v>1.359</v>
+        <v>1.458</v>
       </c>
       <c r="L64" t="n">
-        <v>13.32</v>
+        <v>15.11</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4093</v>
+        <v>0.02161</v>
       </c>
       <c r="N64" t="n">
-        <v>0.334</v>
+        <v>0.4261</v>
       </c>
       <c r="O64" t="n">
-        <v>0.3961</v>
+        <v>0.04956</v>
       </c>
       <c r="P64" t="n">
-        <v>0.4323</v>
+        <v>0.2285</v>
       </c>
     </row>
     <row r="65">
@@ -3592,147 +3592,147 @@
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-8</t>
+          <t>ADOM-SL6-9-2025</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.835</v>
+        <v>4.888</v>
       </c>
       <c r="E65" t="n">
-        <v>9.698</v>
+        <v>9.523</v>
       </c>
       <c r="F65" t="n">
-        <v>2.526</v>
+        <v>2.562</v>
       </c>
       <c r="G65" t="n">
-        <v>6.98</v>
+        <v>8.01</v>
       </c>
       <c r="H65" t="n">
-        <v>-93</v>
+        <v>10</v>
       </c>
       <c r="I65" t="n">
-        <v>5.121</v>
+        <v>4.894</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8416</v>
+        <v>0.6965</v>
       </c>
       <c r="K65" t="n">
-        <v>1.458</v>
+        <v>1.389</v>
       </c>
       <c r="L65" t="n">
-        <v>15.11</v>
+        <v>19.96</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4496</v>
+        <v>0.02365</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4482</v>
+        <v>0.4933</v>
       </c>
       <c r="O65" t="n">
-        <v>0.4485</v>
+        <v>0.04115</v>
       </c>
       <c r="P65" t="n">
-        <v>0.4434</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="n"/>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Storage 7</t>
+        </is>
+      </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-9</t>
+          <t>ADOM-SL7-1-2025</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4.889</v>
+        <v>2.971</v>
       </c>
       <c r="E66" t="n">
-        <v>9.523</v>
+        <v>20.8</v>
       </c>
       <c r="F66" t="n">
-        <v>2.562</v>
+        <v>2.876</v>
       </c>
       <c r="G66" t="n">
-        <v>8.01</v>
+        <v>7.06</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="I66" t="n">
-        <v>4.894</v>
+        <v>4.511</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6965</v>
+        <v>0.576</v>
       </c>
       <c r="K66" t="n">
-        <v>1.389</v>
+        <v>1.356</v>
       </c>
       <c r="L66" t="n">
-        <v>19.96</v>
+        <v>23.04</v>
       </c>
       <c r="M66" t="n">
-        <v>0.5286</v>
+        <v>0.01435</v>
       </c>
       <c r="N66" t="n">
-        <v>0.4232</v>
+        <v>0.4037</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2401</v>
+        <v>0.02957</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4983</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Storage 7</t>
-        </is>
-      </c>
+      <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-1</t>
+          <t>ADOM-SL7-10-2025</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4.164</v>
+        <v>2.332</v>
       </c>
       <c r="E67" t="n">
-        <v>20.8</v>
+        <v>9.772</v>
       </c>
       <c r="F67" t="n">
-        <v>2.538</v>
+        <v>2.703</v>
       </c>
       <c r="G67" t="n">
-        <v>7.06</v>
+        <v>7.71</v>
       </c>
       <c r="H67" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="I67" t="n">
-        <v>4.511</v>
+        <v>4.075</v>
       </c>
       <c r="J67" t="n">
-        <v>0.576</v>
+        <v>0.6398</v>
       </c>
       <c r="K67" t="n">
-        <v>1.356</v>
+        <v>1.298</v>
       </c>
       <c r="L67" t="n">
-        <v>23.04</v>
+        <v>16.01</v>
       </c>
       <c r="M67" t="n">
-        <v>0.3879</v>
+        <v>0.01696</v>
       </c>
       <c r="N67" t="n">
-        <v>0.4</v>
+        <v>0.3117</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1431</v>
+        <v>0.02842</v>
       </c>
       <c r="P67" t="n">
-        <v>0.4223</v>
+        <v>0.2034</v>
       </c>
     </row>
     <row r="68">
@@ -3740,47 +3740,47 @@
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-10</t>
+          <t>ADOM-SL7-2-2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.857</v>
+        <v>3.182</v>
       </c>
       <c r="E68" t="n">
-        <v>9.772</v>
+        <v>8.198</v>
       </c>
       <c r="F68" t="n">
-        <v>2.129</v>
+        <v>1.611</v>
       </c>
       <c r="G68" t="n">
-        <v>7.71</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>80</v>
+        <v>-4</v>
       </c>
       <c r="I68" t="n">
-        <v>4.075</v>
+        <v>3.964</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6398</v>
+        <v>1.85</v>
       </c>
       <c r="K68" t="n">
-        <v>1.298</v>
+        <v>1.341</v>
       </c>
       <c r="L68" t="n">
-        <v>16.01</v>
+        <v>4.411</v>
       </c>
       <c r="M68" t="n">
-        <v>0.3541</v>
+        <v>0.02292</v>
       </c>
       <c r="N68" t="n">
-        <v>0.281</v>
+        <v>0.04119</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1675</v>
+        <v>0.05266</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3918</v>
+        <v>0.1515</v>
       </c>
     </row>
     <row r="69">
@@ -3788,47 +3788,47 @@
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-2</t>
+          <t>ADOM-SL7-3-2025</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4.458</v>
+        <v>3.628</v>
       </c>
       <c r="E69" t="n">
-        <v>8.198</v>
+        <v>17.65</v>
       </c>
       <c r="F69" t="n">
-        <v>1.439</v>
+        <v>1.218</v>
       </c>
       <c r="G69" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="H69" t="n">
-        <v>-4</v>
+        <v>-165</v>
       </c>
       <c r="I69" t="n">
-        <v>3.964</v>
+        <v>5.545</v>
       </c>
       <c r="J69" t="n">
-        <v>1.85</v>
+        <v>1.146</v>
       </c>
       <c r="K69" t="n">
-        <v>1.341</v>
+        <v>1.515</v>
       </c>
       <c r="L69" t="n">
-        <v>4.411</v>
+        <v>9.685</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1953</v>
+        <v>0.0175</v>
       </c>
       <c r="N69" t="n">
-        <v>0.1278</v>
+        <v>0.1963</v>
       </c>
       <c r="O69" t="n">
-        <v>0.7457</v>
+        <v>0.03261</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2148</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="70">
@@ -3836,47 +3836,47 @@
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-3</t>
+          <t>ADOM-SL7-5-2025</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4.55</v>
+        <v>2.793</v>
       </c>
       <c r="E70" t="n">
-        <v>17.65</v>
+        <v>7.129</v>
       </c>
       <c r="F70" t="n">
-        <v>1.139</v>
+        <v>1.656</v>
       </c>
       <c r="G70" t="n">
-        <v>6.9</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-165</v>
+        <v>12</v>
       </c>
       <c r="I70" t="n">
-        <v>5.545</v>
+        <v>4.005</v>
       </c>
       <c r="J70" t="n">
-        <v>1.146</v>
+        <v>1.012</v>
       </c>
       <c r="K70" t="n">
-        <v>1.515</v>
+        <v>1.342</v>
       </c>
       <c r="L70" t="n">
-        <v>9.685</v>
+        <v>7.656</v>
       </c>
       <c r="M70" t="n">
-        <v>0.2914</v>
+        <v>0.01558</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1633</v>
+        <v>0.1339</v>
       </c>
       <c r="O70" t="n">
-        <v>0.2579</v>
+        <v>0.02096</v>
       </c>
       <c r="P70" t="n">
-        <v>0.2006</v>
+        <v>0.1312</v>
       </c>
     </row>
     <row r="71">
@@ -3884,47 +3884,47 @@
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-5</t>
+          <t>ADOM-SL7-6-2025</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.8</v>
+        <v>2.264</v>
       </c>
       <c r="E71" t="n">
-        <v>7.129</v>
+        <v>9.097</v>
       </c>
       <c r="F71" t="n">
-        <v>1.459</v>
+        <v>1.309</v>
       </c>
       <c r="G71" t="n">
-        <v>8.210000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>4.005</v>
+        <v>3.69</v>
       </c>
       <c r="J71" t="n">
-        <v>1.012</v>
+        <v>0.9691</v>
       </c>
       <c r="K71" t="n">
-        <v>1.342</v>
+        <v>1.295</v>
       </c>
       <c r="L71" t="n">
-        <v>7.656</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>0.1991</v>
+        <v>0.01189</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1286</v>
+        <v>0.0949</v>
       </c>
       <c r="O71" t="n">
-        <v>0.2419</v>
+        <v>0.01796</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2376</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="72">
@@ -3932,47 +3932,47 @@
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-6</t>
+          <t>ADOM-SL7-7-2025</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.952</v>
+        <v>2.863</v>
       </c>
       <c r="E72" t="n">
-        <v>9.097</v>
+        <v>6.717</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>1.742</v>
       </c>
       <c r="G72" t="n">
-        <v>8.640000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I72" t="n">
-        <v>3.69</v>
+        <v>4.22</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9691</v>
+        <v>1.022</v>
       </c>
       <c r="K72" t="n">
-        <v>1.295</v>
+        <v>1.391</v>
       </c>
       <c r="L72" t="n">
-        <v>8.146000000000001</v>
+        <v>7.665</v>
       </c>
       <c r="M72" t="n">
-        <v>0.1566</v>
+        <v>0.0145</v>
       </c>
       <c r="N72" t="n">
-        <v>0.09177</v>
+        <v>0.1215</v>
       </c>
       <c r="O72" t="n">
-        <v>0.1836</v>
+        <v>0.01931</v>
       </c>
       <c r="P72" t="n">
-        <v>0.1834</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="73">
@@ -3980,47 +3980,47 @@
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-7</t>
+          <t>ADOM-SL7-8-2025</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2.344</v>
       </c>
       <c r="E73" t="n">
-        <v>6.717</v>
+        <v>7.297</v>
       </c>
       <c r="F73" t="n">
-        <v>1.533</v>
+        <v>1.933</v>
       </c>
       <c r="G73" t="n">
-        <v>8.720000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="H73" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I73" t="n">
-        <v>4.22</v>
+        <v>3.882</v>
       </c>
       <c r="J73" t="n">
-        <v>1.022</v>
+        <v>0.8738</v>
       </c>
       <c r="K73" t="n">
-        <v>1.391</v>
+        <v>1.314</v>
       </c>
       <c r="L73" t="n">
-        <v>7.665</v>
+        <v>9.353999999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>0.1848</v>
+        <v>0.01202</v>
       </c>
       <c r="N73" t="n">
-        <v>0.109</v>
+        <v>0.1186</v>
       </c>
       <c r="O73" t="n">
-        <v>0.2206</v>
+        <v>0.01815</v>
       </c>
       <c r="P73" t="n">
-        <v>0.2162</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="74">
@@ -4028,147 +4028,147 @@
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-8</t>
+          <t>ADOM-SL7-9-2025</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.741</v>
+        <v>2.761</v>
       </c>
       <c r="E74" t="n">
-        <v>7.297</v>
+        <v>7.917</v>
       </c>
       <c r="F74" t="n">
-        <v>1.549</v>
+        <v>1.617</v>
       </c>
       <c r="G74" t="n">
-        <v>8.67</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H74" t="n">
         <v>80</v>
       </c>
       <c r="I74" t="n">
-        <v>3.882</v>
+        <v>3.971</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8738</v>
+        <v>0.971</v>
       </c>
       <c r="K74" t="n">
-        <v>1.314</v>
+        <v>1.348</v>
       </c>
       <c r="L74" t="n">
-        <v>9.353999999999999</v>
+        <v>8.121</v>
       </c>
       <c r="M74" t="n">
-        <v>0.1735</v>
+        <v>0.01395</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1125</v>
+        <v>0.1289</v>
       </c>
       <c r="O74" t="n">
-        <v>0.1715</v>
+        <v>0.02044</v>
       </c>
       <c r="P74" t="n">
-        <v>0.2029</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="n"/>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Storage 8</t>
+        </is>
+      </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-9</t>
+          <t>ADOM-SL8-1-2025</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.643</v>
+        <v>1.138</v>
       </c>
       <c r="E75" t="n">
-        <v>7.917</v>
+        <v>2.174</v>
       </c>
       <c r="F75" t="n">
-        <v>1.44</v>
+        <v>1.657</v>
       </c>
       <c r="G75" t="n">
-        <v>8.890000000000001</v>
+        <v>5.46</v>
       </c>
       <c r="H75" t="n">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="I75" t="n">
-        <v>3.971</v>
+        <v>4.892</v>
       </c>
       <c r="J75" t="n">
-        <v>0.971</v>
+        <v>0.7541</v>
       </c>
       <c r="K75" t="n">
-        <v>1.348</v>
+        <v>1.355</v>
       </c>
       <c r="L75" t="n">
-        <v>8.121</v>
+        <v>8.605</v>
       </c>
       <c r="M75" t="n">
-        <v>0.1853</v>
+        <v>0.005713</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1365</v>
+        <v>0.08502999999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>0.2275</v>
+        <v>0.008819</v>
       </c>
       <c r="P75" t="n">
-        <v>0.2229</v>
+        <v>0.06877</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>Storage 8</t>
-        </is>
-      </c>
+      <c r="B76" s="1" t="n"/>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-1</t>
+          <t>ADOM-SL8-10-2025</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.267</v>
+        <v>1.357</v>
       </c>
       <c r="E76" t="n">
-        <v>2.174</v>
+        <v>1.801</v>
       </c>
       <c r="F76" t="n">
-        <v>1.012</v>
+        <v>1.278</v>
       </c>
       <c r="G76" t="n">
-        <v>5.46</v>
+        <v>5.72</v>
       </c>
       <c r="H76" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="I76" t="n">
-        <v>4.892</v>
+        <v>4.824</v>
       </c>
       <c r="J76" t="n">
-        <v>0.7541</v>
+        <v>0.6439</v>
       </c>
       <c r="K76" t="n">
-        <v>1.355</v>
+        <v>1.297</v>
       </c>
       <c r="L76" t="n">
-        <v>8.605</v>
+        <v>11.14</v>
       </c>
       <c r="M76" t="n">
-        <v>0.08862</v>
+        <v>0.006679</v>
       </c>
       <c r="N76" t="n">
-        <v>0.09236999999999999</v>
+        <v>0.1141</v>
       </c>
       <c r="O76" t="n">
-        <v>0.09544</v>
+        <v>0.01039</v>
       </c>
       <c r="P76" t="n">
-        <v>0.1274</v>
+        <v>0.08592</v>
       </c>
     </row>
     <row r="77">
@@ -4176,47 +4176,47 @@
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-10</t>
+          <t>ADOM-SL8-2-2025</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.357</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.801</v>
+        <v>0.8693</v>
       </c>
       <c r="F77" t="n">
-        <v>1.277</v>
+        <v>1.85</v>
       </c>
       <c r="G77" t="n">
-        <v>5.72</v>
+        <v>4.88</v>
       </c>
       <c r="H77" t="n">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="I77" t="n">
-        <v>4.824</v>
+        <v>6.037</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6439</v>
+        <v>1.063</v>
       </c>
       <c r="K77" t="n">
-        <v>1.297</v>
+        <v>1.353</v>
       </c>
       <c r="L77" t="n">
-        <v>11.14</v>
+        <v>2.408</v>
       </c>
       <c r="M77" t="n">
-        <v>0.1184</v>
+        <v>0.003814</v>
       </c>
       <c r="N77" t="n">
-        <v>0.1132</v>
+        <v>0.02562</v>
       </c>
       <c r="O77" t="n">
-        <v>0.09222</v>
+        <v>0.005948</v>
       </c>
       <c r="P77" t="n">
-        <v>0.1645</v>
+        <v>0.03609</v>
       </c>
     </row>
     <row r="78">
@@ -4224,47 +4224,47 @@
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-2</t>
+          <t>ADOM-SL8-3-2025</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0.6163</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8693</v>
+        <v>0.6715</v>
       </c>
       <c r="F78" t="n">
-        <v>1.842</v>
+        <v>1.345</v>
       </c>
       <c r="G78" t="n">
-        <v>4.88</v>
+        <v>5.26</v>
       </c>
       <c r="H78" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I78" t="n">
-        <v>6.037</v>
+        <v>4.797</v>
       </c>
       <c r="J78" t="n">
-        <v>1.063</v>
+        <v>0.9374</v>
       </c>
       <c r="K78" t="n">
-        <v>1.353</v>
+        <v>1.297</v>
       </c>
       <c r="L78" t="n">
-        <v>2.408</v>
+        <v>4.16</v>
       </c>
       <c r="M78" t="n">
-        <v>0.03492</v>
+        <v>0.002023</v>
       </c>
       <c r="N78" t="n">
-        <v>0.04198</v>
+        <v>0.02125</v>
       </c>
       <c r="O78" t="n">
-        <v>0.08487</v>
+        <v>0.005083</v>
       </c>
       <c r="P78" t="n">
-        <v>0.05448</v>
+        <v>0.03163</v>
       </c>
     </row>
     <row r="79">
@@ -4272,47 +4272,47 @@
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-3</t>
+          <t>ADOM-SL8-4-2025</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.6155</v>
+        <v>1.999</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6715</v>
+        <v>0.9102</v>
       </c>
       <c r="F79" t="n">
-        <v>1.341</v>
+        <v>21.32</v>
       </c>
       <c r="G79" t="n">
-        <v>5.26</v>
+        <v>4.64</v>
       </c>
       <c r="H79" t="n">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="I79" t="n">
-        <v>4.797</v>
+        <v>5.602</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9374</v>
+        <v>0.8484</v>
       </c>
       <c r="K79" t="n">
-        <v>1.297</v>
+        <v>1.311</v>
       </c>
       <c r="L79" t="n">
-        <v>4.16</v>
+        <v>4.187</v>
       </c>
       <c r="M79" t="n">
-        <v>0.02688</v>
+        <v>0.002339</v>
       </c>
       <c r="N79" t="n">
-        <v>0.03543</v>
+        <v>0.02625</v>
       </c>
       <c r="O79" t="n">
-        <v>0.05196</v>
+        <v>0.005212</v>
       </c>
       <c r="P79" t="n">
-        <v>0.04416</v>
+        <v>0.03373</v>
       </c>
     </row>
     <row r="80">
@@ -4320,47 +4320,47 @@
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-4</t>
+          <t>ADOM-SL8-6-2025</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.893</v>
+        <v>2.046</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9102</v>
+        <v>6.02</v>
       </c>
       <c r="F80" t="n">
-        <v>16.7</v>
+        <v>1.612</v>
       </c>
       <c r="G80" t="n">
-        <v>4.64</v>
+        <v>6.19</v>
       </c>
       <c r="H80" t="n">
-        <v>246</v>
+        <v>-78</v>
       </c>
       <c r="I80" t="n">
-        <v>5.602</v>
+        <v>4.844</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8484</v>
+        <v>0.9735</v>
       </c>
       <c r="K80" t="n">
-        <v>1.311</v>
+        <v>1.347</v>
       </c>
       <c r="L80" t="n">
-        <v>4.187</v>
+        <v>10.1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.02984</v>
+        <v>0.01396</v>
       </c>
       <c r="N80" t="n">
-        <v>0.03993</v>
+        <v>0.2088</v>
       </c>
       <c r="O80" t="n">
-        <v>0.05594</v>
+        <v>0.02419</v>
       </c>
       <c r="P80" t="n">
-        <v>0.051</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="81">
@@ -4368,47 +4368,47 @@
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-6</t>
+          <t>ADOM-SL8-7-2025</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2.552</v>
+        <v>0.6835</v>
       </c>
       <c r="E81" t="n">
-        <v>6.02</v>
+        <v>0.8862</v>
       </c>
       <c r="F81" t="n">
-        <v>1.379</v>
+        <v>1.932</v>
       </c>
       <c r="G81" t="n">
-        <v>6.19</v>
+        <v>5.17</v>
       </c>
       <c r="H81" t="n">
-        <v>-78</v>
+        <v>174</v>
       </c>
       <c r="I81" t="n">
-        <v>4.844</v>
+        <v>4.667</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9735</v>
+        <v>0.894</v>
       </c>
       <c r="K81" t="n">
-        <v>1.347</v>
+        <v>1.292</v>
       </c>
       <c r="L81" t="n">
-        <v>10.1</v>
+        <v>6.299</v>
       </c>
       <c r="M81" t="n">
-        <v>0.2358</v>
+        <v>0.002951</v>
       </c>
       <c r="N81" t="n">
-        <v>0.2142</v>
+        <v>0.03797</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2438</v>
+        <v>0.00649</v>
       </c>
       <c r="P81" t="n">
-        <v>0.2506</v>
+        <v>0.03998</v>
       </c>
     </row>
     <row r="82">
@@ -4416,47 +4416,47 @@
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-7</t>
+          <t>ADOM-SL8-8-2025</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.9291</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8862</v>
+        <v>1.267</v>
       </c>
       <c r="F82" t="n">
-        <v>1.92</v>
+        <v>1.191</v>
       </c>
       <c r="G82" t="n">
-        <v>5.17</v>
+        <v>8.51</v>
       </c>
       <c r="H82" t="n">
-        <v>174</v>
+        <v>-17</v>
       </c>
       <c r="I82" t="n">
-        <v>4.667</v>
+        <v>4.234</v>
       </c>
       <c r="J82" t="n">
-        <v>0.894</v>
+        <v>0.6378</v>
       </c>
       <c r="K82" t="n">
-        <v>1.292</v>
+        <v>1.316</v>
       </c>
       <c r="L82" t="n">
-        <v>6.299</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>0.04551</v>
+        <v>0.003329</v>
       </c>
       <c r="N82" t="n">
-        <v>0.05003</v>
+        <v>0.06454</v>
       </c>
       <c r="O82" t="n">
-        <v>0.06107</v>
+        <v>0.007661</v>
       </c>
       <c r="P82" t="n">
-        <v>0.06103</v>
+        <v>0.05387</v>
       </c>
     </row>
     <row r="83">
@@ -4464,147 +4464,147 @@
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-8</t>
+          <t>ADOM-SL8-9-2025</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.9286</v>
+        <v>1.182</v>
       </c>
       <c r="E83" t="n">
-        <v>1.267</v>
+        <v>2.747</v>
       </c>
       <c r="F83" t="n">
-        <v>1.185</v>
+        <v>0.583</v>
       </c>
       <c r="G83" t="n">
-        <v>8.51</v>
+        <v>4.79</v>
       </c>
       <c r="H83" t="n">
-        <v>-17</v>
+        <v>189</v>
       </c>
       <c r="I83" t="n">
-        <v>4.234</v>
+        <v>5.901</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6378</v>
+        <v>0.6947</v>
       </c>
       <c r="K83" t="n">
-        <v>1.316</v>
+        <v>1.408</v>
       </c>
       <c r="L83" t="n">
-        <v>9.050000000000001</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="M83" t="n">
-        <v>0.06934</v>
+        <v>0.004853</v>
       </c>
       <c r="N83" t="n">
-        <v>0.07124</v>
+        <v>0.0825</v>
       </c>
       <c r="O83" t="n">
-        <v>0.05398</v>
+        <v>0.007982</v>
       </c>
       <c r="P83" t="n">
-        <v>0.09185</v>
+        <v>0.05669</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="n"/>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>Storage 9</t>
+        </is>
+      </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-9</t>
+          <t>ADOM-SL9-1-2025</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.182</v>
+        <v>1.817</v>
       </c>
       <c r="E84" t="n">
-        <v>2.747</v>
+        <v>5.618</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5825</v>
+        <v>3.455</v>
       </c>
       <c r="G84" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
       <c r="H84" t="n">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I84" t="n">
-        <v>5.901</v>
+        <v>4.796</v>
       </c>
       <c r="J84" t="n">
-        <v>0.6947</v>
+        <v>1.604</v>
       </c>
       <c r="K84" t="n">
-        <v>1.408</v>
+        <v>1.397</v>
       </c>
       <c r="L84" t="n">
-        <v>9.747999999999999</v>
+        <v>6.788</v>
       </c>
       <c r="M84" t="n">
-        <v>0.08236</v>
+        <v>0.02092</v>
       </c>
       <c r="N84" t="n">
-        <v>0.08602</v>
+        <v>0.1221</v>
       </c>
       <c r="O84" t="n">
-        <v>0.07485</v>
+        <v>0.047</v>
       </c>
       <c r="P84" t="n">
-        <v>0.1062</v>
+        <v>0.1436</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>Storage 9</t>
-        </is>
-      </c>
+      <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-1</t>
+          <t>ADOM-SL9-10-2025</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.884</v>
+        <v>1.81</v>
       </c>
       <c r="E85" t="n">
-        <v>5.618</v>
+        <v>5.589</v>
       </c>
       <c r="F85" t="n">
-        <v>2.456</v>
+        <v>3.706</v>
       </c>
       <c r="G85" t="n">
-        <v>5.99</v>
+        <v>6.56</v>
       </c>
       <c r="H85" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I85" t="n">
-        <v>4.796</v>
+        <v>4.577</v>
       </c>
       <c r="J85" t="n">
-        <v>1.604</v>
+        <v>0.7893</v>
       </c>
       <c r="K85" t="n">
-        <v>1.397</v>
+        <v>1.356</v>
       </c>
       <c r="L85" t="n">
-        <v>6.788</v>
+        <v>13.18</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2314</v>
+        <v>0.0154</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1756</v>
+        <v>0.2518</v>
       </c>
       <c r="O85" t="n">
-        <v>0.6224</v>
+        <v>0.02429</v>
       </c>
       <c r="P85" t="n">
-        <v>0.2348</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="86">
@@ -4612,47 +4612,47 @@
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-10</t>
+          <t>ADOM-SL9-11-2025</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.72</v>
+        <v>1.633</v>
       </c>
       <c r="E86" t="n">
-        <v>5.589</v>
+        <v>5.627</v>
       </c>
       <c r="F86" t="n">
-        <v>2.702</v>
+        <v>4.18</v>
       </c>
       <c r="G86" t="n">
-        <v>6.56</v>
+        <v>6.65</v>
       </c>
       <c r="H86" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="I86" t="n">
-        <v>4.577</v>
+        <v>4.516</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7893</v>
+        <v>0.7482</v>
       </c>
       <c r="K86" t="n">
-        <v>1.356</v>
+        <v>1.331</v>
       </c>
       <c r="L86" t="n">
-        <v>13.18</v>
+        <v>15.08</v>
       </c>
       <c r="M86" t="n">
-        <v>0.2864</v>
+        <v>0.01619</v>
       </c>
       <c r="N86" t="n">
-        <v>0.223</v>
+        <v>0.2836</v>
       </c>
       <c r="O86" t="n">
-        <v>0.1894</v>
+        <v>0.02505</v>
       </c>
       <c r="P86" t="n">
-        <v>0.3011</v>
+        <v>0.1678</v>
       </c>
     </row>
     <row r="87">
@@ -4660,47 +4660,47 @@
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-11</t>
+          <t>ADOM-SL9-12-2025</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.7</v>
+        <v>1.479</v>
       </c>
       <c r="E87" t="n">
-        <v>5.627</v>
+        <v>4.749</v>
       </c>
       <c r="F87" t="n">
-        <v>2.684</v>
+        <v>5.649</v>
       </c>
       <c r="G87" t="n">
-        <v>6.65</v>
+        <v>6.79</v>
       </c>
       <c r="H87" t="n">
         <v>69</v>
       </c>
       <c r="I87" t="n">
-        <v>4.516</v>
+        <v>4.708</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7482</v>
+        <v>0.8904</v>
       </c>
       <c r="K87" t="n">
-        <v>1.331</v>
+        <v>1.389</v>
       </c>
       <c r="L87" t="n">
-        <v>15.08</v>
+        <v>11.95</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3131</v>
+        <v>0.01543</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2508</v>
+        <v>0.2227</v>
       </c>
       <c r="O87" t="n">
-        <v>0.1826</v>
+        <v>0.024</v>
       </c>
       <c r="P87" t="n">
-        <v>0.3383</v>
+        <v>0.1317</v>
       </c>
     </row>
     <row r="88">
@@ -4708,47 +4708,47 @@
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-12</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.39</v>
+        <v>1.534</v>
       </c>
       <c r="E88" t="n">
-        <v>4.749</v>
+        <v>5.214</v>
       </c>
       <c r="F88" t="n">
-        <v>3.285</v>
+        <v>6.239</v>
       </c>
       <c r="G88" t="n">
-        <v>6.79</v>
+        <v>6.1</v>
       </c>
       <c r="H88" t="n">
         <v>69</v>
       </c>
       <c r="I88" t="n">
-        <v>4.708</v>
+        <v>5.237</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8904</v>
+        <v>1.018</v>
       </c>
       <c r="K88" t="n">
-        <v>1.389</v>
+        <v>1.44</v>
       </c>
       <c r="L88" t="n">
-        <v>11.95</v>
+        <v>11.23</v>
       </c>
       <c r="M88" t="n">
-        <v>0.2697</v>
+        <v>0.0153</v>
       </c>
       <c r="N88" t="n">
-        <v>0.1904</v>
+        <v>0.1998</v>
       </c>
       <c r="O88" t="n">
-        <v>0.1948</v>
+        <v>0.0244</v>
       </c>
       <c r="P88" t="n">
-        <v>0.2595</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="89">
@@ -4756,17 +4756,17 @@
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.446</v>
+        <v>1.534</v>
       </c>
       <c r="E89" t="n">
         <v>5.214</v>
       </c>
       <c r="F89" t="n">
-        <v>3.817</v>
+        <v>6.239</v>
       </c>
       <c r="G89" t="n">
         <v>6.1</v>
@@ -4787,16 +4787,16 @@
         <v>11.23</v>
       </c>
       <c r="M89" t="n">
-        <v>0.2537</v>
+        <v>0.0153</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1648</v>
+        <v>0.1998</v>
       </c>
       <c r="O89" t="n">
-        <v>0.2165</v>
+        <v>0.0244</v>
       </c>
       <c r="P89" t="n">
-        <v>0.2284</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="90">
@@ -4804,47 +4804,47 @@
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13</t>
+          <t>ADOM-SL9-2-2025</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.446</v>
+        <v>1.942</v>
       </c>
       <c r="E90" t="n">
-        <v>5.214</v>
+        <v>5.405</v>
       </c>
       <c r="F90" t="n">
-        <v>3.817</v>
+        <v>3.425</v>
       </c>
       <c r="G90" t="n">
-        <v>6.1</v>
+        <v>7.23</v>
       </c>
       <c r="H90" t="n">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="I90" t="n">
-        <v>5.237</v>
+        <v>7.363</v>
       </c>
       <c r="J90" t="n">
-        <v>1.018</v>
+        <v>1.082</v>
       </c>
       <c r="K90" t="n">
-        <v>1.44</v>
+        <v>1.689</v>
       </c>
       <c r="L90" t="n">
-        <v>11.23</v>
+        <v>11.72</v>
       </c>
       <c r="M90" t="n">
-        <v>0.2537</v>
+        <v>0.01697</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1648</v>
+        <v>0.3045</v>
       </c>
       <c r="O90" t="n">
-        <v>0.2165</v>
+        <v>0.03229</v>
       </c>
       <c r="P90" t="n">
-        <v>0.2284</v>
+        <v>0.09165</v>
       </c>
     </row>
     <row r="91">
@@ -4852,47 +4852,47 @@
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-2</t>
+          <t>ADOM-SL9-3-2025</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.804</v>
+        <v>2.148</v>
       </c>
       <c r="E91" t="n">
-        <v>5.405</v>
+        <v>5.191</v>
       </c>
       <c r="F91" t="n">
-        <v>2.646</v>
+        <v>3.334</v>
       </c>
       <c r="G91" t="n">
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
       <c r="H91" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="I91" t="n">
-        <v>7.363</v>
+        <v>4.853</v>
       </c>
       <c r="J91" t="n">
-        <v>1.082</v>
+        <v>0.9764</v>
       </c>
       <c r="K91" t="n">
-        <v>1.689</v>
+        <v>1.381</v>
       </c>
       <c r="L91" t="n">
-        <v>11.72</v>
+        <v>11.48</v>
       </c>
       <c r="M91" t="n">
-        <v>0.3505</v>
+        <v>0.01435</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2211</v>
+        <v>0.1855</v>
       </c>
       <c r="O91" t="n">
-        <v>0.2189</v>
+        <v>0.02142</v>
       </c>
       <c r="P91" t="n">
-        <v>0.2036</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="92">
@@ -4900,47 +4900,47 @@
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-3</t>
+          <t>ADOM-SL9-4-2025</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.848</v>
+        <v>1.999</v>
       </c>
       <c r="E92" t="n">
-        <v>5.191</v>
+        <v>4.763</v>
       </c>
       <c r="F92" t="n">
-        <v>2.793</v>
+        <v>4.075</v>
       </c>
       <c r="G92" t="n">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="H92" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I92" t="n">
-        <v>4.853</v>
+        <v>5.237</v>
       </c>
       <c r="J92" t="n">
-        <v>0.9764</v>
+        <v>1.018</v>
       </c>
       <c r="K92" t="n">
-        <v>1.381</v>
+        <v>1.44</v>
       </c>
       <c r="L92" t="n">
-        <v>11.48</v>
+        <v>11.23</v>
       </c>
       <c r="M92" t="n">
-        <v>0.2326</v>
+        <v>0.0153</v>
       </c>
       <c r="N92" t="n">
-        <v>0.153</v>
+        <v>0.1998</v>
       </c>
       <c r="O92" t="n">
-        <v>0.1945</v>
+        <v>0.0244</v>
       </c>
       <c r="P92" t="n">
-        <v>0.2205</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="93">
@@ -4948,47 +4948,47 @@
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-4</t>
+          <t>ADOM-SL9-5-2025</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2.893</v>
+        <v>1.872</v>
       </c>
       <c r="E93" t="n">
-        <v>4.763</v>
+        <v>4.609</v>
       </c>
       <c r="F93" t="n">
-        <v>3.191</v>
+        <v>5.188</v>
       </c>
       <c r="G93" t="n">
-        <v>6.98</v>
+        <v>7.02</v>
       </c>
       <c r="H93" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="I93" t="n">
-        <v>5.237</v>
+        <v>5.117</v>
       </c>
       <c r="J93" t="n">
-        <v>1.018</v>
+        <v>1.06</v>
       </c>
       <c r="K93" t="n">
-        <v>1.44</v>
+        <v>1.442</v>
       </c>
       <c r="L93" t="n">
-        <v>11.23</v>
+        <v>8.09</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2537</v>
+        <v>0.01605</v>
       </c>
       <c r="N93" t="n">
-        <v>0.1648</v>
+        <v>0.2035</v>
       </c>
       <c r="O93" t="n">
-        <v>0.2165</v>
+        <v>0.02525</v>
       </c>
       <c r="P93" t="n">
-        <v>0.2284</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="94">
@@ -4996,47 +4996,47 @@
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-5</t>
+          <t>ADOM-SL9-7-2025</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2.661</v>
+        <v>1.739</v>
       </c>
       <c r="E94" t="n">
-        <v>4.609</v>
+        <v>5.684</v>
       </c>
       <c r="F94" t="n">
-        <v>3.971</v>
+        <v>5.827</v>
       </c>
       <c r="G94" t="n">
-        <v>7.02</v>
+        <v>7.11</v>
       </c>
       <c r="H94" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="I94" t="n">
-        <v>5.117</v>
+        <v>4.533</v>
       </c>
       <c r="J94" t="n">
-        <v>1.06</v>
+        <v>0.8555</v>
       </c>
       <c r="K94" t="n">
-        <v>1.442</v>
+        <v>1.361</v>
       </c>
       <c r="L94" t="n">
-        <v>8.09</v>
+        <v>12.25</v>
       </c>
       <c r="M94" t="n">
-        <v>0.2545</v>
+        <v>0.01737</v>
       </c>
       <c r="N94" t="n">
-        <v>0.1848</v>
+        <v>0.2832</v>
       </c>
       <c r="O94" t="n">
-        <v>0.2475</v>
+        <v>0.02867</v>
       </c>
       <c r="P94" t="n">
-        <v>0.2384</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="95">
@@ -5044,47 +5044,47 @@
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-7</t>
+          <t>ADOM-SL9-8-2025</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2.658</v>
+        <v>1.529</v>
       </c>
       <c r="E95" t="n">
-        <v>5.684</v>
+        <v>6.126</v>
       </c>
       <c r="F95" t="n">
-        <v>4.099</v>
+        <v>5.31</v>
       </c>
       <c r="G95" t="n">
-        <v>7.11</v>
+        <v>5.6</v>
       </c>
       <c r="H95" t="n">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="I95" t="n">
-        <v>4.533</v>
+        <v>4.951</v>
       </c>
       <c r="J95" t="n">
-        <v>0.8555</v>
+        <v>0.8032</v>
       </c>
       <c r="K95" t="n">
-        <v>1.361</v>
+        <v>1.393</v>
       </c>
       <c r="L95" t="n">
-        <v>12.25</v>
+        <v>14.36</v>
       </c>
       <c r="M95" t="n">
-        <v>0.3195</v>
+        <v>0.01786</v>
       </c>
       <c r="N95" t="n">
-        <v>0.2594</v>
+        <v>0.3555</v>
       </c>
       <c r="O95" t="n">
-        <v>0.248</v>
+        <v>0.03093</v>
       </c>
       <c r="P95" t="n">
-        <v>0.3357</v>
+        <v>0.1761</v>
       </c>
     </row>
     <row r="96">
@@ -5092,147 +5092,147 @@
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-8</t>
+          <t>ADOM-SL9-9-2025</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2.432</v>
+        <v>1.697</v>
       </c>
       <c r="E96" t="n">
-        <v>6.126</v>
+        <v>5.754</v>
       </c>
       <c r="F96" t="n">
-        <v>3.249</v>
+        <v>5.339</v>
       </c>
       <c r="G96" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H96" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I96" t="n">
-        <v>4.951</v>
+        <v>4.367</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8032</v>
+        <v>0.7004</v>
       </c>
       <c r="K96" t="n">
-        <v>1.393</v>
+        <v>1.32</v>
       </c>
       <c r="L96" t="n">
-        <v>14.36</v>
+        <v>15.31</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3774</v>
+        <v>0.01673</v>
       </c>
       <c r="N96" t="n">
-        <v>0.3187</v>
+        <v>0.3408</v>
       </c>
       <c r="O96" t="n">
-        <v>0.2176</v>
+        <v>0.02799</v>
       </c>
       <c r="P96" t="n">
-        <v>0.36</v>
+        <v>0.1958</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
-      <c r="B97" s="1" t="n"/>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>Baikal</t>
+        </is>
+      </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-9</t>
+          <t>ADOM-SLB-B1-1-2025</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.662</v>
+        <v>2.178</v>
       </c>
       <c r="E97" t="n">
-        <v>5.754</v>
+        <v>1.255</v>
       </c>
       <c r="F97" t="n">
-        <v>3.632</v>
+        <v>2.075</v>
       </c>
       <c r="G97" t="n">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="I97" t="n">
-        <v>4.367</v>
+        <v>4.83</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7004</v>
+        <v>0.6644</v>
       </c>
       <c r="K97" t="n">
-        <v>1.32</v>
+        <v>1.461</v>
       </c>
       <c r="L97" t="n">
-        <v>15.31</v>
+        <v>14.82</v>
       </c>
       <c r="M97" t="n">
-        <v>0.3562</v>
+        <v>0.003038</v>
       </c>
       <c r="N97" t="n">
-        <v>0.3186</v>
+        <v>0.06713</v>
       </c>
       <c r="O97" t="n">
-        <v>0.1885</v>
+        <v>0.006135</v>
       </c>
       <c r="P97" t="n">
-        <v>0.3918</v>
+        <v>0.05129</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
+      <c r="B98" s="1" t="n"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-1</t>
+          <t>ADOM-SLB-B1-2-2025</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.181</v>
+        <v>1.184</v>
       </c>
       <c r="E98" t="n">
-        <v>1.255</v>
+        <v>0.9669</v>
       </c>
       <c r="F98" t="n">
-        <v>2.072</v>
+        <v>16.57</v>
       </c>
       <c r="G98" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="I98" t="n">
-        <v>4.83</v>
+        <v>4.517</v>
       </c>
       <c r="J98" t="n">
-        <v>0.6644</v>
+        <v>0.584</v>
       </c>
       <c r="K98" t="n">
-        <v>1.461</v>
+        <v>1.329</v>
       </c>
       <c r="L98" t="n">
-        <v>14.82</v>
+        <v>19.6</v>
       </c>
       <c r="M98" t="n">
-        <v>0.06116</v>
+        <v>0.002565</v>
       </c>
       <c r="N98" t="n">
-        <v>0.07804999999999999</v>
+        <v>0.05626</v>
       </c>
       <c r="O98" t="n">
-        <v>0.05188</v>
+        <v>0.005975</v>
       </c>
       <c r="P98" t="n">
-        <v>0.09157999999999999</v>
+        <v>0.04882</v>
       </c>
     </row>
     <row r="99">
@@ -5240,47 +5240,47 @@
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-2</t>
+          <t>ADOM-SLB-B1-3-2025</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.852</v>
+        <v>1.379</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9669</v>
+        <v>1.36</v>
       </c>
       <c r="F99" t="n">
-        <v>6.413</v>
+        <v>3.238</v>
       </c>
       <c r="G99" t="n">
-        <v>9.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="H99" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="I99" t="n">
-        <v>4.517</v>
+        <v>4.169</v>
       </c>
       <c r="J99" t="n">
-        <v>0.584</v>
+        <v>0.755</v>
       </c>
       <c r="K99" t="n">
-        <v>1.329</v>
+        <v>1.382</v>
       </c>
       <c r="L99" t="n">
-        <v>19.6</v>
+        <v>12.41</v>
       </c>
       <c r="M99" t="n">
-        <v>0.05516</v>
+        <v>0.0016</v>
       </c>
       <c r="N99" t="n">
-        <v>0.06553</v>
+        <v>0.01986</v>
       </c>
       <c r="O99" t="n">
-        <v>0.04063</v>
+        <v>0.003855</v>
       </c>
       <c r="P99" t="n">
-        <v>0.08323</v>
+        <v>0.03123</v>
       </c>
     </row>
     <row r="100">
@@ -5288,47 +5288,47 @@
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-3</t>
+          <t>ADOM-SLB-B1-5-2025</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.733</v>
+        <v>0.8895</v>
       </c>
       <c r="E100" t="n">
-        <v>1.36</v>
+        <v>0.948</v>
       </c>
       <c r="F100" t="n">
-        <v>2.206</v>
+        <v>0.849</v>
       </c>
       <c r="G100" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H100" t="n">
         <v>118</v>
       </c>
       <c r="I100" t="n">
-        <v>4.169</v>
+        <v>4.463</v>
       </c>
       <c r="J100" t="n">
-        <v>0.755</v>
+        <v>0.5681</v>
       </c>
       <c r="K100" t="n">
-        <v>1.382</v>
+        <v>1.396</v>
       </c>
       <c r="L100" t="n">
-        <v>12.41</v>
+        <v>18.02</v>
       </c>
       <c r="M100" t="n">
-        <v>0.02187</v>
+        <v>0.002735</v>
       </c>
       <c r="N100" t="n">
-        <v>0.03372</v>
+        <v>0.06064</v>
       </c>
       <c r="O100" t="n">
-        <v>0.03769</v>
+        <v>0.006006</v>
       </c>
       <c r="P100" t="n">
-        <v>0.04434</v>
+        <v>0.05267</v>
       </c>
     </row>
     <row r="101">
@@ -5336,47 +5336,47 @@
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-5</t>
+          <t>ADOM-SLB-B2-1-2025</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.889</v>
+        <v>2.991</v>
       </c>
       <c r="E101" t="n">
-        <v>0.948</v>
+        <v>1.909</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8445</v>
+        <v>1.154</v>
       </c>
       <c r="G101" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="H101" t="n">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I101" t="n">
-        <v>4.463</v>
+        <v>4.992</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5681</v>
+        <v>1.219</v>
       </c>
       <c r="K101" t="n">
-        <v>1.396</v>
+        <v>1.586</v>
       </c>
       <c r="L101" t="n">
-        <v>18.02</v>
+        <v>7.106</v>
       </c>
       <c r="M101" t="n">
-        <v>0.05659</v>
+        <v>0.007555</v>
       </c>
       <c r="N101" t="n">
-        <v>0.07341</v>
+        <v>0.06475</v>
       </c>
       <c r="O101" t="n">
-        <v>0.04571</v>
+        <v>0.0111</v>
       </c>
       <c r="P101" t="n">
-        <v>0.09132999999999999</v>
+        <v>0.06783</v>
       </c>
     </row>
     <row r="102">
@@ -5384,47 +5384,47 @@
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B2-1</t>
+          <t>ADOM-SLB-B2-3-2025</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.999</v>
+        <v>2.886</v>
       </c>
       <c r="E102" t="n">
-        <v>1.909</v>
+        <v>4.241</v>
       </c>
       <c r="F102" t="n">
-        <v>1.153</v>
+        <v>0.6842</v>
       </c>
       <c r="G102" t="n">
-        <v>9.1</v>
+        <v>7.56</v>
       </c>
       <c r="H102" t="n">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="I102" t="n">
-        <v>4.992</v>
+        <v>4.423</v>
       </c>
       <c r="J102" t="n">
-        <v>1.219</v>
+        <v>1.4</v>
       </c>
       <c r="K102" t="n">
-        <v>1.586</v>
+        <v>1.452</v>
       </c>
       <c r="L102" t="n">
-        <v>7.106</v>
+        <v>4.868</v>
       </c>
       <c r="M102" t="n">
-        <v>0.08339000000000001</v>
+        <v>0.008389000000000001</v>
       </c>
       <c r="N102" t="n">
-        <v>0.07854</v>
+        <v>0.03517</v>
       </c>
       <c r="O102" t="n">
-        <v>0.1621</v>
+        <v>0.01446</v>
       </c>
       <c r="P102" t="n">
-        <v>0.12</v>
+        <v>0.06918000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -5432,47 +5432,47 @@
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B2-3</t>
+          <t>ADOM-SLB-B3-1-2025</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.888</v>
+        <v>2.329</v>
       </c>
       <c r="E103" t="n">
-        <v>4.241</v>
+        <v>2.923</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6838</v>
+        <v>0.7537</v>
       </c>
       <c r="G103" t="n">
-        <v>7.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="I103" t="n">
-        <v>4.423</v>
+        <v>4.675</v>
       </c>
       <c r="J103" t="n">
-        <v>1.4</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="K103" t="n">
-        <v>1.452</v>
+        <v>1.45</v>
       </c>
       <c r="L103" t="n">
-        <v>4.868</v>
+        <v>14.43</v>
       </c>
       <c r="M103" t="n">
-        <v>0.07112</v>
+        <v>0.006542</v>
       </c>
       <c r="N103" t="n">
-        <v>0.06152</v>
+        <v>0.1098</v>
       </c>
       <c r="O103" t="n">
-        <v>0.2246</v>
+        <v>0.01137</v>
       </c>
       <c r="P103" t="n">
-        <v>0.1114</v>
+        <v>0.08056000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -5480,47 +5480,47 @@
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-1</t>
+          <t>ADOM-SLB-B3-2-2025</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.333</v>
+        <v>2.764</v>
       </c>
       <c r="E104" t="n">
-        <v>2.923</v>
+        <v>2.336</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7528</v>
+        <v>8.394</v>
       </c>
       <c r="G104" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H104" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="I104" t="n">
-        <v>4.675</v>
+        <v>3.917</v>
       </c>
       <c r="J104" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="K104" t="n">
-        <v>1.45</v>
+        <v>1.285</v>
       </c>
       <c r="L104" t="n">
-        <v>14.43</v>
+        <v>14.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0.119</v>
+        <v>0.03162</v>
       </c>
       <c r="N104" t="n">
-        <v>0.1125</v>
+        <v>0.4224</v>
       </c>
       <c r="O104" t="n">
-        <v>0.09284000000000001</v>
+        <v>0.03417</v>
       </c>
       <c r="P104" t="n">
-        <v>0.1498</v>
+        <v>0.3151</v>
       </c>
     </row>
     <row r="105">
@@ -5528,47 +5528,47 @@
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-2</t>
+          <t>ADOM-SLB-B3-3-2025</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4.139</v>
+        <v>1.818</v>
       </c>
       <c r="E105" t="n">
-        <v>2.336</v>
+        <v>1.969</v>
       </c>
       <c r="F105" t="n">
-        <v>7.192</v>
+        <v>1.169</v>
       </c>
       <c r="G105" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="H105" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="I105" t="n">
-        <v>3.917</v>
+        <v>5.659</v>
       </c>
       <c r="J105" t="n">
-        <v>0.725</v>
+        <v>0.8879</v>
       </c>
       <c r="K105" t="n">
-        <v>1.285</v>
+        <v>1.552</v>
       </c>
       <c r="L105" t="n">
-        <v>14.83</v>
+        <v>11.61</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4916</v>
+        <v>0.006405</v>
       </c>
       <c r="N105" t="n">
-        <v>0.3276</v>
+        <v>0.08916</v>
       </c>
       <c r="O105" t="n">
-        <v>0.3258</v>
+        <v>0.009858</v>
       </c>
       <c r="P105" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.06308999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -5576,47 +5576,47 @@
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-3</t>
+          <t>ADOM-SLB-BO-2-2025</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.818</v>
+        <v>1.816</v>
       </c>
       <c r="E106" t="n">
-        <v>1.969</v>
+        <v>2.27</v>
       </c>
       <c r="F106" t="n">
-        <v>1.168</v>
+        <v>0.9262</v>
       </c>
       <c r="G106" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="H106" t="n">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I106" t="n">
-        <v>5.659</v>
+        <v>5.274</v>
       </c>
       <c r="J106" t="n">
-        <v>0.8879</v>
+        <v>0.7196</v>
       </c>
       <c r="K106" t="n">
-        <v>1.552</v>
+        <v>1.503</v>
       </c>
       <c r="L106" t="n">
-        <v>11.61</v>
+        <v>10.89</v>
       </c>
       <c r="M106" t="n">
-        <v>0.09982000000000001</v>
+        <v>0.00346</v>
       </c>
       <c r="N106" t="n">
-        <v>0.08505</v>
+        <v>0.07242</v>
       </c>
       <c r="O106" t="n">
-        <v>0.1019</v>
+        <v>0.006231</v>
       </c>
       <c r="P106" t="n">
-        <v>0.1199</v>
+        <v>0.05028</v>
       </c>
     </row>
     <row r="107">
@@ -5624,111 +5624,63 @@
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-BO-2</t>
+          <t>ADOM-SLB-BO-3-2025</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1.818</v>
+        <v>1.897</v>
       </c>
       <c r="E107" t="n">
-        <v>2.27</v>
+        <v>1.902</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9252</v>
+        <v>1.106</v>
       </c>
       <c r="G107" t="n">
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="H107" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I107" t="n">
-        <v>5.274</v>
+        <v>4.594</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7196</v>
+        <v>0.7145</v>
       </c>
       <c r="K107" t="n">
-        <v>1.503</v>
+        <v>1.369</v>
       </c>
       <c r="L107" t="n">
-        <v>10.89</v>
+        <v>13.52</v>
       </c>
       <c r="M107" t="n">
-        <v>0.06675</v>
+        <v>0.003427</v>
       </c>
       <c r="N107" t="n">
-        <v>0.07915</v>
+        <v>0.06415</v>
       </c>
       <c r="O107" t="n">
-        <v>0.05468</v>
+        <v>0.006812</v>
       </c>
       <c r="P107" t="n">
-        <v>0.09221</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n"/>
-      <c r="B108" s="1" t="n"/>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-3</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1.902</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="G108" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="H108" t="n">
-        <v>24</v>
-      </c>
-      <c r="I108" t="n">
-        <v>4.594</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0.7145</v>
-      </c>
-      <c r="K108" t="n">
-        <v>1.369</v>
-      </c>
-      <c r="L108" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0.06177</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0.07821</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0.06526999999999999</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0.09508999999999999</v>
+        <v>0.05444</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B67:B75"/>
-    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="B39:B50"/>
+    <mergeCell ref="B66:B74"/>
+    <mergeCell ref="B30:B38"/>
+    <mergeCell ref="B75:B83"/>
+    <mergeCell ref="B97:B107"/>
     <mergeCell ref="B20:B27"/>
-    <mergeCell ref="A2:A108"/>
-    <mergeCell ref="B52:B66"/>
-    <mergeCell ref="B85:B97"/>
-    <mergeCell ref="B76:B84"/>
-    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="B51:B65"/>
+    <mergeCell ref="A2:A107"/>
     <mergeCell ref="B11:B19"/>
-    <mergeCell ref="B98:B108"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B84:B96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Server/Received_data/Statistics/2025/Documents/Исходные данные за 2025 год.xlsx
+++ b/Server/Received_data/Statistics/2025/Documents/Исходные данные за 2025 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,22 +472,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>epsilon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>C_org</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Suva</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>eH</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6933</v>
+        <v>6.724</v>
       </c>
       <c r="E2" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02422</v>
+      </c>
+      <c r="G2" t="n">
         <v>69.16</v>
       </c>
-      <c r="F2" t="n">
-        <v>2059</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.99</v>
-      </c>
       <c r="H2" t="n">
-        <v>-110</v>
+        <v>2.023</v>
       </c>
       <c r="I2" t="n">
         <v>4.881</v>
@@ -596,19 +596,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.352</v>
+        <v>8.118</v>
       </c>
       <c r="E3" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="G3" t="n">
         <v>43</v>
       </c>
-      <c r="F3" t="n">
-        <v>2.128</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.23</v>
-      </c>
       <c r="H3" t="n">
-        <v>-112</v>
+        <v>1.988</v>
       </c>
       <c r="I3" t="n">
         <v>4.963</v>
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2960</v>
+        <v>3.962</v>
       </c>
       <c r="E4" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04445</v>
+      </c>
+      <c r="G4" t="n">
         <v>33.8</v>
       </c>
-      <c r="F4" t="n">
-        <v>3290</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.98</v>
-      </c>
       <c r="H4" t="n">
-        <v>-104</v>
+        <v>3.03</v>
       </c>
       <c r="I4" t="n">
         <v>4.1</v>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.164</v>
+        <v>5.353</v>
       </c>
       <c r="E5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01314</v>
+      </c>
+      <c r="G5" t="n">
         <v>30.27</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.92</v>
-      </c>
       <c r="H5" t="n">
-        <v>-124</v>
+        <v>1.335</v>
       </c>
       <c r="I5" t="n">
         <v>4.273</v>
@@ -740,19 +740,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.499</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
         <v>16</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.1002</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.43</v>
-      </c>
       <c r="H6" t="n">
-        <v>-170</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
         <v>4.174</v>
@@ -788,19 +786,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.053</v>
+        <v>5.667</v>
       </c>
       <c r="E7" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01043</v>
+      </c>
+      <c r="G7" t="n">
         <v>15.63</v>
       </c>
-      <c r="F7" t="n">
-        <v>2.585</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="H7" t="n">
-        <v>-94</v>
+        <v>2.297</v>
       </c>
       <c r="I7" t="n">
         <v>4.257</v>
@@ -836,19 +834,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.355</v>
+        <v>5.356</v>
       </c>
       <c r="E8" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.009788</v>
+      </c>
+      <c r="G8" t="n">
         <v>16.12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>2.19</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-10</v>
       </c>
       <c r="I8" t="n">
         <v>4.247</v>
@@ -887,16 +885,16 @@
         <v>4.775</v>
       </c>
       <c r="E9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="G9" t="n">
         <v>18.97</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>2.483</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>3.985</v>
@@ -932,19 +930,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.443</v>
+        <v>5.444</v>
       </c>
       <c r="E10" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="G10" t="n">
         <v>8.755000000000001</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>4.386</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="H10" t="n">
-        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>4.27</v>
@@ -984,19 +982,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.268</v>
+        <v>2.595</v>
       </c>
       <c r="E11" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="G11" t="n">
         <v>7.019</v>
       </c>
-      <c r="F11" t="n">
-        <v>4.665</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.19</v>
-      </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>1.695</v>
       </c>
       <c r="I11" t="n">
         <v>3.944</v>
@@ -1032,19 +1030,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.124</v>
+        <v>3.25</v>
       </c>
       <c r="E12" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.008009</v>
+      </c>
+      <c r="G12" t="n">
         <v>12.26</v>
       </c>
-      <c r="F12" t="n">
-        <v>1.191</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.59</v>
-      </c>
       <c r="H12" t="n">
-        <v>-107</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>6.295</v>
@@ -1083,16 +1081,16 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005933</v>
+      </c>
+      <c r="G13" t="n">
         <v>4.67</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>2.484</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="H13" t="n">
-        <v>115</v>
       </c>
       <c r="I13" t="n">
         <v>4.992</v>
@@ -1128,19 +1126,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.168</v>
+        <v>3.729</v>
       </c>
       <c r="E14" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="G14" t="n">
         <v>10.54</v>
       </c>
-      <c r="F14" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.01</v>
-      </c>
       <c r="H14" t="n">
-        <v>113</v>
+        <v>1.841</v>
       </c>
       <c r="I14" t="n">
         <v>4.443</v>
@@ -1176,19 +1174,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.303</v>
+        <v>4.304</v>
       </c>
       <c r="E15" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.005665</v>
+      </c>
+      <c r="G15" t="n">
         <v>4.835</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>2.296</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-83</v>
       </c>
       <c r="I15" t="n">
         <v>3.613</v>
@@ -1224,19 +1222,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.195</v>
+        <v>4.211</v>
       </c>
       <c r="E16" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.004856</v>
+      </c>
+      <c r="G16" t="n">
         <v>13.22</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.9082</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.49</v>
-      </c>
       <c r="H16" t="n">
-        <v>-110</v>
+        <v>0.6657</v>
       </c>
       <c r="I16" t="n">
         <v>4.552</v>
@@ -1272,19 +1270,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.656</v>
+        <v>2.963</v>
       </c>
       <c r="E17" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="G17" t="n">
         <v>4.182</v>
       </c>
-      <c r="F17" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.87</v>
-      </c>
       <c r="H17" t="n">
-        <v>-110</v>
+        <v>12.32</v>
       </c>
       <c r="I17" t="n">
         <v>4.119</v>
@@ -1320,19 +1318,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.779</v>
+        <v>2.651</v>
       </c>
       <c r="E18" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="G18" t="n">
         <v>24.07</v>
       </c>
-      <c r="F18" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.47</v>
-      </c>
       <c r="H18" t="n">
-        <v>-105</v>
+        <v>1.018</v>
       </c>
       <c r="I18" t="n">
         <v>4.78</v>
@@ -1368,19 +1366,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.762</v>
+        <v>3.631</v>
       </c>
       <c r="E19" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="G19" t="n">
         <v>9.007999999999999</v>
       </c>
-      <c r="F19" t="n">
-        <v>3.298</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.09</v>
-      </c>
       <c r="H19" t="n">
-        <v>-30</v>
+        <v>2.942</v>
       </c>
       <c r="I19" t="n">
         <v>4.743</v>
@@ -1420,19 +1418,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.945</v>
+        <v>3.136</v>
       </c>
       <c r="E20" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="G20" t="n">
         <v>11.45</v>
       </c>
-      <c r="F20" t="n">
-        <v>5.715</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H20" t="n">
-        <v>-5</v>
+        <v>4.175</v>
       </c>
       <c r="I20" t="n">
         <v>4.658</v>
@@ -1468,19 +1466,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.372</v>
+        <v>3.611</v>
       </c>
       <c r="E21" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.04311</v>
+      </c>
+      <c r="G21" t="n">
         <v>24.62</v>
       </c>
-      <c r="F21" t="n">
-        <v>4.762</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="H21" t="n">
-        <v>-90</v>
+        <v>3.335</v>
       </c>
       <c r="I21" t="n">
         <v>4.05</v>
@@ -1516,19 +1514,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.785</v>
+        <v>3.574</v>
       </c>
       <c r="E22" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.02716</v>
+      </c>
+      <c r="G22" t="n">
         <v>24.03</v>
       </c>
-      <c r="F22" t="n">
-        <v>3.923</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.94</v>
-      </c>
       <c r="H22" t="n">
-        <v>-99</v>
+        <v>1.989</v>
       </c>
       <c r="I22" t="n">
         <v>4.525</v>
@@ -1564,19 +1562,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.295</v>
+        <v>3.359</v>
       </c>
       <c r="E23" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.009927</v>
+      </c>
+      <c r="G23" t="n">
         <v>6.966</v>
       </c>
-      <c r="F23" t="n">
-        <v>2.542</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6</v>
-      </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>2.082</v>
       </c>
       <c r="I23" t="n">
         <v>4.884</v>
@@ -1612,19 +1610,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.999</v>
+        <v>3.5</v>
       </c>
       <c r="E24" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.008453</v>
+      </c>
+      <c r="G24" t="n">
         <v>2.448</v>
       </c>
-      <c r="F24" t="n">
-        <v>7.029</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.07</v>
-      </c>
       <c r="H24" t="n">
-        <v>64</v>
+        <v>5.065</v>
       </c>
       <c r="I24" t="n">
         <v>4.84</v>
@@ -1660,19 +1658,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.92</v>
+        <v>3.514</v>
       </c>
       <c r="E25" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.007009</v>
+      </c>
+      <c r="G25" t="n">
         <v>5.335</v>
       </c>
-      <c r="F25" t="n">
-        <v>3.901</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.6</v>
-      </c>
       <c r="H25" t="n">
-        <v>107</v>
+        <v>2.699</v>
       </c>
       <c r="I25" t="n">
         <v>4.326</v>
@@ -1708,19 +1706,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.689</v>
+        <v>3.36</v>
       </c>
       <c r="E26" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="G26" t="n">
         <v>9.819000000000001</v>
       </c>
-      <c r="F26" t="n">
-        <v>5.392</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H26" t="n">
-        <v>116</v>
+        <v>3.269</v>
       </c>
       <c r="I26" t="n">
         <v>4.36</v>
@@ -1756,19 +1754,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.616</v>
+        <v>3.458</v>
       </c>
       <c r="E27" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.01363</v>
+      </c>
+      <c r="G27" t="n">
         <v>7.737</v>
       </c>
-      <c r="F27" t="n">
-        <v>5.213</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3.72</v>
-      </c>
       <c r="H27" t="n">
-        <v>68</v>
+        <v>2.934</v>
       </c>
       <c r="I27" t="n">
         <v>4.819</v>
@@ -1804,47 +1802,47 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-5-2025</t>
+          <t>ADOM-SL3-2-2025</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.548</v>
+        <v>1.873</v>
       </c>
       <c r="E28" t="n">
-        <v>6.378</v>
+        <v>0.335</v>
       </c>
       <c r="F28" t="n">
-        <v>4.693</v>
+        <v>0.1106</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>14.55</v>
       </c>
       <c r="H28" t="n">
-        <v>-59</v>
+        <v>2.302</v>
       </c>
       <c r="I28" t="n">
-        <v>4.527</v>
+        <v>4.509</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7696</v>
+        <v>0.8922</v>
       </c>
       <c r="K28" t="n">
-        <v>1.396</v>
+        <v>1.353</v>
       </c>
       <c r="L28" t="n">
-        <v>14.37</v>
+        <v>12.61</v>
       </c>
       <c r="M28" t="n">
-        <v>0.01512</v>
+        <v>0.01529</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3248</v>
+        <v>0.291</v>
       </c>
       <c r="O28" t="n">
-        <v>0.02716</v>
+        <v>0.03684</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1766</v>
+        <v>0.1882</v>
       </c>
     </row>
     <row r="29">
@@ -1852,147 +1850,147 @@
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-6-2025</t>
+          <t>ADOM-SL3-5-2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.174</v>
+        <v>3.525</v>
       </c>
       <c r="E29" t="n">
-        <v>5.197</v>
+        <v>0.155</v>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>0.0109</v>
       </c>
       <c r="G29" t="n">
-        <v>7.15</v>
+        <v>6.378</v>
       </c>
       <c r="H29" t="n">
-        <v>-35</v>
+        <v>2.43</v>
       </c>
       <c r="I29" t="n">
-        <v>4.78</v>
+        <v>4.527</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8157</v>
+        <v>0.7696</v>
       </c>
       <c r="K29" t="n">
-        <v>1.368</v>
+        <v>1.396</v>
       </c>
       <c r="L29" t="n">
-        <v>14.38</v>
+        <v>14.37</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01422</v>
+        <v>0.01512</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2361</v>
+        <v>0.3248</v>
       </c>
       <c r="O29" t="n">
-        <v>0.02211</v>
+        <v>0.02716</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1355</v>
+        <v>0.1766</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Storage 4</t>
-        </is>
-      </c>
+      <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-1-2025</t>
+          <t>ADOM-SL3-6-2025</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.654</v>
+        <v>3.68</v>
       </c>
       <c r="E30" t="n">
-        <v>30.24</v>
+        <v>0.102</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5457</v>
+        <v>0.006235</v>
       </c>
       <c r="G30" t="n">
-        <v>9.18</v>
+        <v>5.197</v>
       </c>
       <c r="H30" t="n">
-        <v>105</v>
+        <v>1.963</v>
       </c>
       <c r="I30" t="n">
-        <v>5.162</v>
+        <v>4.78</v>
       </c>
       <c r="J30" t="n">
-        <v>1.217</v>
+        <v>0.8157</v>
       </c>
       <c r="K30" t="n">
-        <v>1.495</v>
+        <v>1.368</v>
       </c>
       <c r="L30" t="n">
-        <v>6.572</v>
+        <v>14.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0.01007</v>
+        <v>0.01422</v>
       </c>
       <c r="N30" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.2361</v>
       </c>
       <c r="O30" t="n">
-        <v>0.01357</v>
+        <v>0.02211</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0678</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Storage 4</t>
+        </is>
+      </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-2-2025</t>
+          <t>ADOM-SL4-1-2025</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.082</v>
+        <v>4.656</v>
       </c>
       <c r="E31" t="n">
-        <v>22.83</v>
+        <v>0.165</v>
       </c>
       <c r="F31" t="n">
-        <v>2.468</v>
+        <v>0.01233</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78</v>
+        <v>30.24</v>
       </c>
       <c r="H31" t="n">
-        <v>107</v>
+        <v>0.5456</v>
       </c>
       <c r="I31" t="n">
-        <v>5.028</v>
+        <v>5.162</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6597</v>
+        <v>1.217</v>
       </c>
       <c r="K31" t="n">
-        <v>1.435</v>
+        <v>1.495</v>
       </c>
       <c r="L31" t="n">
-        <v>21.35</v>
+        <v>6.572</v>
       </c>
       <c r="M31" t="n">
-        <v>0.01738</v>
+        <v>0.01007</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3456</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.02753</v>
+        <v>0.01357</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1791</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="32">
@@ -2000,47 +1998,47 @@
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-3-2025</t>
+          <t>ADOM-SL4-10-2025</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.412</v>
+        <v>4.417</v>
       </c>
       <c r="E32" t="n">
-        <v>10.18</v>
+        <v>0.118</v>
       </c>
       <c r="F32" t="n">
-        <v>1.395</v>
+        <v>0.00831</v>
       </c>
       <c r="G32" t="n">
-        <v>7.56</v>
+        <v>6.712</v>
       </c>
       <c r="H32" t="n">
-        <v>127</v>
+        <v>1.758</v>
       </c>
       <c r="I32" t="n">
-        <v>4.893</v>
+        <v>4.829</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7004</v>
+        <v>0.8122</v>
       </c>
       <c r="K32" t="n">
-        <v>1.382</v>
+        <v>1.418</v>
       </c>
       <c r="L32" t="n">
-        <v>20.06</v>
+        <v>12.89</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01859</v>
+        <v>0.02142</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3305</v>
+        <v>0.2707</v>
       </c>
       <c r="O32" t="n">
-        <v>0.028</v>
+        <v>0.02597</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1791</v>
+        <v>0.1796</v>
       </c>
     </row>
     <row r="33">
@@ -2048,47 +2046,47 @@
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-4-2025</t>
+          <t>ADOM-SL4-2-2025</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3.548</v>
+        <v>4.627</v>
       </c>
       <c r="E33" t="n">
-        <v>8.74</v>
+        <v>0.387</v>
       </c>
       <c r="F33" t="n">
-        <v>1.396</v>
+        <v>0.0197</v>
       </c>
       <c r="G33" t="n">
-        <v>6.95</v>
+        <v>22.83</v>
       </c>
       <c r="H33" t="n">
-        <v>43</v>
+        <v>1.695</v>
       </c>
       <c r="I33" t="n">
-        <v>4.648</v>
+        <v>5.028</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8043</v>
+        <v>0.6597</v>
       </c>
       <c r="K33" t="n">
-        <v>1.366</v>
+        <v>1.435</v>
       </c>
       <c r="L33" t="n">
-        <v>13.7</v>
+        <v>21.35</v>
       </c>
       <c r="M33" t="n">
-        <v>0.01318</v>
+        <v>0.01738</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1817</v>
+        <v>0.3456</v>
       </c>
       <c r="O33" t="n">
-        <v>0.01974</v>
+        <v>0.02753</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1166</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="34">
@@ -2096,47 +2094,47 @@
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-5-2025</t>
+          <t>ADOM-SL4-3-2025</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.498</v>
+        <v>4.414</v>
       </c>
       <c r="E34" t="n">
-        <v>6.687</v>
+        <v>0.142</v>
       </c>
       <c r="F34" t="n">
-        <v>1.511</v>
+        <v>0.01045</v>
       </c>
       <c r="G34" t="n">
-        <v>7.9</v>
+        <v>10.18</v>
       </c>
       <c r="H34" t="n">
-        <v>60</v>
+        <v>1.395</v>
       </c>
       <c r="I34" t="n">
-        <v>5.084</v>
+        <v>4.893</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9669</v>
+        <v>0.7004</v>
       </c>
       <c r="K34" t="n">
-        <v>1.481</v>
+        <v>1.382</v>
       </c>
       <c r="L34" t="n">
-        <v>10.87</v>
+        <v>20.06</v>
       </c>
       <c r="M34" t="n">
-        <v>0.02028</v>
+        <v>0.01859</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2602</v>
+        <v>0.3305</v>
       </c>
       <c r="O34" t="n">
-        <v>0.03134</v>
+        <v>0.028</v>
       </c>
       <c r="P34" t="n">
-        <v>0.155</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="35">
@@ -2144,47 +2142,47 @@
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-6-2025</t>
+          <t>ADOM-SL4-4-2025</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.112</v>
+        <v>3.548</v>
       </c>
       <c r="E35" t="n">
-        <v>6.655</v>
+        <v>0.122</v>
       </c>
       <c r="F35" t="n">
-        <v>2.12</v>
+        <v>0.009035</v>
       </c>
       <c r="G35" t="n">
-        <v>7.62</v>
+        <v>8.74</v>
       </c>
       <c r="H35" t="n">
-        <v>95</v>
+        <v>1.396</v>
       </c>
       <c r="I35" t="n">
-        <v>5.286</v>
+        <v>4.648</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8024</v>
+        <v>0.8043</v>
       </c>
       <c r="K35" t="n">
-        <v>1.443</v>
+        <v>1.366</v>
       </c>
       <c r="L35" t="n">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01533</v>
+        <v>0.01318</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2425</v>
+        <v>0.1817</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0237</v>
+        <v>0.01974</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1297</v>
+        <v>0.1166</v>
       </c>
     </row>
     <row r="36">
@@ -2192,47 +2190,45 @@
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-7-2025</t>
+          <t>ADOM-SL4-5-2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.823</v>
+        <v>3.5</v>
       </c>
       <c r="E36" t="n">
-        <v>8.260999999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.187</v>
-      </c>
+        <v>0.101</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>8.16</v>
+        <v>6.687</v>
       </c>
       <c r="H36" t="n">
-        <v>121</v>
+        <v>1.51</v>
       </c>
       <c r="I36" t="n">
-        <v>5.202</v>
+        <v>5.084</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9537</v>
+        <v>0.9669</v>
       </c>
       <c r="K36" t="n">
-        <v>1.407</v>
+        <v>1.481</v>
       </c>
       <c r="L36" t="n">
-        <v>9.884</v>
+        <v>10.87</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01314</v>
+        <v>0.02028</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1479</v>
+        <v>0.2602</v>
       </c>
       <c r="O36" t="n">
-        <v>0.019</v>
+        <v>0.03134</v>
       </c>
       <c r="P36" t="n">
-        <v>0.09665</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="37">
@@ -2240,47 +2236,47 @@
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-8-2025</t>
+          <t>ADOM-SL4-6-2025</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.086</v>
+        <v>3.3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.989</v>
+        <v>0.109</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>0.009639</v>
       </c>
       <c r="G37" t="n">
-        <v>7.66</v>
+        <v>6.655</v>
       </c>
       <c r="H37" t="n">
-        <v>139</v>
+        <v>1.638</v>
       </c>
       <c r="I37" t="n">
-        <v>4.898</v>
+        <v>5.286</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8845</v>
+        <v>0.8024</v>
       </c>
       <c r="K37" t="n">
-        <v>1.371</v>
+        <v>1.443</v>
       </c>
       <c r="L37" t="n">
-        <v>12.27</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01798</v>
+        <v>0.01533</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2375</v>
+        <v>0.2425</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02637</v>
+        <v>0.0237</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1426</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="38">
@@ -2288,99 +2284,93 @@
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-9-2025</t>
+          <t>ADOM-SL4-7-2025</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.803</v>
+        <v>3.826</v>
       </c>
       <c r="E38" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4.821</v>
-      </c>
+        <v>0.098</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>8.289999999999999</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>63</v>
+        <v>1.186</v>
       </c>
       <c r="I38" t="n">
-        <v>4.567</v>
+        <v>5.202</v>
       </c>
       <c r="J38" t="n">
-        <v>0.577</v>
+        <v>0.9537</v>
       </c>
       <c r="K38" t="n">
-        <v>1.373</v>
+        <v>1.407</v>
       </c>
       <c r="L38" t="n">
-        <v>28.37</v>
+        <v>9.884</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02514</v>
+        <v>0.01314</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6325</v>
+        <v>0.1479</v>
       </c>
       <c r="O38" t="n">
-        <v>0.04413</v>
+        <v>0.019</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3088</v>
+        <v>0.09665</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>Storage 5</t>
-        </is>
-      </c>
+      <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-10-2025</t>
+          <t>ADOM-SL4-8-2025</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.12</v>
+        <v>2.647</v>
       </c>
       <c r="E39" t="n">
-        <v>8.589</v>
+        <v>0.148</v>
       </c>
       <c r="F39" t="n">
-        <v>2.958</v>
+        <v>0.02242</v>
       </c>
       <c r="G39" t="n">
-        <v>7.58</v>
+        <v>5.989</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="I39" t="n">
-        <v>4.937</v>
+        <v>4.898</v>
       </c>
       <c r="J39" t="n">
-        <v>0.786</v>
+        <v>0.8845</v>
       </c>
       <c r="K39" t="n">
-        <v>1.441</v>
+        <v>1.371</v>
       </c>
       <c r="L39" t="n">
-        <v>16.35</v>
+        <v>12.27</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03037</v>
+        <v>0.01798</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5641</v>
+        <v>0.2375</v>
       </c>
       <c r="O39" t="n">
-        <v>0.05713</v>
+        <v>0.02637</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2696</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="40">
@@ -2388,95 +2378,99 @@
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-5-2025</t>
+          <t>ADOM-SL4-9-2025</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.985</v>
+        <v>5.362</v>
       </c>
       <c r="E40" t="n">
-        <v>5.377</v>
+        <v>0.279</v>
       </c>
       <c r="F40" t="n">
-        <v>2.829</v>
+        <v>0.01078</v>
       </c>
       <c r="G40" t="n">
-        <v>8.199999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="H40" t="n">
-        <v>80</v>
+        <v>2.76</v>
       </c>
       <c r="I40" t="n">
-        <v>5.189</v>
+        <v>4.567</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9896</v>
+        <v>0.577</v>
       </c>
       <c r="K40" t="n">
-        <v>1.471</v>
+        <v>1.373</v>
       </c>
       <c r="L40" t="n">
-        <v>11.54</v>
+        <v>28.37</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02226</v>
+        <v>0.02514</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2991</v>
+        <v>0.6325</v>
       </c>
       <c r="O40" t="n">
-        <v>0.03865</v>
+        <v>0.04413</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1485</v>
+        <v>0.3088</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Storage 5</t>
+        </is>
+      </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6-2025</t>
+          <t>ADOM-SL5-10-2025</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.332</v>
+        <v>4.738</v>
       </c>
       <c r="E41" t="n">
-        <v>2.09</v>
+        <v>0.222</v>
       </c>
       <c r="F41" t="n">
-        <v>6.177</v>
+        <v>0.009342</v>
       </c>
       <c r="G41" t="n">
-        <v>7.9</v>
+        <v>8.589</v>
       </c>
       <c r="H41" t="n">
-        <v>126</v>
+        <v>2.585</v>
       </c>
       <c r="I41" t="n">
-        <v>5.135</v>
+        <v>4.937</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7693</v>
+        <v>0.786</v>
       </c>
       <c r="K41" t="n">
-        <v>1.426</v>
+        <v>1.441</v>
       </c>
       <c r="L41" t="n">
-        <v>16.24</v>
+        <v>16.35</v>
       </c>
       <c r="M41" t="n">
-        <v>0.02916</v>
+        <v>0.03037</v>
       </c>
       <c r="N41" t="n">
-        <v>0.5155</v>
+        <v>0.5641</v>
       </c>
       <c r="O41" t="n">
-        <v>0.04511</v>
+        <v>0.05713</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2481</v>
+        <v>0.2696</v>
       </c>
     </row>
     <row r="42">
@@ -2484,47 +2478,45 @@
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6-2025</t>
+          <t>ADOM-SL5-2-2025</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.332</v>
+        <v>5.643</v>
       </c>
       <c r="E42" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="F42" t="n">
-        <v>6.177</v>
-      </c>
+        <v>0.267</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>7.9</v>
+        <v>11.87</v>
       </c>
       <c r="H42" t="n">
-        <v>126</v>
+        <v>2.249</v>
       </c>
       <c r="I42" t="n">
-        <v>5.135</v>
+        <v>4.644</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7693</v>
+        <v>0.827</v>
       </c>
       <c r="K42" t="n">
-        <v>1.426</v>
+        <v>1.356</v>
       </c>
       <c r="L42" t="n">
-        <v>16.24</v>
+        <v>14.07</v>
       </c>
       <c r="M42" t="n">
-        <v>0.02916</v>
+        <v>0.02523</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5155</v>
+        <v>0.4844</v>
       </c>
       <c r="O42" t="n">
-        <v>0.04511</v>
+        <v>0.05134</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2481</v>
+        <v>0.2381</v>
       </c>
     </row>
     <row r="43">
@@ -2532,47 +2524,47 @@
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6-2025</t>
+          <t>ADOM-SL5-4-2025</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.332</v>
+        <v>5.511</v>
       </c>
       <c r="E43" t="n">
-        <v>2.09</v>
+        <v>0.29</v>
       </c>
       <c r="F43" t="n">
-        <v>6.177</v>
+        <v>0.007262</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9</v>
+        <v>12.39</v>
       </c>
       <c r="H43" t="n">
-        <v>126</v>
+        <v>2.341</v>
       </c>
       <c r="I43" t="n">
-        <v>5.135</v>
+        <v>4.676</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7693</v>
+        <v>0.7368</v>
       </c>
       <c r="K43" t="n">
-        <v>1.426</v>
+        <v>1.372</v>
       </c>
       <c r="L43" t="n">
-        <v>16.24</v>
+        <v>15.97</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02916</v>
+        <v>0.02481</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5155</v>
+        <v>0.525</v>
       </c>
       <c r="O43" t="n">
-        <v>0.04511</v>
+        <v>0.0507</v>
       </c>
       <c r="P43" t="n">
-        <v>0.2481</v>
+        <v>0.2515</v>
       </c>
     </row>
     <row r="44">
@@ -2580,47 +2572,47 @@
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7-2025</t>
+          <t>ADOM-SL5-5-2025</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.7</v>
+        <v>4.043</v>
       </c>
       <c r="E44" t="n">
-        <v>4.861</v>
+        <v>0.104</v>
       </c>
       <c r="F44" t="n">
-        <v>2.139</v>
+        <v>0.005198</v>
       </c>
       <c r="G44" t="n">
-        <v>7.8</v>
+        <v>5.377</v>
       </c>
       <c r="H44" t="n">
-        <v>118</v>
+        <v>1.934</v>
       </c>
       <c r="I44" t="n">
-        <v>4.883</v>
+        <v>5.189</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9748</v>
+        <v>0.9896</v>
       </c>
       <c r="K44" t="n">
-        <v>1.448</v>
+        <v>1.471</v>
       </c>
       <c r="L44" t="n">
-        <v>11.25</v>
+        <v>11.54</v>
       </c>
       <c r="M44" t="n">
-        <v>0.02195</v>
+        <v>0.02226</v>
       </c>
       <c r="N44" t="n">
-        <v>0.2926</v>
+        <v>0.2991</v>
       </c>
       <c r="O44" t="n">
-        <v>0.03929</v>
+        <v>0.03865</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1596</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="45">
@@ -2628,47 +2620,47 @@
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7-2025</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.7</v>
+        <v>4.579</v>
       </c>
       <c r="E45" t="n">
-        <v>4.861</v>
+        <v>0.097</v>
       </c>
       <c r="F45" t="n">
-        <v>2.139</v>
+        <v>0.006097</v>
       </c>
       <c r="G45" t="n">
-        <v>7.8</v>
+        <v>2.09</v>
       </c>
       <c r="H45" t="n">
-        <v>118</v>
+        <v>4.642</v>
       </c>
       <c r="I45" t="n">
-        <v>4.883</v>
+        <v>5.135</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9748</v>
+        <v>0.7693</v>
       </c>
       <c r="K45" t="n">
-        <v>1.448</v>
+        <v>1.426</v>
       </c>
       <c r="L45" t="n">
-        <v>11.25</v>
+        <v>16.24</v>
       </c>
       <c r="M45" t="n">
-        <v>0.02195</v>
+        <v>0.02916</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2926</v>
+        <v>0.5155</v>
       </c>
       <c r="O45" t="n">
-        <v>0.03929</v>
+        <v>0.04511</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1596</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="46">
@@ -2676,47 +2668,47 @@
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8-2025</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.237</v>
+        <v>4.579</v>
       </c>
       <c r="E46" t="n">
-        <v>5.999</v>
+        <v>0.097</v>
       </c>
       <c r="F46" t="n">
-        <v>2.967</v>
+        <v>0.006097</v>
       </c>
       <c r="G46" t="n">
-        <v>8.15</v>
+        <v>2.09</v>
       </c>
       <c r="H46" t="n">
-        <v>108</v>
+        <v>4.642</v>
       </c>
       <c r="I46" t="n">
-        <v>4.427</v>
+        <v>5.135</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7196</v>
+        <v>0.7693</v>
       </c>
       <c r="K46" t="n">
-        <v>1.362</v>
+        <v>1.426</v>
       </c>
       <c r="L46" t="n">
-        <v>15.77</v>
+        <v>16.24</v>
       </c>
       <c r="M46" t="n">
-        <v>0.02534</v>
+        <v>0.02916</v>
       </c>
       <c r="N46" t="n">
-        <v>0.4913</v>
+        <v>0.5155</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0466</v>
+        <v>0.04511</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2661</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="47">
@@ -2724,47 +2716,47 @@
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8-2025</t>
+          <t>ADOM-SL5-6-2025</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.237</v>
+        <v>4.579</v>
       </c>
       <c r="E47" t="n">
-        <v>5.999</v>
+        <v>0.097</v>
       </c>
       <c r="F47" t="n">
-        <v>2.967</v>
+        <v>0.006097</v>
       </c>
       <c r="G47" t="n">
-        <v>8.15</v>
+        <v>2.09</v>
       </c>
       <c r="H47" t="n">
-        <v>108</v>
+        <v>4.642</v>
       </c>
       <c r="I47" t="n">
-        <v>4.427</v>
+        <v>5.135</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7196</v>
+        <v>0.7693</v>
       </c>
       <c r="K47" t="n">
-        <v>1.362</v>
+        <v>1.426</v>
       </c>
       <c r="L47" t="n">
-        <v>15.77</v>
+        <v>16.24</v>
       </c>
       <c r="M47" t="n">
-        <v>0.02534</v>
+        <v>0.02916</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4913</v>
+        <v>0.5155</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0466</v>
+        <v>0.04511</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2661</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="48">
@@ -2772,47 +2764,47 @@
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8-2025</t>
+          <t>ADOM-SL5-7-2025</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.237</v>
+        <v>4.7</v>
       </c>
       <c r="E48" t="n">
-        <v>5.999</v>
+        <v>0.104</v>
       </c>
       <c r="F48" t="n">
-        <v>2.967</v>
+        <v>0.004993</v>
       </c>
       <c r="G48" t="n">
-        <v>8.15</v>
+        <v>4.861</v>
       </c>
       <c r="H48" t="n">
-        <v>108</v>
+        <v>2.139</v>
       </c>
       <c r="I48" t="n">
-        <v>4.427</v>
+        <v>4.883</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7196</v>
+        <v>0.9748</v>
       </c>
       <c r="K48" t="n">
-        <v>1.362</v>
+        <v>1.448</v>
       </c>
       <c r="L48" t="n">
-        <v>15.77</v>
+        <v>11.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0.02534</v>
+        <v>0.02195</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4913</v>
+        <v>0.2926</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0466</v>
+        <v>0.03929</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2661</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="49">
@@ -2820,47 +2812,47 @@
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9-2025</t>
+          <t>ADOM-SL5-7-2025</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.071</v>
+        <v>4.7</v>
       </c>
       <c r="E49" t="n">
-        <v>7.726</v>
+        <v>0.104</v>
       </c>
       <c r="F49" t="n">
-        <v>3.275</v>
+        <v>0.004993</v>
       </c>
       <c r="G49" t="n">
-        <v>7.67</v>
+        <v>4.861</v>
       </c>
       <c r="H49" t="n">
-        <v>62</v>
+        <v>2.139</v>
       </c>
       <c r="I49" t="n">
-        <v>4.309</v>
+        <v>4.883</v>
       </c>
       <c r="J49" t="n">
-        <v>0.631</v>
+        <v>0.9748</v>
       </c>
       <c r="K49" t="n">
-        <v>1.317</v>
+        <v>1.448</v>
       </c>
       <c r="L49" t="n">
-        <v>19.52</v>
+        <v>11.25</v>
       </c>
       <c r="M49" t="n">
-        <v>0.02894</v>
+        <v>0.02195</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6939</v>
+        <v>0.2926</v>
       </c>
       <c r="O49" t="n">
-        <v>0.05412</v>
+        <v>0.03929</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3558</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="50">
@@ -2868,99 +2860,95 @@
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9-2025</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.071</v>
+        <v>4.237</v>
       </c>
       <c r="E50" t="n">
-        <v>7.726</v>
+        <v>0.178</v>
       </c>
       <c r="F50" t="n">
-        <v>3.275</v>
+        <v>0.009098999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>7.67</v>
+        <v>5.999</v>
       </c>
       <c r="H50" t="n">
-        <v>62</v>
+        <v>2.967</v>
       </c>
       <c r="I50" t="n">
-        <v>4.309</v>
+        <v>4.427</v>
       </c>
       <c r="J50" t="n">
-        <v>0.631</v>
+        <v>0.7196</v>
       </c>
       <c r="K50" t="n">
-        <v>1.317</v>
+        <v>1.362</v>
       </c>
       <c r="L50" t="n">
-        <v>19.52</v>
+        <v>15.77</v>
       </c>
       <c r="M50" t="n">
-        <v>0.02894</v>
+        <v>0.02534</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6939</v>
+        <v>0.4913</v>
       </c>
       <c r="O50" t="n">
-        <v>0.05412</v>
+        <v>0.0466</v>
       </c>
       <c r="P50" t="n">
-        <v>0.3558</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>Storage 6</t>
-        </is>
-      </c>
+      <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1-2025</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.858</v>
+        <v>4.237</v>
       </c>
       <c r="E51" t="n">
-        <v>24.45</v>
+        <v>0.178</v>
       </c>
       <c r="F51" t="n">
-        <v>2.925</v>
+        <v>0.009098999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>7.54</v>
+        <v>5.999</v>
       </c>
       <c r="H51" t="n">
-        <v>158</v>
+        <v>2.967</v>
       </c>
       <c r="I51" t="n">
-        <v>4.584</v>
+        <v>4.427</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.7196</v>
       </c>
       <c r="K51" t="n">
-        <v>1.395</v>
+        <v>1.362</v>
       </c>
       <c r="L51" t="n">
-        <v>28.5</v>
+        <v>15.77</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01775</v>
+        <v>0.02534</v>
       </c>
       <c r="N51" t="n">
-        <v>0.4815</v>
+        <v>0.4913</v>
       </c>
       <c r="O51" t="n">
-        <v>0.03025</v>
+        <v>0.0466</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2459</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="52">
@@ -2968,47 +2956,47 @@
       <c r="B52" s="1" t="n"/>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1-2025</t>
+          <t>ADOM-SL5-8-2025</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.858</v>
+        <v>4.237</v>
       </c>
       <c r="E52" t="n">
-        <v>24.45</v>
+        <v>0.178</v>
       </c>
       <c r="F52" t="n">
-        <v>2.925</v>
+        <v>0.009098999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>7.54</v>
+        <v>5.999</v>
       </c>
       <c r="H52" t="n">
-        <v>158</v>
+        <v>2.967</v>
       </c>
       <c r="I52" t="n">
-        <v>4.584</v>
+        <v>4.427</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.7196</v>
       </c>
       <c r="K52" t="n">
-        <v>1.395</v>
+        <v>1.362</v>
       </c>
       <c r="L52" t="n">
-        <v>28.5</v>
+        <v>15.77</v>
       </c>
       <c r="M52" t="n">
-        <v>0.01775</v>
+        <v>0.02534</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4815</v>
+        <v>0.4913</v>
       </c>
       <c r="O52" t="n">
-        <v>0.03025</v>
+        <v>0.0466</v>
       </c>
       <c r="P52" t="n">
-        <v>0.2459</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="53">
@@ -3016,47 +3004,47 @@
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10-2025</t>
+          <t>ADOM-SL5-9-2025</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.135</v>
+        <v>4.071</v>
       </c>
       <c r="E53" t="n">
-        <v>7.377</v>
+        <v>0.253</v>
       </c>
       <c r="F53" t="n">
-        <v>2.779</v>
+        <v>0.0124</v>
       </c>
       <c r="G53" t="n">
-        <v>7.68</v>
+        <v>7.726</v>
       </c>
       <c r="H53" t="n">
-        <v>23</v>
+        <v>3.275</v>
       </c>
       <c r="I53" t="n">
-        <v>4.499</v>
+        <v>4.309</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5392</v>
+        <v>0.631</v>
       </c>
       <c r="K53" t="n">
-        <v>1.331</v>
+        <v>1.317</v>
       </c>
       <c r="L53" t="n">
-        <v>31.71</v>
+        <v>19.52</v>
       </c>
       <c r="M53" t="n">
-        <v>0.02497</v>
+        <v>0.02894</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5331</v>
+        <v>0.6939</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03323</v>
+        <v>0.05412</v>
       </c>
       <c r="P53" t="n">
-        <v>0.2959</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="54">
@@ -3064,95 +3052,99 @@
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10-2025</t>
+          <t>ADOM-SL5-9-2025</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.135</v>
+        <v>4.071</v>
       </c>
       <c r="E54" t="n">
-        <v>7.377</v>
+        <v>0.253</v>
       </c>
       <c r="F54" t="n">
-        <v>2.779</v>
+        <v>0.0124</v>
       </c>
       <c r="G54" t="n">
-        <v>7.68</v>
+        <v>7.726</v>
       </c>
       <c r="H54" t="n">
-        <v>23</v>
+        <v>3.275</v>
       </c>
       <c r="I54" t="n">
-        <v>4.499</v>
+        <v>4.309</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5392</v>
+        <v>0.631</v>
       </c>
       <c r="K54" t="n">
-        <v>1.331</v>
+        <v>1.317</v>
       </c>
       <c r="L54" t="n">
-        <v>31.71</v>
+        <v>19.52</v>
       </c>
       <c r="M54" t="n">
-        <v>0.02497</v>
+        <v>0.02894</v>
       </c>
       <c r="N54" t="n">
-        <v>0.5331</v>
+        <v>0.6939</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03323</v>
+        <v>0.05412</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2959</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Storage 6</t>
+        </is>
+      </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2-2025</t>
+          <t>ADOM-SL6-1-2025</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.199</v>
+        <v>5.02</v>
       </c>
       <c r="E55" t="n">
-        <v>13.93</v>
+        <v>0.553</v>
       </c>
       <c r="F55" t="n">
-        <v>2.175</v>
+        <v>0.01413</v>
       </c>
       <c r="G55" t="n">
-        <v>6.61</v>
+        <v>24.45</v>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>2.262</v>
       </c>
       <c r="I55" t="n">
-        <v>4.712</v>
+        <v>4.584</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8028</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>1.415</v>
+        <v>1.395</v>
       </c>
       <c r="L55" t="n">
-        <v>14.4</v>
+        <v>28.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0.02235</v>
+        <v>0.01775</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4232</v>
+        <v>0.4815</v>
       </c>
       <c r="O55" t="n">
-        <v>0.04509</v>
+        <v>0.03025</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2539</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="56">
@@ -3160,47 +3152,47 @@
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2-2025</t>
+          <t>ADOM-SL6-1-2025</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.199</v>
+        <v>5.02</v>
       </c>
       <c r="E56" t="n">
-        <v>13.93</v>
+        <v>0.553</v>
       </c>
       <c r="F56" t="n">
-        <v>2.175</v>
+        <v>0.01413</v>
       </c>
       <c r="G56" t="n">
-        <v>6.61</v>
+        <v>24.45</v>
       </c>
       <c r="H56" t="n">
-        <v>45</v>
+        <v>2.262</v>
       </c>
       <c r="I56" t="n">
-        <v>4.712</v>
+        <v>4.584</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8028</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>1.415</v>
+        <v>1.395</v>
       </c>
       <c r="L56" t="n">
-        <v>14.4</v>
+        <v>28.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0.02235</v>
+        <v>0.01775</v>
       </c>
       <c r="N56" t="n">
-        <v>0.4232</v>
+        <v>0.4815</v>
       </c>
       <c r="O56" t="n">
-        <v>0.04509</v>
+        <v>0.03025</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2539</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="57">
@@ -3208,47 +3200,47 @@
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3-2025</t>
+          <t>ADOM-SL6-10-2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.619</v>
+        <v>4.136</v>
       </c>
       <c r="E57" t="n">
-        <v>8.983000000000001</v>
+        <v>0.205</v>
       </c>
       <c r="F57" t="n">
-        <v>2.093</v>
+        <v>0.009126</v>
       </c>
       <c r="G57" t="n">
-        <v>6.91</v>
+        <v>7.377</v>
       </c>
       <c r="H57" t="n">
-        <v>25</v>
+        <v>2.779</v>
       </c>
       <c r="I57" t="n">
-        <v>4.516</v>
+        <v>4.499</v>
       </c>
       <c r="J57" t="n">
-        <v>0.6419</v>
+        <v>0.5392</v>
       </c>
       <c r="K57" t="n">
-        <v>1.369</v>
+        <v>1.331</v>
       </c>
       <c r="L57" t="n">
-        <v>20.53</v>
+        <v>31.71</v>
       </c>
       <c r="M57" t="n">
-        <v>0.01709</v>
+        <v>0.02497</v>
       </c>
       <c r="N57" t="n">
-        <v>0.3512</v>
+        <v>0.5331</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02824</v>
+        <v>0.03323</v>
       </c>
       <c r="P57" t="n">
-        <v>0.2014</v>
+        <v>0.2959</v>
       </c>
     </row>
     <row r="58">
@@ -3256,47 +3248,47 @@
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3-2025</t>
+          <t>ADOM-SL6-10-2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.619</v>
+        <v>4.136</v>
       </c>
       <c r="E58" t="n">
-        <v>8.983000000000001</v>
+        <v>0.205</v>
       </c>
       <c r="F58" t="n">
-        <v>2.093</v>
+        <v>0.009126</v>
       </c>
       <c r="G58" t="n">
-        <v>6.91</v>
+        <v>7.377</v>
       </c>
       <c r="H58" t="n">
-        <v>25</v>
+        <v>2.779</v>
       </c>
       <c r="I58" t="n">
-        <v>4.516</v>
+        <v>4.499</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6419</v>
+        <v>0.5392</v>
       </c>
       <c r="K58" t="n">
-        <v>1.369</v>
+        <v>1.331</v>
       </c>
       <c r="L58" t="n">
-        <v>20.53</v>
+        <v>31.71</v>
       </c>
       <c r="M58" t="n">
-        <v>0.01709</v>
+        <v>0.02497</v>
       </c>
       <c r="N58" t="n">
-        <v>0.3512</v>
+        <v>0.5331</v>
       </c>
       <c r="O58" t="n">
-        <v>0.02824</v>
+        <v>0.03323</v>
       </c>
       <c r="P58" t="n">
-        <v>0.2014</v>
+        <v>0.2959</v>
       </c>
     </row>
     <row r="59">
@@ -3304,47 +3296,47 @@
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3-2025</t>
+          <t>ADOM-SL6-2-2025</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.619</v>
+        <v>4.2</v>
       </c>
       <c r="E59" t="n">
-        <v>8.983000000000001</v>
+        <v>0.303</v>
       </c>
       <c r="F59" t="n">
-        <v>2.093</v>
+        <v>0.0143</v>
       </c>
       <c r="G59" t="n">
-        <v>6.91</v>
+        <v>13.93</v>
       </c>
       <c r="H59" t="n">
-        <v>25</v>
+        <v>2.175</v>
       </c>
       <c r="I59" t="n">
-        <v>4.516</v>
+        <v>4.712</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6419</v>
+        <v>0.8028</v>
       </c>
       <c r="K59" t="n">
-        <v>1.369</v>
+        <v>1.415</v>
       </c>
       <c r="L59" t="n">
-        <v>20.53</v>
+        <v>14.4</v>
       </c>
       <c r="M59" t="n">
-        <v>0.01709</v>
+        <v>0.02235</v>
       </c>
       <c r="N59" t="n">
-        <v>0.3512</v>
+        <v>0.4232</v>
       </c>
       <c r="O59" t="n">
-        <v>0.02824</v>
+        <v>0.04509</v>
       </c>
       <c r="P59" t="n">
-        <v>0.2014</v>
+        <v>0.2539</v>
       </c>
     </row>
     <row r="60">
@@ -3352,47 +3344,47 @@
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4-2025</t>
+          <t>ADOM-SL6-2-2025</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.639</v>
+        <v>4.2</v>
       </c>
       <c r="E60" t="n">
-        <v>8.987</v>
+        <v>0.303</v>
       </c>
       <c r="F60" t="n">
-        <v>2.226</v>
+        <v>0.0143</v>
       </c>
       <c r="G60" t="n">
-        <v>6.63</v>
+        <v>13.93</v>
       </c>
       <c r="H60" t="n">
-        <v>-46</v>
+        <v>2.175</v>
       </c>
       <c r="I60" t="n">
-        <v>4.954</v>
+        <v>4.712</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8028</v>
       </c>
       <c r="K60" t="n">
-        <v>1.436</v>
+        <v>1.415</v>
       </c>
       <c r="L60" t="n">
-        <v>12.45</v>
+        <v>14.4</v>
       </c>
       <c r="M60" t="n">
-        <v>0.02173</v>
+        <v>0.02235</v>
       </c>
       <c r="N60" t="n">
-        <v>0.3436</v>
+        <v>0.4232</v>
       </c>
       <c r="O60" t="n">
-        <v>0.04184</v>
+        <v>0.04509</v>
       </c>
       <c r="P60" t="n">
-        <v>0.2084</v>
+        <v>0.2539</v>
       </c>
     </row>
     <row r="61">
@@ -3400,47 +3392,47 @@
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4-2025</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.639</v>
+        <v>4.622</v>
       </c>
       <c r="E61" t="n">
-        <v>8.987</v>
+        <v>0.188</v>
       </c>
       <c r="F61" t="n">
-        <v>2.226</v>
+        <v>0.01227</v>
       </c>
       <c r="G61" t="n">
-        <v>6.63</v>
+        <v>8.983000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>-46</v>
+        <v>2.093</v>
       </c>
       <c r="I61" t="n">
-        <v>4.954</v>
+        <v>4.516</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.6419</v>
       </c>
       <c r="K61" t="n">
-        <v>1.436</v>
+        <v>1.369</v>
       </c>
       <c r="L61" t="n">
-        <v>12.45</v>
+        <v>20.53</v>
       </c>
       <c r="M61" t="n">
-        <v>0.02173</v>
+        <v>0.01709</v>
       </c>
       <c r="N61" t="n">
-        <v>0.3436</v>
+        <v>0.3512</v>
       </c>
       <c r="O61" t="n">
-        <v>0.04184</v>
+        <v>0.02824</v>
       </c>
       <c r="P61" t="n">
-        <v>0.2084</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="62">
@@ -3448,47 +3440,47 @@
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-6-2025</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.998</v>
+        <v>4.622</v>
       </c>
       <c r="E62" t="n">
-        <v>8.151</v>
+        <v>0.188</v>
       </c>
       <c r="F62" t="n">
-        <v>1.73</v>
+        <v>0.01227</v>
       </c>
       <c r="G62" t="n">
-        <v>6.99</v>
+        <v>8.983000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>-43</v>
+        <v>2.093</v>
       </c>
       <c r="I62" t="n">
-        <v>4.513</v>
+        <v>4.516</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8676</v>
+        <v>0.6419</v>
       </c>
       <c r="K62" t="n">
-        <v>1.374</v>
+        <v>1.369</v>
       </c>
       <c r="L62" t="n">
-        <v>12.4</v>
+        <v>20.53</v>
       </c>
       <c r="M62" t="n">
-        <v>0.01654</v>
+        <v>0.01709</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2206</v>
+        <v>0.3512</v>
       </c>
       <c r="O62" t="n">
-        <v>0.02485</v>
+        <v>0.02824</v>
       </c>
       <c r="P62" t="n">
-        <v>0.1534</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="63">
@@ -3496,47 +3488,47 @@
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-7-2025</t>
+          <t>ADOM-SL6-3-2025</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.115</v>
+        <v>4.622</v>
       </c>
       <c r="E63" t="n">
-        <v>8.904999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="F63" t="n">
-        <v>2.65</v>
+        <v>0.01227</v>
       </c>
       <c r="G63" t="n">
-        <v>7.15</v>
+        <v>8.983000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>2.093</v>
       </c>
       <c r="I63" t="n">
-        <v>4.706</v>
+        <v>4.516</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8653</v>
+        <v>0.6419</v>
       </c>
       <c r="K63" t="n">
-        <v>1.359</v>
+        <v>1.369</v>
       </c>
       <c r="L63" t="n">
-        <v>13.32</v>
+        <v>20.53</v>
       </c>
       <c r="M63" t="n">
-        <v>0.02341</v>
+        <v>0.01709</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3523</v>
+        <v>0.3512</v>
       </c>
       <c r="O63" t="n">
-        <v>0.04123</v>
+        <v>0.02824</v>
       </c>
       <c r="P63" t="n">
-        <v>0.219</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="64">
@@ -3544,47 +3536,47 @@
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-8-2025</t>
+          <t>ADOM-SL6-4-2025</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.197</v>
+        <v>3.64</v>
       </c>
       <c r="E64" t="n">
-        <v>9.698</v>
+        <v>0.2</v>
       </c>
       <c r="F64" t="n">
-        <v>2.96</v>
+        <v>0.01358</v>
       </c>
       <c r="G64" t="n">
-        <v>6.98</v>
+        <v>8.987</v>
       </c>
       <c r="H64" t="n">
-        <v>-93</v>
+        <v>2.225</v>
       </c>
       <c r="I64" t="n">
-        <v>5.121</v>
+        <v>4.954</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8416</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>1.458</v>
+        <v>1.436</v>
       </c>
       <c r="L64" t="n">
-        <v>15.11</v>
+        <v>12.45</v>
       </c>
       <c r="M64" t="n">
-        <v>0.02161</v>
+        <v>0.02173</v>
       </c>
       <c r="N64" t="n">
-        <v>0.4261</v>
+        <v>0.3436</v>
       </c>
       <c r="O64" t="n">
-        <v>0.04956</v>
+        <v>0.04184</v>
       </c>
       <c r="P64" t="n">
-        <v>0.2285</v>
+        <v>0.2084</v>
       </c>
     </row>
     <row r="65">
@@ -3592,99 +3584,95 @@
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-9-2025</t>
+          <t>ADOM-SL6-4-2025</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4.888</v>
+        <v>3.64</v>
       </c>
       <c r="E65" t="n">
-        <v>9.523</v>
+        <v>0.2</v>
       </c>
       <c r="F65" t="n">
-        <v>2.562</v>
+        <v>0.01358</v>
       </c>
       <c r="G65" t="n">
-        <v>8.01</v>
+        <v>8.987</v>
       </c>
       <c r="H65" t="n">
-        <v>10</v>
+        <v>2.225</v>
       </c>
       <c r="I65" t="n">
-        <v>4.894</v>
+        <v>4.954</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6965</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>1.389</v>
+        <v>1.436</v>
       </c>
       <c r="L65" t="n">
-        <v>19.96</v>
+        <v>12.45</v>
       </c>
       <c r="M65" t="n">
-        <v>0.02365</v>
+        <v>0.02173</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4933</v>
+        <v>0.3436</v>
       </c>
       <c r="O65" t="n">
-        <v>0.04115</v>
+        <v>0.04184</v>
       </c>
       <c r="P65" t="n">
-        <v>0.239</v>
+        <v>0.2084</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>Storage 7</t>
-        </is>
-      </c>
+      <c r="B66" s="1" t="n"/>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-1-2025</t>
+          <t>ADOM-SL6-6-2025</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2.971</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>20.8</v>
+        <v>0.141</v>
       </c>
       <c r="F66" t="n">
-        <v>2.876</v>
+        <v>0.01359</v>
       </c>
       <c r="G66" t="n">
-        <v>7.06</v>
+        <v>8.151</v>
       </c>
       <c r="H66" t="n">
-        <v>52</v>
+        <v>1.73</v>
       </c>
       <c r="I66" t="n">
-        <v>4.511</v>
+        <v>4.513</v>
       </c>
       <c r="J66" t="n">
-        <v>0.576</v>
+        <v>0.8676</v>
       </c>
       <c r="K66" t="n">
-        <v>1.356</v>
+        <v>1.374</v>
       </c>
       <c r="L66" t="n">
-        <v>23.04</v>
+        <v>12.4</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01435</v>
+        <v>0.01654</v>
       </c>
       <c r="N66" t="n">
-        <v>0.4037</v>
+        <v>0.2206</v>
       </c>
       <c r="O66" t="n">
-        <v>0.02957</v>
+        <v>0.02485</v>
       </c>
       <c r="P66" t="n">
-        <v>0.2128</v>
+        <v>0.1534</v>
       </c>
     </row>
     <row r="67">
@@ -3692,47 +3680,47 @@
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-10-2025</t>
+          <t>ADOM-SL6-7-2025</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2.332</v>
+        <v>4.115</v>
       </c>
       <c r="E67" t="n">
-        <v>9.772</v>
+        <v>0.236</v>
       </c>
       <c r="F67" t="n">
-        <v>2.703</v>
+        <v>0.01234</v>
       </c>
       <c r="G67" t="n">
-        <v>7.71</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>80</v>
+        <v>2.65</v>
       </c>
       <c r="I67" t="n">
-        <v>4.075</v>
+        <v>4.706</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6398</v>
+        <v>0.8653</v>
       </c>
       <c r="K67" t="n">
-        <v>1.298</v>
+        <v>1.359</v>
       </c>
       <c r="L67" t="n">
-        <v>16.01</v>
+        <v>13.32</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01696</v>
+        <v>0.02341</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3117</v>
+        <v>0.3523</v>
       </c>
       <c r="O67" t="n">
-        <v>0.02842</v>
+        <v>0.04123</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2034</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="68">
@@ -3740,47 +3728,47 @@
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-2-2025</t>
+          <t>ADOM-SL6-8-2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.182</v>
+        <v>2.986</v>
       </c>
       <c r="E68" t="n">
-        <v>8.198</v>
+        <v>0.239</v>
       </c>
       <c r="F68" t="n">
-        <v>1.611</v>
+        <v>0.02295</v>
       </c>
       <c r="G68" t="n">
-        <v>8.800000000000001</v>
+        <v>9.698</v>
       </c>
       <c r="H68" t="n">
-        <v>-4</v>
+        <v>2.464</v>
       </c>
       <c r="I68" t="n">
-        <v>3.964</v>
+        <v>5.121</v>
       </c>
       <c r="J68" t="n">
-        <v>1.85</v>
+        <v>0.8416</v>
       </c>
       <c r="K68" t="n">
-        <v>1.341</v>
+        <v>1.458</v>
       </c>
       <c r="L68" t="n">
-        <v>4.411</v>
+        <v>15.11</v>
       </c>
       <c r="M68" t="n">
-        <v>0.02292</v>
+        <v>0.02161</v>
       </c>
       <c r="N68" t="n">
-        <v>0.04119</v>
+        <v>0.4261</v>
       </c>
       <c r="O68" t="n">
-        <v>0.05266</v>
+        <v>0.04956</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1515</v>
+        <v>0.2285</v>
       </c>
     </row>
     <row r="69">
@@ -3788,95 +3776,99 @@
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-3-2025</t>
+          <t>ADOM-SL6-9-2025</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3.628</v>
+        <v>4.889</v>
       </c>
       <c r="E69" t="n">
-        <v>17.65</v>
+        <v>0.244</v>
       </c>
       <c r="F69" t="n">
-        <v>1.218</v>
+        <v>0.008755000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>6.9</v>
+        <v>9.523</v>
       </c>
       <c r="H69" t="n">
-        <v>-165</v>
+        <v>2.562</v>
       </c>
       <c r="I69" t="n">
-        <v>5.545</v>
+        <v>4.894</v>
       </c>
       <c r="J69" t="n">
-        <v>1.146</v>
+        <v>0.6965</v>
       </c>
       <c r="K69" t="n">
-        <v>1.515</v>
+        <v>1.389</v>
       </c>
       <c r="L69" t="n">
-        <v>9.685</v>
+        <v>19.96</v>
       </c>
       <c r="M69" t="n">
-        <v>0.0175</v>
+        <v>0.02365</v>
       </c>
       <c r="N69" t="n">
-        <v>0.1963</v>
+        <v>0.4933</v>
       </c>
       <c r="O69" t="n">
-        <v>0.03261</v>
+        <v>0.04115</v>
       </c>
       <c r="P69" t="n">
-        <v>0.1118</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Storage 7</t>
+        </is>
+      </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-5-2025</t>
+          <t>ADOM-SL7-1-2025</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.793</v>
+        <v>4.462</v>
       </c>
       <c r="E70" t="n">
-        <v>7.129</v>
+        <v>0.518</v>
       </c>
       <c r="F70" t="n">
-        <v>1.656</v>
+        <v>0.01786</v>
       </c>
       <c r="G70" t="n">
-        <v>8.210000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="H70" t="n">
-        <v>12</v>
+        <v>2.49</v>
       </c>
       <c r="I70" t="n">
-        <v>4.005</v>
+        <v>4.511</v>
       </c>
       <c r="J70" t="n">
-        <v>1.012</v>
+        <v>0.576</v>
       </c>
       <c r="K70" t="n">
-        <v>1.342</v>
+        <v>1.356</v>
       </c>
       <c r="L70" t="n">
-        <v>7.656</v>
+        <v>23.04</v>
       </c>
       <c r="M70" t="n">
-        <v>0.01558</v>
+        <v>0.01435</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1339</v>
+        <v>0.4037</v>
       </c>
       <c r="O70" t="n">
-        <v>0.02096</v>
+        <v>0.02957</v>
       </c>
       <c r="P70" t="n">
-        <v>0.1312</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="71">
@@ -3884,47 +3876,47 @@
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-6-2025</t>
+          <t>ADOM-SL7-10-2025</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.264</v>
+        <v>4.415</v>
       </c>
       <c r="E71" t="n">
-        <v>9.097</v>
+        <v>0.2</v>
       </c>
       <c r="F71" t="n">
-        <v>1.309</v>
+        <v>0.007326</v>
       </c>
       <c r="G71" t="n">
-        <v>8.640000000000001</v>
+        <v>9.772</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>2.047</v>
       </c>
       <c r="I71" t="n">
-        <v>3.69</v>
+        <v>4.075</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9691</v>
+        <v>0.6398</v>
       </c>
       <c r="K71" t="n">
-        <v>1.295</v>
+        <v>1.298</v>
       </c>
       <c r="L71" t="n">
-        <v>8.146000000000001</v>
+        <v>16.01</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01189</v>
+        <v>0.01696</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0949</v>
+        <v>0.3117</v>
       </c>
       <c r="O71" t="n">
-        <v>0.01796</v>
+        <v>0.02842</v>
       </c>
       <c r="P71" t="n">
-        <v>0.1067</v>
+        <v>0.2034</v>
       </c>
     </row>
     <row r="72">
@@ -3932,47 +3924,47 @@
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-7-2025</t>
+          <t>ADOM-SL7-2-2025</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2.863</v>
+        <v>4.773</v>
       </c>
       <c r="E72" t="n">
-        <v>6.717</v>
+        <v>0.116</v>
       </c>
       <c r="F72" t="n">
-        <v>1.742</v>
+        <v>0.00474</v>
       </c>
       <c r="G72" t="n">
-        <v>8.720000000000001</v>
+        <v>8.198</v>
       </c>
       <c r="H72" t="n">
-        <v>90</v>
+        <v>1.415</v>
       </c>
       <c r="I72" t="n">
-        <v>4.22</v>
+        <v>3.964</v>
       </c>
       <c r="J72" t="n">
-        <v>1.022</v>
+        <v>1.85</v>
       </c>
       <c r="K72" t="n">
-        <v>1.391</v>
+        <v>1.341</v>
       </c>
       <c r="L72" t="n">
-        <v>7.665</v>
+        <v>4.411</v>
       </c>
       <c r="M72" t="n">
-        <v>0.0145</v>
+        <v>0.02292</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1215</v>
+        <v>0.04119</v>
       </c>
       <c r="O72" t="n">
-        <v>0.01931</v>
+        <v>0.05266</v>
       </c>
       <c r="P72" t="n">
-        <v>0.1188</v>
+        <v>0.1515</v>
       </c>
     </row>
     <row r="73">
@@ -3980,47 +3972,47 @@
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-8-2025</t>
+          <t>ADOM-SL7-3-2025</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.344</v>
+        <v>4.737</v>
       </c>
       <c r="E73" t="n">
-        <v>7.297</v>
+        <v>0.199</v>
       </c>
       <c r="F73" t="n">
-        <v>1.933</v>
+        <v>0.007839</v>
       </c>
       <c r="G73" t="n">
-        <v>8.67</v>
+        <v>17.65</v>
       </c>
       <c r="H73" t="n">
-        <v>80</v>
+        <v>1.127</v>
       </c>
       <c r="I73" t="n">
-        <v>3.882</v>
+        <v>5.545</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8738</v>
+        <v>1.146</v>
       </c>
       <c r="K73" t="n">
-        <v>1.314</v>
+        <v>1.515</v>
       </c>
       <c r="L73" t="n">
-        <v>9.353999999999999</v>
+        <v>9.685</v>
       </c>
       <c r="M73" t="n">
-        <v>0.01202</v>
+        <v>0.0175</v>
       </c>
       <c r="N73" t="n">
-        <v>0.1186</v>
+        <v>0.1963</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01815</v>
+        <v>0.03261</v>
       </c>
       <c r="P73" t="n">
-        <v>0.1148</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="74">
@@ -4028,99 +4020,93 @@
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-9-2025</t>
+          <t>ADOM-SL7-5-2025</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.761</v>
+        <v>4.043</v>
       </c>
       <c r="E74" t="n">
-        <v>7.917</v>
+        <v>0.102</v>
       </c>
       <c r="F74" t="n">
-        <v>1.617</v>
+        <v>0.005955</v>
       </c>
       <c r="G74" t="n">
-        <v>8.890000000000001</v>
+        <v>7.129</v>
       </c>
       <c r="H74" t="n">
-        <v>80</v>
+        <v>1.431</v>
       </c>
       <c r="I74" t="n">
-        <v>3.971</v>
+        <v>4.005</v>
       </c>
       <c r="J74" t="n">
-        <v>0.971</v>
+        <v>1.012</v>
       </c>
       <c r="K74" t="n">
-        <v>1.348</v>
+        <v>1.342</v>
       </c>
       <c r="L74" t="n">
-        <v>8.121</v>
+        <v>7.656</v>
       </c>
       <c r="M74" t="n">
-        <v>0.01395</v>
+        <v>0.01558</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1289</v>
+        <v>0.1339</v>
       </c>
       <c r="O74" t="n">
-        <v>0.02044</v>
+        <v>0.02096</v>
       </c>
       <c r="P74" t="n">
-        <v>0.126</v>
+        <v>0.1312</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>Storage 8</t>
-        </is>
-      </c>
+      <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-1-2025</t>
+          <t>ADOM-SL7-6-2025</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.138</v>
+        <v>4.647</v>
       </c>
       <c r="E75" t="n">
-        <v>2.174</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1.657</v>
-      </c>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>5.46</v>
+        <v>9.097</v>
       </c>
       <c r="H75" t="n">
-        <v>163</v>
+        <v>0.9564</v>
       </c>
       <c r="I75" t="n">
-        <v>4.892</v>
+        <v>3.69</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7541</v>
+        <v>0.9691</v>
       </c>
       <c r="K75" t="n">
-        <v>1.355</v>
+        <v>1.295</v>
       </c>
       <c r="L75" t="n">
-        <v>8.605</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>0.005713</v>
+        <v>0.01189</v>
       </c>
       <c r="N75" t="n">
-        <v>0.08502999999999999</v>
+        <v>0.0949</v>
       </c>
       <c r="O75" t="n">
-        <v>0.008819</v>
+        <v>0.01796</v>
       </c>
       <c r="P75" t="n">
-        <v>0.06877</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="76">
@@ -4128,47 +4114,47 @@
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-10-2025</t>
+          <t>ADOM-SL7-7-2025</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.357</v>
+        <v>4.286</v>
       </c>
       <c r="E76" t="n">
-        <v>1.801</v>
+        <v>0.101</v>
       </c>
       <c r="F76" t="n">
-        <v>1.278</v>
+        <v>0.006432</v>
       </c>
       <c r="G76" t="n">
-        <v>5.72</v>
+        <v>6.717</v>
       </c>
       <c r="H76" t="n">
-        <v>59</v>
+        <v>1.504</v>
       </c>
       <c r="I76" t="n">
-        <v>4.824</v>
+        <v>4.22</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6439</v>
+        <v>1.022</v>
       </c>
       <c r="K76" t="n">
-        <v>1.297</v>
+        <v>1.391</v>
       </c>
       <c r="L76" t="n">
-        <v>11.14</v>
+        <v>7.665</v>
       </c>
       <c r="M76" t="n">
-        <v>0.006679</v>
+        <v>0.0145</v>
       </c>
       <c r="N76" t="n">
-        <v>0.1141</v>
+        <v>0.1215</v>
       </c>
       <c r="O76" t="n">
-        <v>0.01039</v>
+        <v>0.01931</v>
       </c>
       <c r="P76" t="n">
-        <v>0.08592</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="77">
@@ -4176,47 +4162,47 @@
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-2-2025</t>
+          <t>ADOM-SL7-8-2025</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>4.217</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8693</v>
+        <v>0.109</v>
       </c>
       <c r="F77" t="n">
-        <v>1.85</v>
+        <v>0.006072</v>
       </c>
       <c r="G77" t="n">
-        <v>4.88</v>
+        <v>7.297</v>
       </c>
       <c r="H77" t="n">
-        <v>167</v>
+        <v>1.494</v>
       </c>
       <c r="I77" t="n">
-        <v>6.037</v>
+        <v>3.882</v>
       </c>
       <c r="J77" t="n">
-        <v>1.063</v>
+        <v>0.8738</v>
       </c>
       <c r="K77" t="n">
-        <v>1.353</v>
+        <v>1.314</v>
       </c>
       <c r="L77" t="n">
-        <v>2.408</v>
+        <v>9.353999999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>0.003814</v>
+        <v>0.01202</v>
       </c>
       <c r="N77" t="n">
-        <v>0.02562</v>
+        <v>0.1186</v>
       </c>
       <c r="O77" t="n">
-        <v>0.005948</v>
+        <v>0.01815</v>
       </c>
       <c r="P77" t="n">
-        <v>0.03609</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="78">
@@ -4224,95 +4210,99 @@
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-3-2025</t>
+          <t>ADOM-SL7-9-2025</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.6163</v>
+        <v>3.846</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6715</v>
+        <v>0.112</v>
       </c>
       <c r="F78" t="n">
-        <v>1.345</v>
+        <v>0.008274</v>
       </c>
       <c r="G78" t="n">
-        <v>5.26</v>
+        <v>7.917</v>
       </c>
       <c r="H78" t="n">
-        <v>170</v>
+        <v>1.415</v>
       </c>
       <c r="I78" t="n">
-        <v>4.797</v>
+        <v>3.971</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9374</v>
+        <v>0.971</v>
       </c>
       <c r="K78" t="n">
-        <v>1.297</v>
+        <v>1.348</v>
       </c>
       <c r="L78" t="n">
-        <v>4.16</v>
+        <v>8.121</v>
       </c>
       <c r="M78" t="n">
-        <v>0.002023</v>
+        <v>0.01395</v>
       </c>
       <c r="N78" t="n">
-        <v>0.02125</v>
+        <v>0.1289</v>
       </c>
       <c r="O78" t="n">
-        <v>0.005083</v>
+        <v>0.02044</v>
       </c>
       <c r="P78" t="n">
-        <v>0.03163</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="n"/>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>Storage 8</t>
+        </is>
+      </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-4-2025</t>
+          <t>ADOM-SL8-1-2025</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.999</v>
+        <v>1.308</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9102</v>
+        <v>0.02</v>
       </c>
       <c r="F79" t="n">
-        <v>21.32</v>
+        <v>0.00671</v>
       </c>
       <c r="G79" t="n">
-        <v>4.64</v>
+        <v>2.174</v>
       </c>
       <c r="H79" t="n">
-        <v>246</v>
+        <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>5.602</v>
+        <v>4.892</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8484</v>
+        <v>0.7541</v>
       </c>
       <c r="K79" t="n">
-        <v>1.311</v>
+        <v>1.355</v>
       </c>
       <c r="L79" t="n">
-        <v>4.187</v>
+        <v>8.605</v>
       </c>
       <c r="M79" t="n">
-        <v>0.002339</v>
+        <v>0.005713</v>
       </c>
       <c r="N79" t="n">
-        <v>0.02625</v>
+        <v>0.08502999999999999</v>
       </c>
       <c r="O79" t="n">
-        <v>0.005212</v>
+        <v>0.008819</v>
       </c>
       <c r="P79" t="n">
-        <v>0.03373</v>
+        <v>0.06877</v>
       </c>
     </row>
     <row r="80">
@@ -4320,47 +4310,47 @@
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-6-2025</t>
+          <t>ADOM-SL8-10-2025</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.046</v>
+        <v>1.357</v>
       </c>
       <c r="E80" t="n">
-        <v>6.02</v>
+        <v>0.023</v>
       </c>
       <c r="F80" t="n">
-        <v>1.612</v>
+        <v>0.00673</v>
       </c>
       <c r="G80" t="n">
-        <v>6.19</v>
+        <v>1.801</v>
       </c>
       <c r="H80" t="n">
-        <v>-78</v>
+        <v>1.277</v>
       </c>
       <c r="I80" t="n">
-        <v>4.844</v>
+        <v>4.824</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9735</v>
+        <v>0.6439</v>
       </c>
       <c r="K80" t="n">
-        <v>1.347</v>
+        <v>1.297</v>
       </c>
       <c r="L80" t="n">
-        <v>10.1</v>
+        <v>11.14</v>
       </c>
       <c r="M80" t="n">
-        <v>0.01396</v>
+        <v>0.006679</v>
       </c>
       <c r="N80" t="n">
-        <v>0.2088</v>
+        <v>0.1141</v>
       </c>
       <c r="O80" t="n">
-        <v>0.02419</v>
+        <v>0.01039</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1314</v>
+        <v>0.08592</v>
       </c>
     </row>
     <row r="81">
@@ -4368,47 +4358,47 @@
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-7-2025</t>
+          <t>ADOM-SL8-2-2025</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.6835</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8862</v>
+        <v>0.006</v>
       </c>
       <c r="F81" t="n">
-        <v>1.932</v>
+        <v>0.004351</v>
       </c>
       <c r="G81" t="n">
-        <v>5.17</v>
+        <v>0.8693</v>
       </c>
       <c r="H81" t="n">
-        <v>174</v>
+        <v>0.6902</v>
       </c>
       <c r="I81" t="n">
-        <v>4.667</v>
+        <v>6.037</v>
       </c>
       <c r="J81" t="n">
-        <v>0.894</v>
+        <v>1.063</v>
       </c>
       <c r="K81" t="n">
-        <v>1.292</v>
+        <v>1.353</v>
       </c>
       <c r="L81" t="n">
-        <v>6.299</v>
+        <v>2.408</v>
       </c>
       <c r="M81" t="n">
-        <v>0.002951</v>
+        <v>0.003814</v>
       </c>
       <c r="N81" t="n">
-        <v>0.03797</v>
+        <v>0.02562</v>
       </c>
       <c r="O81" t="n">
-        <v>0.00649</v>
+        <v>0.005948</v>
       </c>
       <c r="P81" t="n">
-        <v>0.03998</v>
+        <v>0.03609</v>
       </c>
     </row>
     <row r="82">
@@ -4416,47 +4406,47 @@
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-8-2025</t>
+          <t>ADOM-SL8-3-2025</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.9291</v>
+        <v>1.5</v>
       </c>
       <c r="E82" t="n">
-        <v>1.267</v>
+        <v>0.006</v>
       </c>
       <c r="F82" t="n">
-        <v>1.191</v>
+        <v>0.00475</v>
       </c>
       <c r="G82" t="n">
-        <v>8.51</v>
+        <v>0.6715</v>
       </c>
       <c r="H82" t="n">
-        <v>-17</v>
+        <v>0.8935</v>
       </c>
       <c r="I82" t="n">
-        <v>4.234</v>
+        <v>4.797</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6378</v>
+        <v>0.9374</v>
       </c>
       <c r="K82" t="n">
-        <v>1.316</v>
+        <v>1.297</v>
       </c>
       <c r="L82" t="n">
-        <v>9.050000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="M82" t="n">
-        <v>0.003329</v>
+        <v>0.002023</v>
       </c>
       <c r="N82" t="n">
-        <v>0.06454</v>
+        <v>0.02125</v>
       </c>
       <c r="O82" t="n">
-        <v>0.007661</v>
+        <v>0.005083</v>
       </c>
       <c r="P82" t="n">
-        <v>0.05387</v>
+        <v>0.03163</v>
       </c>
     </row>
     <row r="83">
@@ -4464,99 +4454,95 @@
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL8-9-2025</t>
+          <t>ADOM-SL8-4-2025</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.182</v>
+        <v>3.171</v>
       </c>
       <c r="E83" t="n">
-        <v>2.747</v>
+        <v>0.146</v>
       </c>
       <c r="F83" t="n">
-        <v>0.583</v>
+        <v>0.009873</v>
       </c>
       <c r="G83" t="n">
-        <v>4.79</v>
+        <v>0.9102</v>
       </c>
       <c r="H83" t="n">
-        <v>189</v>
+        <v>16.04</v>
       </c>
       <c r="I83" t="n">
-        <v>5.901</v>
+        <v>5.602</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6947</v>
+        <v>0.8484</v>
       </c>
       <c r="K83" t="n">
-        <v>1.408</v>
+        <v>1.311</v>
       </c>
       <c r="L83" t="n">
-        <v>9.747999999999999</v>
+        <v>4.187</v>
       </c>
       <c r="M83" t="n">
-        <v>0.004853</v>
+        <v>0.002339</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0825</v>
+        <v>0.02625</v>
       </c>
       <c r="O83" t="n">
-        <v>0.007982</v>
+        <v>0.005212</v>
       </c>
       <c r="P83" t="n">
-        <v>0.05669</v>
+        <v>0.03373</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>Storage 9</t>
-        </is>
-      </c>
+      <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-1-2025</t>
+          <t>ADOM-SL8-6-2025</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.817</v>
+        <v>2.667</v>
       </c>
       <c r="E84" t="n">
-        <v>5.618</v>
+        <v>0.081</v>
       </c>
       <c r="F84" t="n">
-        <v>3.455</v>
+        <v>0.01059</v>
       </c>
       <c r="G84" t="n">
-        <v>5.99</v>
+        <v>6.02</v>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>1.346</v>
       </c>
       <c r="I84" t="n">
-        <v>4.796</v>
+        <v>4.844</v>
       </c>
       <c r="J84" t="n">
-        <v>1.604</v>
+        <v>0.9735</v>
       </c>
       <c r="K84" t="n">
-        <v>1.397</v>
+        <v>1.347</v>
       </c>
       <c r="L84" t="n">
-        <v>6.788</v>
+        <v>10.1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.02092</v>
+        <v>0.01396</v>
       </c>
       <c r="N84" t="n">
-        <v>0.1221</v>
+        <v>0.2088</v>
       </c>
       <c r="O84" t="n">
-        <v>0.047</v>
+        <v>0.02419</v>
       </c>
       <c r="P84" t="n">
-        <v>0.1436</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="85">
@@ -4564,47 +4550,47 @@
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-10-2025</t>
+          <t>ADOM-SL8-7-2025</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="E85" t="n">
-        <v>5.589</v>
+        <v>0.013</v>
       </c>
       <c r="F85" t="n">
-        <v>3.706</v>
+        <v>0.003594</v>
       </c>
       <c r="G85" t="n">
-        <v>6.56</v>
+        <v>0.8862</v>
       </c>
       <c r="H85" t="n">
-        <v>42</v>
+        <v>1.467</v>
       </c>
       <c r="I85" t="n">
-        <v>4.577</v>
+        <v>4.667</v>
       </c>
       <c r="J85" t="n">
-        <v>0.7893</v>
+        <v>0.894</v>
       </c>
       <c r="K85" t="n">
-        <v>1.356</v>
+        <v>1.292</v>
       </c>
       <c r="L85" t="n">
-        <v>13.18</v>
+        <v>6.299</v>
       </c>
       <c r="M85" t="n">
-        <v>0.0154</v>
+        <v>0.002951</v>
       </c>
       <c r="N85" t="n">
-        <v>0.2518</v>
+        <v>0.03797</v>
       </c>
       <c r="O85" t="n">
-        <v>0.02429</v>
+        <v>0.00649</v>
       </c>
       <c r="P85" t="n">
-        <v>0.151</v>
+        <v>0.03998</v>
       </c>
     </row>
     <row r="86">
@@ -4612,47 +4598,47 @@
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-11-2025</t>
+          <t>ADOM-SL8-8-2025</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.633</v>
+        <v>1.75</v>
       </c>
       <c r="E86" t="n">
-        <v>5.627</v>
+        <v>0.007</v>
       </c>
       <c r="F86" t="n">
-        <v>4.18</v>
+        <v>0.004113</v>
       </c>
       <c r="G86" t="n">
-        <v>6.65</v>
+        <v>1.267</v>
       </c>
       <c r="H86" t="n">
-        <v>69</v>
+        <v>0.5525</v>
       </c>
       <c r="I86" t="n">
-        <v>4.516</v>
+        <v>4.234</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7482</v>
+        <v>0.6378</v>
       </c>
       <c r="K86" t="n">
-        <v>1.331</v>
+        <v>1.316</v>
       </c>
       <c r="L86" t="n">
-        <v>15.08</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>0.01619</v>
+        <v>0.003329</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2836</v>
+        <v>0.06454</v>
       </c>
       <c r="O86" t="n">
-        <v>0.02505</v>
+        <v>0.007661</v>
       </c>
       <c r="P86" t="n">
-        <v>0.1678</v>
+        <v>0.05387</v>
       </c>
     </row>
     <row r="87">
@@ -4660,95 +4646,99 @@
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-12-2025</t>
+          <t>ADOM-SL8-9-2025</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.479</v>
+        <v>1.182</v>
       </c>
       <c r="E87" t="n">
-        <v>4.749</v>
+        <v>0.016</v>
       </c>
       <c r="F87" t="n">
-        <v>5.649</v>
+        <v>0.006689</v>
       </c>
       <c r="G87" t="n">
-        <v>6.79</v>
+        <v>2.747</v>
       </c>
       <c r="H87" t="n">
-        <v>69</v>
+        <v>0.5825</v>
       </c>
       <c r="I87" t="n">
-        <v>4.708</v>
+        <v>5.901</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8904</v>
+        <v>0.6947</v>
       </c>
       <c r="K87" t="n">
-        <v>1.389</v>
+        <v>1.408</v>
       </c>
       <c r="L87" t="n">
-        <v>11.95</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="M87" t="n">
-        <v>0.01543</v>
+        <v>0.004853</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2227</v>
+        <v>0.0825</v>
       </c>
       <c r="O87" t="n">
-        <v>0.024</v>
+        <v>0.007982</v>
       </c>
       <c r="P87" t="n">
-        <v>0.1317</v>
+        <v>0.05669</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="n"/>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>Storage 9</t>
+        </is>
+      </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13-2025</t>
+          <t>ADOM-SL9-1-2025</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.534</v>
+        <v>3.314</v>
       </c>
       <c r="E88" t="n">
-        <v>5.214</v>
+        <v>0.13</v>
       </c>
       <c r="F88" t="n">
-        <v>6.239</v>
+        <v>0.009601</v>
       </c>
       <c r="G88" t="n">
-        <v>6.1</v>
+        <v>5.618</v>
       </c>
       <c r="H88" t="n">
-        <v>69</v>
+        <v>2.314</v>
       </c>
       <c r="I88" t="n">
-        <v>5.237</v>
+        <v>4.796</v>
       </c>
       <c r="J88" t="n">
-        <v>1.018</v>
+        <v>1.604</v>
       </c>
       <c r="K88" t="n">
-        <v>1.44</v>
+        <v>1.397</v>
       </c>
       <c r="L88" t="n">
-        <v>11.23</v>
+        <v>6.788</v>
       </c>
       <c r="M88" t="n">
-        <v>0.0153</v>
+        <v>0.02092</v>
       </c>
       <c r="N88" t="n">
-        <v>0.1998</v>
+        <v>0.1221</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0244</v>
+        <v>0.047</v>
       </c>
       <c r="P88" t="n">
-        <v>0.1157</v>
+        <v>0.1436</v>
       </c>
     </row>
     <row r="89">
@@ -4756,47 +4746,47 @@
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13-2025</t>
+          <t>ADOM-SL9-10-2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.534</v>
+        <v>3.048</v>
       </c>
       <c r="E89" t="n">
-        <v>5.214</v>
+        <v>0.143</v>
       </c>
       <c r="F89" t="n">
-        <v>6.239</v>
+        <v>0.01267</v>
       </c>
       <c r="G89" t="n">
-        <v>6.1</v>
+        <v>5.589</v>
       </c>
       <c r="H89" t="n">
-        <v>69</v>
+        <v>2.559</v>
       </c>
       <c r="I89" t="n">
-        <v>5.237</v>
+        <v>4.577</v>
       </c>
       <c r="J89" t="n">
-        <v>1.018</v>
+        <v>0.7893</v>
       </c>
       <c r="K89" t="n">
-        <v>1.44</v>
+        <v>1.356</v>
       </c>
       <c r="L89" t="n">
-        <v>11.23</v>
+        <v>13.18</v>
       </c>
       <c r="M89" t="n">
-        <v>0.0153</v>
+        <v>0.0154</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1998</v>
+        <v>0.2518</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0244</v>
+        <v>0.02429</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1157</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="90">
@@ -4804,47 +4794,47 @@
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-2-2025</t>
+          <t>ADOM-SL9-11-2025</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.942</v>
+        <v>3.237</v>
       </c>
       <c r="E90" t="n">
-        <v>5.405</v>
+        <v>0.139</v>
       </c>
       <c r="F90" t="n">
-        <v>3.425</v>
+        <v>0.009639999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>7.23</v>
+        <v>5.627</v>
       </c>
       <c r="H90" t="n">
-        <v>173</v>
+        <v>2.47</v>
       </c>
       <c r="I90" t="n">
-        <v>7.363</v>
+        <v>4.516</v>
       </c>
       <c r="J90" t="n">
-        <v>1.082</v>
+        <v>0.7482</v>
       </c>
       <c r="K90" t="n">
-        <v>1.689</v>
+        <v>1.331</v>
       </c>
       <c r="L90" t="n">
-        <v>11.72</v>
+        <v>15.08</v>
       </c>
       <c r="M90" t="n">
-        <v>0.01697</v>
+        <v>0.01619</v>
       </c>
       <c r="N90" t="n">
-        <v>0.3045</v>
+        <v>0.2836</v>
       </c>
       <c r="O90" t="n">
-        <v>0.03229</v>
+        <v>0.02505</v>
       </c>
       <c r="P90" t="n">
-        <v>0.09165</v>
+        <v>0.1678</v>
       </c>
     </row>
     <row r="91">
@@ -4852,47 +4842,47 @@
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-3-2025</t>
+          <t>ADOM-SL9-12-2025</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.148</v>
+        <v>2.907</v>
       </c>
       <c r="E91" t="n">
-        <v>5.191</v>
+        <v>0.14</v>
       </c>
       <c r="F91" t="n">
-        <v>3.334</v>
+        <v>0.01284</v>
       </c>
       <c r="G91" t="n">
-        <v>7.1</v>
+        <v>4.749</v>
       </c>
       <c r="H91" t="n">
-        <v>140</v>
+        <v>2.948</v>
       </c>
       <c r="I91" t="n">
-        <v>4.853</v>
+        <v>4.708</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9764</v>
+        <v>0.8904</v>
       </c>
       <c r="K91" t="n">
-        <v>1.381</v>
+        <v>1.389</v>
       </c>
       <c r="L91" t="n">
-        <v>11.48</v>
+        <v>11.95</v>
       </c>
       <c r="M91" t="n">
-        <v>0.01435</v>
+        <v>0.01543</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1855</v>
+        <v>0.2227</v>
       </c>
       <c r="O91" t="n">
-        <v>0.02142</v>
+        <v>0.024</v>
       </c>
       <c r="P91" t="n">
-        <v>0.111</v>
+        <v>0.1317</v>
       </c>
     </row>
     <row r="92">
@@ -4900,23 +4890,23 @@
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-4-2025</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.999</v>
+        <v>2.911</v>
       </c>
       <c r="E92" t="n">
-        <v>4.763</v>
+        <v>0.181</v>
       </c>
       <c r="F92" t="n">
-        <v>4.075</v>
+        <v>0.01485</v>
       </c>
       <c r="G92" t="n">
-        <v>6.98</v>
+        <v>5.214</v>
       </c>
       <c r="H92" t="n">
-        <v>143</v>
+        <v>3.471</v>
       </c>
       <c r="I92" t="n">
         <v>5.237</v>
@@ -4948,47 +4938,47 @@
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-5-2025</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.872</v>
+        <v>2.911</v>
       </c>
       <c r="E93" t="n">
-        <v>4.609</v>
+        <v>0.181</v>
       </c>
       <c r="F93" t="n">
-        <v>5.188</v>
+        <v>0.01485</v>
       </c>
       <c r="G93" t="n">
-        <v>7.02</v>
+        <v>5.214</v>
       </c>
       <c r="H93" t="n">
-        <v>110</v>
+        <v>3.471</v>
       </c>
       <c r="I93" t="n">
-        <v>5.117</v>
+        <v>5.237</v>
       </c>
       <c r="J93" t="n">
-        <v>1.06</v>
+        <v>1.018</v>
       </c>
       <c r="K93" t="n">
-        <v>1.442</v>
+        <v>1.44</v>
       </c>
       <c r="L93" t="n">
-        <v>8.09</v>
+        <v>11.23</v>
       </c>
       <c r="M93" t="n">
-        <v>0.01605</v>
+        <v>0.0153</v>
       </c>
       <c r="N93" t="n">
-        <v>0.2035</v>
+        <v>0.1998</v>
       </c>
       <c r="O93" t="n">
-        <v>0.02525</v>
+        <v>0.0244</v>
       </c>
       <c r="P93" t="n">
-        <v>0.124</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="94">
@@ -4996,47 +4986,47 @@
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-7-2025</t>
+          <t>ADOM-SL9-2-2025</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1.739</v>
+        <v>3.075</v>
       </c>
       <c r="E94" t="n">
-        <v>5.684</v>
+        <v>0.137</v>
       </c>
       <c r="F94" t="n">
-        <v>5.827</v>
+        <v>0.01</v>
       </c>
       <c r="G94" t="n">
-        <v>7.11</v>
+        <v>5.405</v>
       </c>
       <c r="H94" t="n">
-        <v>125</v>
+        <v>2.535</v>
       </c>
       <c r="I94" t="n">
-        <v>4.533</v>
+        <v>7.363</v>
       </c>
       <c r="J94" t="n">
-        <v>0.8555</v>
+        <v>1.082</v>
       </c>
       <c r="K94" t="n">
-        <v>1.361</v>
+        <v>1.689</v>
       </c>
       <c r="L94" t="n">
-        <v>12.25</v>
+        <v>11.72</v>
       </c>
       <c r="M94" t="n">
-        <v>0.01737</v>
+        <v>0.01697</v>
       </c>
       <c r="N94" t="n">
-        <v>0.2832</v>
+        <v>0.3045</v>
       </c>
       <c r="O94" t="n">
-        <v>0.02867</v>
+        <v>0.03229</v>
       </c>
       <c r="P94" t="n">
-        <v>0.1694</v>
+        <v>0.09165</v>
       </c>
     </row>
     <row r="95">
@@ -5044,47 +5034,47 @@
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-8-2025</t>
+          <t>ADOM-SL9-3-2025</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.529</v>
+        <v>3.024</v>
       </c>
       <c r="E95" t="n">
-        <v>6.126</v>
+        <v>0.141</v>
       </c>
       <c r="F95" t="n">
-        <v>5.31</v>
+        <v>0.009646</v>
       </c>
       <c r="G95" t="n">
-        <v>5.6</v>
+        <v>5.191</v>
       </c>
       <c r="H95" t="n">
-        <v>52</v>
+        <v>2.716</v>
       </c>
       <c r="I95" t="n">
-        <v>4.951</v>
+        <v>4.853</v>
       </c>
       <c r="J95" t="n">
-        <v>0.8032</v>
+        <v>0.9764</v>
       </c>
       <c r="K95" t="n">
-        <v>1.393</v>
+        <v>1.381</v>
       </c>
       <c r="L95" t="n">
-        <v>14.36</v>
+        <v>11.48</v>
       </c>
       <c r="M95" t="n">
-        <v>0.01786</v>
+        <v>0.01435</v>
       </c>
       <c r="N95" t="n">
-        <v>0.3555</v>
+        <v>0.1855</v>
       </c>
       <c r="O95" t="n">
-        <v>0.03093</v>
+        <v>0.02142</v>
       </c>
       <c r="P95" t="n">
-        <v>0.1761</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="96">
@@ -5092,99 +5082,95 @@
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL9-9-2025</t>
+          <t>ADOM-SL9-4-2025</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.697</v>
+        <v>3.171</v>
       </c>
       <c r="E96" t="n">
-        <v>5.754</v>
+        <v>0.146</v>
       </c>
       <c r="F96" t="n">
-        <v>5.339</v>
+        <v>0.009873</v>
       </c>
       <c r="G96" t="n">
-        <v>5.9</v>
+        <v>4.763</v>
       </c>
       <c r="H96" t="n">
-        <v>42</v>
+        <v>3.065</v>
       </c>
       <c r="I96" t="n">
-        <v>4.367</v>
+        <v>5.237</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7004</v>
+        <v>1.018</v>
       </c>
       <c r="K96" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="L96" t="n">
-        <v>15.31</v>
+        <v>11.23</v>
       </c>
       <c r="M96" t="n">
-        <v>0.01673</v>
+        <v>0.0153</v>
       </c>
       <c r="N96" t="n">
-        <v>0.3408</v>
+        <v>0.1998</v>
       </c>
       <c r="O96" t="n">
-        <v>0.02799</v>
+        <v>0.0244</v>
       </c>
       <c r="P96" t="n">
-        <v>0.1958</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
+      <c r="B97" s="1" t="n"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-1-2025</t>
+          <t>ADOM-SL9-5-2025</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.178</v>
+        <v>2.907</v>
       </c>
       <c r="E97" t="n">
-        <v>1.255</v>
+        <v>0.175</v>
       </c>
       <c r="F97" t="n">
-        <v>2.075</v>
+        <v>0.01333</v>
       </c>
       <c r="G97" t="n">
-        <v>8.300000000000001</v>
+        <v>4.609</v>
       </c>
       <c r="H97" t="n">
-        <v>120</v>
+        <v>3.797</v>
       </c>
       <c r="I97" t="n">
-        <v>4.83</v>
+        <v>5.117</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6644</v>
+        <v>1.06</v>
       </c>
       <c r="K97" t="n">
-        <v>1.461</v>
+        <v>1.442</v>
       </c>
       <c r="L97" t="n">
-        <v>14.82</v>
+        <v>8.09</v>
       </c>
       <c r="M97" t="n">
-        <v>0.003038</v>
+        <v>0.01605</v>
       </c>
       <c r="N97" t="n">
-        <v>0.06713</v>
+        <v>0.2035</v>
       </c>
       <c r="O97" t="n">
-        <v>0.006135</v>
+        <v>0.02525</v>
       </c>
       <c r="P97" t="n">
-        <v>0.05129</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="98">
@@ -5192,47 +5178,47 @@
       <c r="B98" s="1" t="n"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-2-2025</t>
+          <t>ADOM-SL9-7-2025</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.184</v>
+        <v>3.015</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9669</v>
+        <v>0.219</v>
       </c>
       <c r="F98" t="n">
-        <v>16.57</v>
+        <v>0.01513</v>
       </c>
       <c r="G98" t="n">
-        <v>9.300000000000001</v>
+        <v>5.684</v>
       </c>
       <c r="H98" t="n">
-        <v>47</v>
+        <v>3.853</v>
       </c>
       <c r="I98" t="n">
-        <v>4.517</v>
+        <v>4.533</v>
       </c>
       <c r="J98" t="n">
-        <v>0.584</v>
+        <v>0.8555</v>
       </c>
       <c r="K98" t="n">
-        <v>1.329</v>
+        <v>1.361</v>
       </c>
       <c r="L98" t="n">
-        <v>19.6</v>
+        <v>12.25</v>
       </c>
       <c r="M98" t="n">
-        <v>0.002565</v>
+        <v>0.01737</v>
       </c>
       <c r="N98" t="n">
-        <v>0.05626</v>
+        <v>0.2832</v>
       </c>
       <c r="O98" t="n">
-        <v>0.005975</v>
+        <v>0.02867</v>
       </c>
       <c r="P98" t="n">
-        <v>0.04882</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="99">
@@ -5240,47 +5226,47 @@
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-3-2025</t>
+          <t>ADOM-SL9-8-2025</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.379</v>
+        <v>2.893</v>
       </c>
       <c r="E99" t="n">
-        <v>1.36</v>
+        <v>0.181</v>
       </c>
       <c r="F99" t="n">
-        <v>3.238</v>
+        <v>0.01616</v>
       </c>
       <c r="G99" t="n">
-        <v>7.6</v>
+        <v>6.126</v>
       </c>
       <c r="H99" t="n">
-        <v>118</v>
+        <v>2.955</v>
       </c>
       <c r="I99" t="n">
-        <v>4.169</v>
+        <v>4.951</v>
       </c>
       <c r="J99" t="n">
-        <v>0.755</v>
+        <v>0.8032</v>
       </c>
       <c r="K99" t="n">
-        <v>1.382</v>
+        <v>1.393</v>
       </c>
       <c r="L99" t="n">
-        <v>12.41</v>
+        <v>14.36</v>
       </c>
       <c r="M99" t="n">
-        <v>0.0016</v>
+        <v>0.01786</v>
       </c>
       <c r="N99" t="n">
-        <v>0.01986</v>
+        <v>0.3555</v>
       </c>
       <c r="O99" t="n">
-        <v>0.003855</v>
+        <v>0.03093</v>
       </c>
       <c r="P99" t="n">
-        <v>0.03123</v>
+        <v>0.1761</v>
       </c>
     </row>
     <row r="100">
@@ -5288,95 +5274,99 @@
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-5-2025</t>
+          <t>ADOM-SL9-9-2025</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.8895</v>
+        <v>3.07</v>
       </c>
       <c r="E100" t="n">
-        <v>0.948</v>
+        <v>0.195</v>
       </c>
       <c r="F100" t="n">
-        <v>0.849</v>
+        <v>0.01657</v>
       </c>
       <c r="G100" t="n">
-        <v>7.5</v>
+        <v>5.754</v>
       </c>
       <c r="H100" t="n">
-        <v>118</v>
+        <v>3.389</v>
       </c>
       <c r="I100" t="n">
-        <v>4.463</v>
+        <v>4.367</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5681</v>
+        <v>0.7004</v>
       </c>
       <c r="K100" t="n">
-        <v>1.396</v>
+        <v>1.32</v>
       </c>
       <c r="L100" t="n">
-        <v>18.02</v>
+        <v>15.31</v>
       </c>
       <c r="M100" t="n">
-        <v>0.002735</v>
+        <v>0.01673</v>
       </c>
       <c r="N100" t="n">
-        <v>0.06064</v>
+        <v>0.3408</v>
       </c>
       <c r="O100" t="n">
-        <v>0.006006</v>
+        <v>0.02799</v>
       </c>
       <c r="P100" t="n">
-        <v>0.05267</v>
+        <v>0.1958</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n"/>
-      <c r="B101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>Baikal</t>
+        </is>
+      </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B2-1-2025</t>
+          <t>ADOM-SLB-B-1-2025</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2.991</v>
+        <v>2.231</v>
       </c>
       <c r="E101" t="n">
-        <v>1.909</v>
+        <v>0.033</v>
       </c>
       <c r="F101" t="n">
-        <v>1.154</v>
+        <v>0.004534</v>
       </c>
       <c r="G101" t="n">
-        <v>9.1</v>
+        <v>2.58</v>
       </c>
       <c r="H101" t="n">
-        <v>59</v>
+        <v>1.279</v>
       </c>
       <c r="I101" t="n">
-        <v>4.992</v>
+        <v>4.704</v>
       </c>
       <c r="J101" t="n">
-        <v>1.219</v>
+        <v>0.8225</v>
       </c>
       <c r="K101" t="n">
-        <v>1.586</v>
+        <v>1.411</v>
       </c>
       <c r="L101" t="n">
-        <v>7.106</v>
+        <v>11.5</v>
       </c>
       <c r="M101" t="n">
-        <v>0.007555</v>
+        <v>0.005262</v>
       </c>
       <c r="N101" t="n">
-        <v>0.06475</v>
+        <v>0.05857</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0111</v>
+        <v>0.008392999999999999</v>
       </c>
       <c r="P101" t="n">
-        <v>0.06783</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="102">
@@ -5384,47 +5374,47 @@
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B2-3-2025</t>
+          <t>ADOM-SLB-B-2-2025</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.886</v>
+        <v>2.909</v>
       </c>
       <c r="E102" t="n">
-        <v>4.241</v>
+        <v>0.036</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6842</v>
+        <v>0.005273</v>
       </c>
       <c r="G102" t="n">
-        <v>7.56</v>
+        <v>1.83</v>
       </c>
       <c r="H102" t="n">
-        <v>138</v>
+        <v>1.967</v>
       </c>
       <c r="I102" t="n">
-        <v>4.423</v>
+        <v>4.729</v>
       </c>
       <c r="J102" t="n">
-        <v>1.4</v>
+        <v>0.7667</v>
       </c>
       <c r="K102" t="n">
-        <v>1.452</v>
+        <v>1.493</v>
       </c>
       <c r="L102" t="n">
-        <v>4.868</v>
+        <v>12.46</v>
       </c>
       <c r="M102" t="n">
-        <v>0.008389000000000001</v>
+        <v>0.005723</v>
       </c>
       <c r="N102" t="n">
-        <v>0.03517</v>
+        <v>0.08099000000000001</v>
       </c>
       <c r="O102" t="n">
-        <v>0.01446</v>
+        <v>0.008656</v>
       </c>
       <c r="P102" t="n">
-        <v>0.06918000000000001</v>
+        <v>0.06659</v>
       </c>
     </row>
     <row r="103">
@@ -5432,47 +5422,47 @@
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-1-2025</t>
+          <t>ADOM-SLB-B1-1-2025</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.329</v>
+        <v>2.182</v>
       </c>
       <c r="E103" t="n">
-        <v>2.923</v>
+        <v>0.026</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7537</v>
+        <v>0.005204</v>
       </c>
       <c r="G103" t="n">
-        <v>8.800000000000001</v>
+        <v>1.255</v>
       </c>
       <c r="H103" t="n">
-        <v>82</v>
+        <v>2.072</v>
       </c>
       <c r="I103" t="n">
-        <v>4.675</v>
+        <v>4.83</v>
       </c>
       <c r="J103" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6644</v>
       </c>
       <c r="K103" t="n">
-        <v>1.45</v>
+        <v>1.461</v>
       </c>
       <c r="L103" t="n">
-        <v>14.43</v>
+        <v>14.82</v>
       </c>
       <c r="M103" t="n">
-        <v>0.006542</v>
+        <v>0.003038</v>
       </c>
       <c r="N103" t="n">
-        <v>0.1098</v>
+        <v>0.06713</v>
       </c>
       <c r="O103" t="n">
-        <v>0.01137</v>
+        <v>0.006135</v>
       </c>
       <c r="P103" t="n">
-        <v>0.08056000000000001</v>
+        <v>0.05129</v>
       </c>
     </row>
     <row r="104">
@@ -5480,47 +5470,45 @@
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-2-2025</t>
+          <t>ADOM-SLB-B1-2-2025</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.764</v>
+        <v>2.769</v>
       </c>
       <c r="E104" t="n">
-        <v>2.336</v>
-      </c>
-      <c r="F104" t="n">
-        <v>8.394</v>
-      </c>
+        <v>0.048</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>8.6</v>
+        <v>0.9669</v>
       </c>
       <c r="H104" t="n">
-        <v>108</v>
+        <v>4.964</v>
       </c>
       <c r="I104" t="n">
-        <v>3.917</v>
+        <v>4.517</v>
       </c>
       <c r="J104" t="n">
-        <v>0.725</v>
+        <v>0.584</v>
       </c>
       <c r="K104" t="n">
-        <v>1.285</v>
+        <v>1.329</v>
       </c>
       <c r="L104" t="n">
-        <v>14.83</v>
+        <v>19.6</v>
       </c>
       <c r="M104" t="n">
-        <v>0.03162</v>
+        <v>0.002565</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4224</v>
+        <v>0.05626</v>
       </c>
       <c r="O104" t="n">
-        <v>0.03417</v>
+        <v>0.005975</v>
       </c>
       <c r="P104" t="n">
-        <v>0.3151</v>
+        <v>0.04882</v>
       </c>
     </row>
     <row r="105">
@@ -5528,47 +5516,45 @@
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B3-3-2025</t>
+          <t>ADOM-SLB-B1-3-2025</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.818</v>
+        <v>1.846</v>
       </c>
       <c r="E105" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1.169</v>
-      </c>
+        <v>0.028</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>9.6</v>
+        <v>1.36</v>
       </c>
       <c r="H105" t="n">
-        <v>132</v>
+        <v>2.059</v>
       </c>
       <c r="I105" t="n">
-        <v>5.659</v>
+        <v>4.169</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8879</v>
+        <v>0.755</v>
       </c>
       <c r="K105" t="n">
-        <v>1.552</v>
+        <v>1.382</v>
       </c>
       <c r="L105" t="n">
-        <v>11.61</v>
+        <v>12.41</v>
       </c>
       <c r="M105" t="n">
-        <v>0.006405</v>
+        <v>0.0016</v>
       </c>
       <c r="N105" t="n">
-        <v>0.08916</v>
+        <v>0.01986</v>
       </c>
       <c r="O105" t="n">
-        <v>0.009858</v>
+        <v>0.003855</v>
       </c>
       <c r="P105" t="n">
-        <v>0.06308999999999999</v>
+        <v>0.03123</v>
       </c>
     </row>
     <row r="106">
@@ -5576,47 +5562,47 @@
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SLB-BO-2-2025</t>
+          <t>ADOM-SLB-B1-5-2025</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.816</v>
+        <v>0.8889</v>
       </c>
       <c r="E106" t="n">
-        <v>2.27</v>
+        <v>0.008</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9262</v>
+        <v>0.004991</v>
       </c>
       <c r="G106" t="n">
-        <v>8.5</v>
+        <v>0.948</v>
       </c>
       <c r="H106" t="n">
-        <v>18</v>
+        <v>0.8439</v>
       </c>
       <c r="I106" t="n">
-        <v>5.274</v>
+        <v>4.463</v>
       </c>
       <c r="J106" t="n">
-        <v>0.7196</v>
+        <v>0.5681</v>
       </c>
       <c r="K106" t="n">
-        <v>1.503</v>
+        <v>1.396</v>
       </c>
       <c r="L106" t="n">
-        <v>10.89</v>
+        <v>18.02</v>
       </c>
       <c r="M106" t="n">
-        <v>0.00346</v>
+        <v>0.002735</v>
       </c>
       <c r="N106" t="n">
-        <v>0.07242</v>
+        <v>0.06064</v>
       </c>
       <c r="O106" t="n">
-        <v>0.006231</v>
+        <v>0.006006</v>
       </c>
       <c r="P106" t="n">
-        <v>0.05028</v>
+        <v>0.05267</v>
       </c>
     </row>
     <row r="107">
@@ -5624,63 +5610,349 @@
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
+          <t>ADOM-SLB-B2-1-2025</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="I107" t="n">
+        <v>4.992</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.106</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.007555</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.06783</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="n"/>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SLB-B2-3-2025</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.004164</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4.241</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.6838</v>
+      </c>
+      <c r="I108" t="n">
+        <v>4.423</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4.868</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.008389000000000001</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.06918000000000001</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="n"/>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SLB-B3-1-2025</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.003777</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.7527</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4.675</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L109" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.006542</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.01137</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.08056000000000001</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="n"/>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SLB-B3-2-2025</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>4.531</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.006553</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="H110" t="n">
+        <v>7.021</v>
+      </c>
+      <c r="I110" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L110" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.03162</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.3151</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="n"/>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SLB-B3-3-2025</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.004272</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="I111" t="n">
+        <v>5.659</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.8879</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.006405</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.08916</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.009858</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="n"/>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SLB-BO-2-2025</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.004834</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.9251</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5.274</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="L112" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.00346</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.07242</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.006231</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.05028</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n"/>
+      <c r="B113" s="1" t="n"/>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
           <t>ADOM-SLB-BO-3-2025</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D113" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.006262</v>
+      </c>
+      <c r="G113" t="n">
         <v>1.902</v>
       </c>
-      <c r="F107" t="n">
-        <v>1.106</v>
-      </c>
-      <c r="G107" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="H107" t="n">
-        <v>24</v>
-      </c>
-      <c r="I107" t="n">
+      <c r="H113" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="I113" t="n">
         <v>4.594</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J113" t="n">
         <v>0.7145</v>
       </c>
-      <c r="K107" t="n">
+      <c r="K113" t="n">
         <v>1.369</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L113" t="n">
         <v>13.52</v>
       </c>
-      <c r="M107" t="n">
+      <c r="M113" t="n">
         <v>0.003427</v>
       </c>
-      <c r="N107" t="n">
+      <c r="N113" t="n">
         <v>0.06415</v>
       </c>
-      <c r="O107" t="n">
+      <c r="O113" t="n">
         <v>0.006812</v>
       </c>
-      <c r="P107" t="n">
+      <c r="P113" t="n">
         <v>0.05444</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B39:B50"/>
-    <mergeCell ref="B66:B74"/>
-    <mergeCell ref="B30:B38"/>
-    <mergeCell ref="B75:B83"/>
-    <mergeCell ref="B97:B107"/>
+    <mergeCell ref="B70:B78"/>
+    <mergeCell ref="B31:B40"/>
+    <mergeCell ref="B79:B87"/>
     <mergeCell ref="B20:B27"/>
-    <mergeCell ref="B51:B65"/>
-    <mergeCell ref="A2:A107"/>
+    <mergeCell ref="A2:A113"/>
+    <mergeCell ref="B88:B100"/>
     <mergeCell ref="B11:B19"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B55:B69"/>
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B84:B96"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B101:B113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
